--- a/docs/lem/files/xslope_acads_simple.xlsx
+++ b/docs/lem/files/xslope_acads_simple.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/lem/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3293A3-B1F8-4840-BCCF-D44260C5241D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4EF2E34-D733-5B43-BA55-58EC7C920AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25040" yWindow="2500" windowWidth="42700" windowHeight="22800" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
+    <workbookView xWindow="25040" yWindow="2500" windowWidth="42700" windowHeight="22800" activeTab="2" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
     <definedName name="solution2">mat!#REF!</definedName>
     <definedName name="version">main!$D$5</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="182">
   <si>
     <t>X</t>
   </si>
@@ -752,6 +752,9 @@
   </si>
   <si>
     <t>Fixity</t>
+  </si>
+  <si>
+    <t>Soil</t>
   </si>
 </sst>
 </file>
@@ -1209,13 +1212,13 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1392,6 +1395,18 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>90</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -1401,6 +1416,18 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>35</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -12430,37 +12457,40 @@
       <c r="A9" s="3">
         <v>1</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Soil</t>
-        </is>
+      <c r="B9" s="3" t="s">
+        <v>181</v>
       </c>
       <c r="C9" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>mc</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="E9" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F9" s="3">
-        <v>19.6</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
+      <c r="K9" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="L9" s="3">
+        <f>C9*0.06</f>
+        <v>1.2</v>
+      </c>
+      <c r="M9" s="3">
+        <f>E9*0.6</f>
+        <v>1.7999999999999998</v>
+      </c>
+      <c r="N9" s="3">
+        <f>F9*0.14</f>
+        <v>2.7440000000000007</v>
+      </c>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
@@ -13226,74 +13256,74 @@
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="52"/>
-      <c r="D4" s="52" t="s">
+      <c r="B4" s="50"/>
+      <c r="D4" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="52"/>
-      <c r="G4" s="52" t="s">
+      <c r="E4" s="50"/>
+      <c r="G4" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="52"/>
-      <c r="J4" s="52" t="s">
+      <c r="H4" s="50"/>
+      <c r="J4" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="52"/>
-      <c r="M4" s="52" t="s">
+      <c r="K4" s="50"/>
+      <c r="M4" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="52"/>
-      <c r="P4" s="52" t="s">
+      <c r="N4" s="50"/>
+      <c r="P4" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="52"/>
+      <c r="Q4" s="50"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="52" t="s">
+      <c r="S4" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="T4" s="52"/>
+      <c r="T4" s="50"/>
       <c r="U4" s="1"/>
-      <c r="V4" s="52" t="s">
+      <c r="V4" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="W4" s="52"/>
+      <c r="W4" s="50"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="52" t="s">
+      <c r="Y4" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="Z4" s="52"/>
+      <c r="Z4" s="50"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="52" t="s">
+      <c r="AB4" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="AC4" s="52"/>
-      <c r="AE4" s="52" t="s">
+      <c r="AC4" s="50"/>
+      <c r="AE4" s="50" t="s">
         <v>114</v>
       </c>
-      <c r="AF4" s="52"/>
+      <c r="AF4" s="50"/>
       <c r="AG4" s="1"/>
-      <c r="AH4" s="52" t="s">
+      <c r="AH4" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="AI4" s="52"/>
+      <c r="AI4" s="50"/>
       <c r="AJ4" s="1"/>
-      <c r="AK4" s="52" t="s">
+      <c r="AK4" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="AL4" s="52"/>
+      <c r="AL4" s="50"/>
       <c r="AM4" s="1"/>
-      <c r="AN4" s="52" t="s">
+      <c r="AN4" s="50" t="s">
         <v>117</v>
       </c>
-      <c r="AO4" s="52"/>
+      <c r="AO4" s="50"/>
       <c r="AP4" s="1"/>
-      <c r="AQ4" s="52" t="s">
+      <c r="AQ4" s="50" t="s">
         <v>118</v>
       </c>
-      <c r="AR4" s="52"/>
+      <c r="AR4" s="50"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="41" t="s">
@@ -13396,89 +13426,89 @@
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A6" s="50" t="str">
+      <c r="A6" s="51" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
-        <v/>
-      </c>
-      <c r="B6" s="51"/>
-      <c r="D6" s="50" t="str">
+        <v>Soil</v>
+      </c>
+      <c r="B6" s="52"/>
+      <c r="D6" s="51" t="str">
         <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="E6" s="51"/>
-      <c r="G6" s="50" t="str">
+      <c r="E6" s="52"/>
+      <c r="G6" s="51" t="str">
         <f>_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="H6" s="51"/>
-      <c r="J6" s="50" t="str">
+      <c r="H6" s="52"/>
+      <c r="J6" s="51" t="str">
         <f>_xlfn.XLOOKUP(K5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="K6" s="51"/>
-      <c r="M6" s="50" t="str">
+      <c r="K6" s="52"/>
+      <c r="M6" s="51" t="str">
         <f>_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="N6" s="51"/>
-      <c r="P6" s="50" t="str">
+      <c r="N6" s="52"/>
+      <c r="P6" s="51" t="str">
         <f>_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Q6" s="51"/>
+      <c r="Q6" s="52"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="50" t="str">
+      <c r="S6" s="51" t="str">
         <f>_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="T6" s="51"/>
+      <c r="T6" s="52"/>
       <c r="U6" s="1"/>
-      <c r="V6" s="50" t="str">
+      <c r="V6" s="51" t="str">
         <f>_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="W6" s="51"/>
+      <c r="W6" s="52"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="50" t="str">
+      <c r="Y6" s="51" t="str">
         <f>_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Z6" s="51"/>
+      <c r="Z6" s="52"/>
       <c r="AA6" s="1"/>
-      <c r="AB6" s="50" t="str">
+      <c r="AB6" s="51" t="str">
         <f>_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AC6" s="51"/>
-      <c r="AE6" s="50" t="str">
+      <c r="AC6" s="52"/>
+      <c r="AE6" s="51" t="str">
         <f>_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AF6" s="51"/>
+      <c r="AF6" s="52"/>
       <c r="AG6" s="1"/>
-      <c r="AH6" s="50" t="str">
+      <c r="AH6" s="51" t="str">
         <f>_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AI6" s="51"/>
+      <c r="AI6" s="52"/>
       <c r="AJ6" s="1"/>
-      <c r="AK6" s="50" t="str">
+      <c r="AK6" s="51" t="str">
         <f>_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AL6" s="51"/>
+      <c r="AL6" s="52"/>
       <c r="AM6" s="1"/>
-      <c r="AN6" s="50" t="str">
+      <c r="AN6" s="51" t="str">
         <f>_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AO6" s="51"/>
+      <c r="AO6" s="52"/>
       <c r="AP6" s="1"/>
-      <c r="AQ6" s="50" t="str">
+      <c r="AQ6" s="51" t="str">
         <f>_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AR6" s="51"/>
+      <c r="AR6" s="52"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -13582,7 +13612,7 @@
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B8" s="3">
         <v>25</v>
@@ -13714,7 +13744,7 @@
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="B11" s="3">
         <v>35</v>
@@ -14398,36 +14428,36 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="AE6:AF6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AK6:AL6"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AQ6:AR6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AQ4:AR4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="M4:N4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AQ4:AR4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AE6:AF6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AK6:AL6"/>
-    <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="AQ6:AR6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14465,74 +14495,74 @@
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="50" t="s">
         <v>153</v>
       </c>
-      <c r="B4" s="52"/>
-      <c r="D4" s="52" t="s">
+      <c r="B4" s="50"/>
+      <c r="D4" s="50" t="s">
         <v>154</v>
       </c>
-      <c r="E4" s="52"/>
-      <c r="G4" s="52" t="s">
+      <c r="E4" s="50"/>
+      <c r="G4" s="50" t="s">
         <v>155</v>
       </c>
-      <c r="H4" s="52"/>
-      <c r="J4" s="52" t="s">
+      <c r="H4" s="50"/>
+      <c r="J4" s="50" t="s">
         <v>156</v>
       </c>
-      <c r="K4" s="52"/>
-      <c r="M4" s="52" t="s">
+      <c r="K4" s="50"/>
+      <c r="M4" s="50" t="s">
         <v>157</v>
       </c>
-      <c r="N4" s="52"/>
-      <c r="P4" s="52" t="s">
+      <c r="N4" s="50"/>
+      <c r="P4" s="50" t="s">
         <v>158</v>
       </c>
-      <c r="Q4" s="52"/>
+      <c r="Q4" s="50"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="52" t="s">
+      <c r="S4" s="50" t="s">
         <v>159</v>
       </c>
-      <c r="T4" s="52"/>
+      <c r="T4" s="50"/>
       <c r="U4" s="1"/>
-      <c r="V4" s="52" t="s">
+      <c r="V4" s="50" t="s">
         <v>160</v>
       </c>
-      <c r="W4" s="52"/>
+      <c r="W4" s="50"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="52" t="s">
+      <c r="Y4" s="50" t="s">
         <v>161</v>
       </c>
-      <c r="Z4" s="52"/>
+      <c r="Z4" s="50"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="52" t="s">
+      <c r="AB4" s="50" t="s">
         <v>162</v>
       </c>
-      <c r="AC4" s="52"/>
-      <c r="AE4" s="52" t="s">
+      <c r="AC4" s="50"/>
+      <c r="AE4" s="50" t="s">
         <v>163</v>
       </c>
-      <c r="AF4" s="52"/>
+      <c r="AF4" s="50"/>
       <c r="AG4" s="1"/>
-      <c r="AH4" s="52" t="s">
+      <c r="AH4" s="50" t="s">
         <v>164</v>
       </c>
-      <c r="AI4" s="52"/>
+      <c r="AI4" s="50"/>
       <c r="AJ4" s="1"/>
-      <c r="AK4" s="52" t="s">
+      <c r="AK4" s="50" t="s">
         <v>165</v>
       </c>
-      <c r="AL4" s="52"/>
+      <c r="AL4" s="50"/>
       <c r="AM4" s="1"/>
-      <c r="AN4" s="52" t="s">
+      <c r="AN4" s="50" t="s">
         <v>166</v>
       </c>
-      <c r="AO4" s="52"/>
+      <c r="AO4" s="50"/>
       <c r="AP4" s="1"/>
-      <c r="AQ4" s="52" t="s">
+      <c r="AQ4" s="50" t="s">
         <v>167</v>
       </c>
-      <c r="AR4" s="52"/>
+      <c r="AR4" s="50"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="43" t="s">
@@ -14637,7 +14667,7 @@
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A6" s="53" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
-        <v/>
+        <v>Soil</v>
       </c>
       <c r="B6" s="54"/>
       <c r="D6" s="53" t="str">
@@ -15621,12 +15651,14 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AQ6:AR6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="AE6:AF6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AK6:AL6"/>
     <mergeCell ref="AK4:AL4"/>
     <mergeCell ref="AN4:AO4"/>
     <mergeCell ref="AQ4:AR4"/>
@@ -15643,14 +15675,12 @@
     <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="AE4:AF4"/>
     <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="AQ6:AR6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AE6:AF6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AK6:AL6"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15873,10 +15903,8 @@
       <c r="C3" s="3">
         <v>45</v>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
+      <c r="D3" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3">
@@ -15903,10 +15931,8 @@
       <c r="C4" s="3">
         <v>48</v>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Depth</t>
-        </is>
+      <c r="D4" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="E4" s="3">
         <v>20</v>

--- a/docs/lem/files/xslope_acads_simple.xlsx
+++ b/docs/lem/files/xslope_acads_simple.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/lem/files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4EF2E34-D733-5B43-BA55-58EC7C920AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D53F4FFA-A72E-9849-8C3B-3C3A51EB7D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25040" yWindow="2500" windowWidth="42700" windowHeight="22800" activeTab="2" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
+    <workbookView xWindow="11520" yWindow="2900" windowWidth="42700" windowHeight="22800" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -25,8 +25,9 @@
     <sheet name="dloads (2)" sheetId="13" r:id="rId10"/>
     <sheet name="reinforce" sheetId="12" r:id="rId11"/>
     <sheet name="piles" sheetId="16" r:id="rId12"/>
-    <sheet name="seep bc" sheetId="11" r:id="rId13"/>
-    <sheet name="seep bc (2)" sheetId="14" r:id="rId14"/>
+    <sheet name="lloads" sheetId="17" r:id="rId13"/>
+    <sheet name="seep bc" sheetId="11" r:id="rId14"/>
+    <sheet name="seep bc (2)" sheetId="14" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="crack_depth">main!$D$9</definedName>
@@ -40,7 +41,7 @@
     <definedName name="solution2">mat!#REF!</definedName>
     <definedName name="version">main!$D$5</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -61,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="212">
   <si>
     <t>X</t>
   </si>
@@ -422,9 +423,6 @@
     <t>Piezometric Line 1</t>
   </si>
   <si>
-    <t>Pore presssue (u) options</t>
-  </si>
-  <si>
     <t>u</t>
   </si>
   <si>
@@ -492,12 +490,6 @@
   </si>
   <si>
     <t>Tmax</t>
-  </si>
-  <si>
-    <t>Required for FEM only</t>
-  </si>
-  <si>
-    <t>Required for both LEM and FEM</t>
   </si>
   <si>
     <t>Lp1</t>
@@ -754,14 +746,130 @@
     <t>Fixity</t>
   </si>
   <si>
-    <t>Soil</t>
+    <t>unsat</t>
+  </si>
+  <si>
+    <t>lf</t>
+  </si>
+  <si>
+    <t>vg</t>
+  </si>
+  <si>
+    <t>linear front model (kr0,h0)</t>
+  </si>
+  <si>
+    <t>van Genuchten model (vb_a, vg_n)</t>
+  </si>
+  <si>
+    <t>Unsat model option</t>
+  </si>
+  <si>
+    <t>vg_a</t>
+  </si>
+  <si>
+    <t>vg_n</t>
+  </si>
+  <si>
+    <t>Pore pressure (u) options</t>
+  </si>
+  <si>
+    <t>pow</t>
+  </si>
+  <si>
+    <t>ru</t>
+  </si>
+  <si>
+    <t>pow_a</t>
+  </si>
+  <si>
+    <t>pow_b</t>
+  </si>
+  <si>
+    <t>pow_c</t>
+  </si>
+  <si>
+    <t>pow_d</t>
+  </si>
+  <si>
+    <t>Appl</t>
+  </si>
+  <si>
+    <t>Tend1</t>
+  </si>
+  <si>
+    <t>Tend2</t>
+  </si>
+  <si>
+    <t>Geosynthetic</t>
+  </si>
+  <si>
+    <t>Tangent</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Nail</t>
+  </si>
+  <si>
+    <t>Axial</t>
+  </si>
+  <si>
+    <t>Passive</t>
+  </si>
+  <si>
+    <t>Tieback</t>
+  </si>
+  <si>
+    <t>Anchor</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>g</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>sat</t>
+    </r>
+  </si>
+  <si>
+    <t>Pore pressure ratio (u = ru * sigma_v)</t>
+  </si>
+  <si>
+    <t>Power curve envelope: t = pow_a * (sn + pow_d)^pow_b + pow_c</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Dir</t>
+  </si>
+  <si>
+    <t>Spacing</t>
+  </si>
+  <si>
+    <t>Angle</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -891,6 +999,17 @@
       <color theme="0"/>
       <name val="Symbol"/>
       <charset val="2"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow (Body)"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="17">
@@ -1077,7 +1196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1206,12 +1325,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1249,7 +1375,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="15">
     <dxf>
       <fill>
         <patternFill>
@@ -1268,6 +1394,20 @@
       <fill>
         <patternFill>
           <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1302,7 +1442,35 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="2" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1395,18 +1563,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>50</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>90</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -1416,18 +1572,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
-                <c:pt idx="0">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>35</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -4161,7 +4305,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$3,reinforce!$D$3)</c:f>
+              <c:f>(reinforce!$C$3,reinforce!$E$3)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4170,7 +4314,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$3,reinforce!$E$3)</c:f>
+              <c:f>(reinforce!$D$3,reinforce!$F$3)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4222,7 +4366,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$4,reinforce!$D$4)</c:f>
+              <c:f>(reinforce!$C$4,reinforce!$E$4)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4231,7 +4375,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$4,reinforce!$C$4,reinforce!$C$4,reinforce!$E$4)</c:f>
+              <c:f>(reinforce!$D$4,reinforce!$D$4,reinforce!$D$4,reinforce!$F$4)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -4283,7 +4427,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$5,reinforce!$D$5)</c:f>
+              <c:f>(reinforce!$C$5,reinforce!$E$5)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4292,7 +4436,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$5,reinforce!$E$5)</c:f>
+              <c:f>(reinforce!$D$5,reinforce!$F$5)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4344,7 +4488,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$6,reinforce!$D$6)</c:f>
+              <c:f>(reinforce!$C$6,reinforce!$E$6)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4353,7 +4497,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$6,reinforce!$E$6)</c:f>
+              <c:f>(reinforce!$D$6,reinforce!$F$6)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4408,7 +4552,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$7,reinforce!$D$7)</c:f>
+              <c:f>(reinforce!$C$7,reinforce!$E$7)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4417,7 +4561,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$7,reinforce!$E$7)</c:f>
+              <c:f>(reinforce!$D$7,reinforce!$F$7)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4472,7 +4616,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$8,reinforce!$D$8)</c:f>
+              <c:f>(reinforce!$C$8,reinforce!$E$8)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4481,7 +4625,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$8,reinforce!$E$8)</c:f>
+              <c:f>(reinforce!$D$8,reinforce!$F$8)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4536,7 +4680,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$9,reinforce!$D$9)</c:f>
+              <c:f>(reinforce!$C$9,reinforce!$E$9)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4545,7 +4689,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$9,reinforce!$E$9)</c:f>
+              <c:f>(reinforce!$D$9,reinforce!$F$9)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4600,7 +4744,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$10,reinforce!$D$10)</c:f>
+              <c:f>(reinforce!$C$10,reinforce!$E$10)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4609,7 +4753,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$10,reinforce!$E$10)</c:f>
+              <c:f>(reinforce!$D$10,reinforce!$F$10)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4664,7 +4808,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$11,reinforce!$D$11)</c:f>
+              <c:f>(reinforce!$C$11,reinforce!$E$11)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4673,7 +4817,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$11,reinforce!$E$11)</c:f>
+              <c:f>(reinforce!$D$11,reinforce!$F$11)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4728,7 +4872,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$12,reinforce!$D$12)</c:f>
+              <c:f>(reinforce!$C$12,reinforce!$E$12)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4737,7 +4881,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$12,reinforce!$E$12)</c:f>
+              <c:f>(reinforce!$D$12,reinforce!$F$12)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4789,7 +4933,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$13,reinforce!$D$13)</c:f>
+              <c:f>(reinforce!$C$13,reinforce!$E$13)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4798,7 +4942,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$13,reinforce!$E$13)</c:f>
+              <c:f>(reinforce!$D$13,reinforce!$F$13)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4850,7 +4994,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$14,reinforce!$D$14)</c:f>
+              <c:f>(reinforce!$C$14,reinforce!$E$14)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4859,7 +5003,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$14,reinforce!$E$14)</c:f>
+              <c:f>(reinforce!$D$14,reinforce!$F$14)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4914,7 +5058,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$15,reinforce!$D$15)</c:f>
+              <c:f>(reinforce!$C$15,reinforce!$E$15)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4923,7 +5067,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$15,reinforce!$E$15)</c:f>
+              <c:f>(reinforce!$D$15,reinforce!$F$15)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4978,7 +5122,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$16,reinforce!$D$16)</c:f>
+              <c:f>(reinforce!$C$16,reinforce!$E$16)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4987,7 +5131,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$16,reinforce!$E$16)</c:f>
+              <c:f>(reinforce!$D$16,reinforce!$F$16)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -5042,7 +5186,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$17,reinforce!$D$17)</c:f>
+              <c:f>(reinforce!$C$17,reinforce!$E$17)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -5051,7 +5195,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$17,reinforce!$E$17)</c:f>
+              <c:f>(reinforce!$D$17,reinforce!$F$17)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -5106,7 +5250,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$18,reinforce!$D$18)</c:f>
+              <c:f>(reinforce!$C$18,reinforce!$E$18)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -5115,7 +5259,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$18,reinforce!$E$18)</c:f>
+              <c:f>(reinforce!$D$18,reinforce!$F$18)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -5170,7 +5314,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$19,reinforce!$D$19)</c:f>
+              <c:f>(reinforce!$C$19,reinforce!$E$19)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -5179,7 +5323,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$19,reinforce!$E$19)</c:f>
+              <c:f>(reinforce!$D$19,reinforce!$F$19)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -5231,7 +5375,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$20,reinforce!$D$20)</c:f>
+              <c:f>(reinforce!$C$20,reinforce!$E$20)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -5240,7 +5384,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$20,reinforce!$E$20)</c:f>
+              <c:f>(reinforce!$D$20,reinforce!$F$20)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -5292,7 +5436,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$21,reinforce!$D$21)</c:f>
+              <c:f>(reinforce!$C$21,reinforce!$E$21)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -5301,7 +5445,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$21,reinforce!$E$21)</c:f>
+              <c:f>(reinforce!$D$21,reinforce!$F$21)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -5353,7 +5497,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>(reinforce!$B$22,reinforce!$D$22)</c:f>
+              <c:f>(reinforce!$C$22,reinforce!$E$22)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -5362,7 +5506,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>(reinforce!$C$22,reinforce!$E$22)</c:f>
+              <c:f>(reinforce!$D$22,reinforce!$F$22)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -9288,16 +9432,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>553357</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>99788</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>308429</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>136072</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>780143</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>181429</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>290286</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>90713</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9312,8 +9456,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9180286" y="498931"/>
-          <a:ext cx="4354286" cy="1877784"/>
+          <a:off x="14895286" y="335643"/>
+          <a:ext cx="3610429" cy="3746499"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9349,119 +9493,122 @@
         <a:p>
           <a:r>
             <a:rPr lang="en-US" sz="1100" b="1"/>
-            <a:t>(x1,</a:t>
+            <a:t>(x1, y1), (x2, y2) </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
-            <a:t> y1), (x2, y2) </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t>= endpoints of reinforcement line</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
-            <a:t>Tmax</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> = maximum tensile strength (per unit width) of reinforcement material. </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
-            <a:t>Tres</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> = residual strenth (per unit width) of reinfocement material.</a:t>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t>= start and end of reinforcement line</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:r>
             <a:rPr lang="en-US" sz="1100" b="1"/>
-            <a:t>Lp1</a:t>
+            <a:t>Label</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t> = pullout</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> length or length required to generate full frictional resistance on end corresponding to point 1.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1"/>
-            <a:t>Lp2</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t> = pullout</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> length or length required to generate full frictional resistance on end corresponding to point 2.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
-            <a:t>E</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> = Young's modulus of reinforcement material (force/length^2)</a:t>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = name used in error messages, summaries, and plots</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Type</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = support preset, fills Dir and Appl: Geosynthetic (Tangent, Active), Nail (Axial, Passive), Tieback (Axial, Active), Anchor (Axial, Active)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Dir</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = force direction at the slip surface (LEM only): Tangent = reorients along slip surface (flexible); Axial = along the reinforcement line (rigid). Set by Type; overtype to override.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Appl</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = force application (LEM only): Active = allowable force, not divided by FS (default). Passive = ultimate force, divided by FS. Set by Type; overtype to override.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Tmax</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = tensile capacity (force/length; or force per element if Spacing is given)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Lp1, Lp2 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t>= pullout length at end 1 / end 2 (0 = fully anchored)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Tend1, Tend2 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t>= anchorage/plate/connection capacity at end 1 / end 2 (0 = friction only)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Spacing</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = out-of-plane spacing for discrete supports (nails, tiebacks); blank or 1 for geosynthetics</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Tres</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = residual capacity after rupture (FEM only)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>E</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = modulus of elasticity of reinforcement (FEM only)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
             <a:t>Area</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> = cross-sectional area (per unit width) of reinforcement material.</a:t>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = cross-sectional area of reinforcement (FEM only)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -9474,16 +9621,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>290285</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>18144</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>344713</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>181429</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>680357</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>9071</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>607785</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>108855</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9498,8 +9645,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13099142" y="217715"/>
-          <a:ext cx="3156858" cy="1986642"/>
+          <a:off x="14260284" y="181429"/>
+          <a:ext cx="3156858" cy="2521855"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9586,6 +9733,32 @@
         </a:p>
         <a:p>
           <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>appl</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = force application (LEM only): Active = allowable force, not divided by FS (default). Passive = ultimate force, divided by FS.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
             <a:rPr lang="en-US" sz="1100" b="1"/>
             <a:t>D</a:t>
           </a:r>
@@ -9660,6 +9833,71 @@
         </a:p>
         <a:p>
           <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Vcap</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = Shear</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> capacity of pile (force)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Mcap</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = Moment capacity of pile (force x length)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
             <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
             <a:t>E</a:t>
           </a:r>
@@ -9723,70 +9961,6 @@
         </a:p>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" i="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Vcap</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t> = Shear</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t> capacity of pile (force)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" i="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Mcap</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t> = Moment capacity of pile (force x length)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
             <a:rPr lang="en-US" sz="1100" b="1" i="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
@@ -9808,7 +9982,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t> = Pile head status (fixed for free)</a:t>
+            <a:t> = Pile head status (fixed or free)</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1100"/>
         </a:p>
@@ -10135,7 +10309,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D02E090B-D957-7046-AD33-44E170F709C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71FAED0A-C8CC-8343-BA2E-B8E4255891E7}">
   <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -10148,7 +10322,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="32" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19" x14ac:dyDescent="0.25">
@@ -10161,15 +10335,15 @@
         <v>79</v>
       </c>
       <c r="D5" s="35">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
       <c r="F7" s="15" t="s">
         <v>15</v>
       </c>
@@ -10185,10 +10359,10 @@
         <v>9.81</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G8" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -10196,7 +10370,7 @@
         <v>49</v>
       </c>
       <c r="D9" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>19</v>
@@ -10210,7 +10384,7 @@
         <v>48</v>
       </c>
       <c r="D10" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>17</v>
@@ -10225,7 +10399,7 @@
         <v>75</v>
       </c>
       <c r="D11" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>21</v>
@@ -10260,10 +10434,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="F15" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G15" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -10277,18 +10451,18 @@
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="1"/>
       <c r="F17" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="F18" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
@@ -10309,7 +10483,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A261BE0-CD66-F942-872D-854CE40C6F7F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{028A122E-8CB6-264D-BE4D-4184948E7CD8}">
   <dimension ref="B2:X22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -10328,36 +10502,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="61" t="s">
+        <v>142</v>
+      </c>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="F2" s="61" t="s">
+        <v>143</v>
+      </c>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="J2" s="61" t="s">
+        <v>144</v>
+      </c>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="N2" s="61" t="s">
         <v>145</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="F2" s="58" t="s">
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="R2" s="61" t="s">
         <v>146</v>
       </c>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="J2" s="58" t="s">
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="V2" s="61" t="s">
         <v>147</v>
       </c>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="N2" s="58" t="s">
-        <v>148</v>
-      </c>
-      <c r="O2" s="58"/>
-      <c r="P2" s="58"/>
-      <c r="R2" s="58" t="s">
-        <v>149</v>
-      </c>
-      <c r="S2" s="58"/>
-      <c r="T2" s="58"/>
-      <c r="V2" s="58" t="s">
-        <v>150</v>
-      </c>
-      <c r="W2" s="58"/>
-      <c r="X2" s="58"/>
+      <c r="W2" s="61"/>
+      <c r="X2" s="61"/>
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -10809,51 +10983,84 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37C4F752-BCE4-AE4E-BC09-D828329F219B}">
-  <dimension ref="A2:N25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C37CF166-6531-CC44-B460-D72E6A0F66E6}">
+  <dimension ref="A2:AB25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="1" customWidth="1"/>
-    <col min="2" max="11" width="10.83203125" style="1"/>
-    <col min="12" max="12" width="7.6640625" customWidth="1"/>
+    <col min="2" max="6" width="10.83203125" style="1"/>
+    <col min="7" max="7" width="13.1640625" customWidth="1"/>
+    <col min="10" max="12" width="10.83203125" style="1"/>
+    <col min="16" max="18" width="10.83203125" style="1"/>
+    <col min="19" max="19" width="4.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="G2" s="45" t="s">
+        <v>208</v>
+      </c>
+      <c r="H2" s="45" t="s">
+        <v>209</v>
+      </c>
+      <c r="I2" s="45" t="s">
+        <v>193</v>
+      </c>
+      <c r="J2" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="K2" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="L2" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="M2" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="N2" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="O2" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="P2" s="33" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q2" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="R2" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="F2" s="32" t="s">
-        <v>108</v>
-      </c>
-      <c r="G2" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="H2" s="32" t="s">
-        <v>111</v>
-      </c>
-      <c r="I2" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="J2" s="33" t="s">
-        <v>101</v>
-      </c>
-      <c r="K2" s="33" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="Z2" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>197</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -10863,12 +11070,34 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="3" t="str">
+        <f t="shared" ref="H3:H22" si="0">IF($G3="","",IFERROR(VLOOKUP($G3,$Z$8:$AB$11,2,0),""))</f>
+        <v/>
+      </c>
+      <c r="I3" s="3" t="str">
+        <f t="shared" ref="I3:I22" si="1">IF($G3="","",IFERROR(VLOOKUP($G3,$Z$8:$AB$11,3,0),""))</f>
+        <v/>
+      </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="Z3" t="s">
+        <v>199</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>200</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -10878,12 +11107,28 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I4" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="Z4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -10893,12 +11138,28 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="H5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I5" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="Z5" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -10908,12 +11169,25 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="H6" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I6" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -10923,12 +11197,25 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="H7" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I7" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -10938,12 +11225,34 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+      <c r="H8" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I8" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="Z8" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>197</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -10953,12 +11262,34 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="H9" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I9" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="Z9" t="s">
+        <v>199</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>200</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -10968,12 +11299,34 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+      <c r="H10" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I10" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="Z10" t="s">
+        <v>202</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>200</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -10983,12 +11336,34 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="H11" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I11" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="Z11" t="s">
+        <v>203</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>200</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -10998,12 +11373,25 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="H12" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I12" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -11013,12 +11401,25 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="H13" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I13" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -11028,16 +11429,25 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+      <c r="H14" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I14" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="M14" s="31"/>
-      <c r="N14" s="9" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -11047,16 +11457,25 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+      <c r="H15" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I15" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="9" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -11066,12 +11485,25 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
+      <c r="H16" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I16" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -11081,12 +11513,25 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
+      <c r="H17" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I17" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -11096,12 +11541,25 @@
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+      <c r="H18" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I18" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -11111,12 +11569,25 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+      <c r="H19" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I19" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -11126,12 +11597,25 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+      <c r="H20" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I20" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -11141,12 +11625,25 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
+      <c r="H21" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I21" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -11156,90 +11653,136 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+      <c r="H22" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I22" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="T23" s="47"/>
+      <c r="U23" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="T24" s="31"/>
+      <c r="U24" s="9" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="T25" s="34"/>
+      <c r="U25" s="9" t="s">
+        <v>176</v>
+      </c>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G22" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+      <formula1>$Z$2:$Z$5</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H22" xr:uid="{00000000-0002-0000-0A00-000001000000}">
+      <formula1>$AA$2:$AA$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I22" xr:uid="{00000000-0002-0000-0A00-000002000000}">
+      <formula1>$AB$2:$AB$3</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C542BD7-5686-4248-AC02-D49DB39A8FC0}">
-  <dimension ref="A2:Z15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3B6221D-E989-B546-ACAF-CEB4607C51A1}">
+  <dimension ref="A2:AA18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" style="1" customWidth="1"/>
-    <col min="3" max="16" width="10.83203125" style="1"/>
-    <col min="17" max="17" width="3.83203125" customWidth="1"/>
+    <col min="3" max="8" width="10.83203125" style="1"/>
+    <col min="9" max="9" width="14.5" customWidth="1"/>
+    <col min="10" max="17" width="10.83203125" style="1"/>
+    <col min="18" max="18" width="5.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C2" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="45" t="s">
+        <v>165</v>
+      </c>
+      <c r="H2" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="I2" s="45" t="s">
+        <v>193</v>
+      </c>
+      <c r="J2" s="32" t="s">
+        <v>166</v>
+      </c>
+      <c r="K2" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="L2" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="M2" s="46" t="s">
+        <v>171</v>
+      </c>
+      <c r="N2" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="O2" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="P2" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="G2" s="45" t="s">
-        <v>168</v>
-      </c>
-      <c r="H2" s="45" t="s">
-        <v>176</v>
-      </c>
-      <c r="I2" s="32" t="s">
-        <v>169</v>
-      </c>
-      <c r="J2" s="32" t="s">
-        <v>170</v>
-      </c>
-      <c r="K2" s="33" t="s">
-        <v>101</v>
-      </c>
-      <c r="L2" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="M2" s="33" t="s">
-        <v>107</v>
-      </c>
-      <c r="N2" s="46" t="s">
-        <v>173</v>
-      </c>
-      <c r="O2" s="46" t="s">
-        <v>174</v>
-      </c>
-      <c r="P2" s="33" t="s">
-        <v>180</v>
+      <c r="Q2" s="33" t="s">
+        <v>177</v>
       </c>
       <c r="Z2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -11258,11 +11801,15 @@
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
       <c r="Z3" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -11281,8 +11828,9 @@
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q4" s="3"/>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -11301,8 +11849,9 @@
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q5" s="3"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -11321,8 +11870,9 @@
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q6" s="3"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -11341,8 +11891,9 @@
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q7" s="3"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -11361,8 +11912,9 @@
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -11381,1130 +11933,11 @@
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A12" s="3">
-        <v>10</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="R13" s="47"/>
-      <c r="S13" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="R14" s="31"/>
-      <c r="S14" s="9" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="9" t="s">
-        <v>179</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:P12" xr:uid="{BD18340F-2DC3-724E-BE00-EA96ECBB898C}">
-      <formula1>$Z$2:$Z$3</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{847CAF5A-5624-4041-9578-842C28E166A5}">
-  <dimension ref="B2:R24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="7" max="7" width="4" customWidth="1"/>
-    <col min="10" max="10" width="4.33203125" customWidth="1"/>
-    <col min="13" max="13" width="3" customWidth="1"/>
-    <col min="16" max="16" width="4" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B2" s="59" t="s">
-        <v>138</v>
-      </c>
-      <c r="C2" s="59"/>
-      <c r="E2" s="55" t="s">
-        <v>133</v>
-      </c>
-      <c r="F2" s="55"/>
-      <c r="H2" s="55" t="s">
-        <v>134</v>
-      </c>
-      <c r="I2" s="55"/>
-      <c r="K2" s="55" t="s">
-        <v>135</v>
-      </c>
-      <c r="L2" s="55"/>
-      <c r="N2" s="55" t="s">
-        <v>136</v>
-      </c>
-      <c r="O2" s="55"/>
-      <c r="Q2" s="55" t="s">
-        <v>137</v>
-      </c>
-      <c r="R2" s="55"/>
-    </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="E3" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="F3" s="38"/>
-      <c r="H3" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="I3" s="38"/>
-      <c r="K3" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="L3" s="38"/>
-      <c r="N3" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="O3" s="38"/>
-      <c r="Q3" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="R3" s="38"/>
-    </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B4" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="K4" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="L4" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="N4" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="O4" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q4" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="R4" s="28" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-    </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-    </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-    </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
-      <c r="Q22" s="3"/>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
-      <c r="Q23" s="3"/>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="3"/>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B2:C3"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1356292-DB08-1D46-A803-E893EDEE17F7}">
-  <dimension ref="B2:R24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="7" max="7" width="4" customWidth="1"/>
-    <col min="10" max="10" width="4.33203125" customWidth="1"/>
-    <col min="13" max="13" width="3" customWidth="1"/>
-    <col min="16" max="16" width="4" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B2" s="60" t="s">
-        <v>140</v>
-      </c>
-      <c r="C2" s="60"/>
-      <c r="E2" s="56" t="s">
-        <v>139</v>
-      </c>
-      <c r="F2" s="56"/>
-      <c r="H2" s="56" t="s">
-        <v>141</v>
-      </c>
-      <c r="I2" s="56"/>
-      <c r="K2" s="56" t="s">
-        <v>142</v>
-      </c>
-      <c r="L2" s="56"/>
-      <c r="N2" s="56" t="s">
-        <v>143</v>
-      </c>
-      <c r="O2" s="56"/>
-      <c r="Q2" s="56" t="s">
-        <v>144</v>
-      </c>
-      <c r="R2" s="56"/>
-    </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B3" s="60"/>
-      <c r="C3" s="60"/>
-      <c r="E3" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="F3" s="40"/>
-      <c r="H3" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="I3" s="40"/>
-      <c r="K3" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="L3" s="40"/>
-      <c r="N3" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="O3" s="40"/>
-      <c r="Q3" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="R3" s="40"/>
-    </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B4" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="K4" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="L4" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="N4" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="O4" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q4" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="R4" s="28" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-    </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-    </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-    </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
-      <c r="Q22" s="3"/>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
-      <c r="Q23" s="3"/>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="3"/>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="B2:C3"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="N2:O2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56CEDAD3-D805-AE4D-9F0D-9E80BF51FF21}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA88A0E-2BF5-FE49-9603-08BE4D91829B}">
-  <dimension ref="A2:X50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="7" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.33203125" style="1" customWidth="1"/>
-    <col min="3" max="9" width="8.5" style="1" customWidth="1"/>
-    <col min="10" max="13" width="8.5" customWidth="1"/>
-    <col min="14" max="17" width="10.83203125" customWidth="1"/>
-    <col min="23" max="23" width="10.83203125" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="C2" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
-      <c r="J2" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="O2" s="6"/>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="C3" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3"/>
-      <c r="F3"/>
-      <c r="J3" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="K3" t="s">
-        <v>59</v>
-      </c>
-      <c r="O3" s="14"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="C4" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E4"/>
-      <c r="F4"/>
-      <c r="J4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" t="s">
-        <v>60</v>
-      </c>
-      <c r="O4" s="14"/>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="J5" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="O5" s="14"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="C7" s="49" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="49" t="s">
-        <v>58</v>
-      </c>
-      <c r="M7" s="49"/>
-      <c r="N7" s="49"/>
-      <c r="O7" s="49"/>
-      <c r="P7" s="49"/>
-      <c r="Q7" s="49"/>
-      <c r="R7" s="49" t="s">
-        <v>93</v>
-      </c>
-      <c r="S7" s="49"/>
-      <c r="T7" s="49"/>
-      <c r="U7" s="49"/>
-      <c r="V7" s="49"/>
-      <c r="W7" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="X7" s="49"/>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A8" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="H8" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="I8" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="J8" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="K8" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="L8" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="M8" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="N8" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="O8" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="P8" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q8" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="R8" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="S8" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="T8" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="U8" s="25" t="s">
-        <v>97</v>
-      </c>
-      <c r="V8" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="W8" s="29" t="s">
-        <v>101</v>
-      </c>
-      <c r="X8" s="30" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
-        <v>1</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C9" s="3">
-        <v>20</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E9" s="3">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="L9" s="3">
-        <f>C9*0.06</f>
-        <v>1.2</v>
-      </c>
-      <c r="M9" s="3">
-        <f>E9*0.6</f>
-        <v>1.7999999999999998</v>
-      </c>
-      <c r="N9" s="3">
-        <f>F9*0.14</f>
-        <v>2.7440000000000007</v>
-      </c>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
-        <v>2</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -12522,17 +11955,1467 @@
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="S16" s="47"/>
+      <c r="T16" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="17" spans="19:20" x14ac:dyDescent="0.2">
+      <c r="S17" s="31"/>
+      <c r="T17" s="9" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="18" spans="19:20" x14ac:dyDescent="0.2">
+      <c r="S18" s="34"/>
+      <c r="T18" s="9" t="s">
+        <v>176</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q3:Q12" xr:uid="{BD18340F-2DC3-724E-BE00-EA96ECBB898C}">
+      <formula1>$Z$2:$Z$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I12" xr:uid="{00000000-0002-0000-0B00-000001000000}">
+      <formula1>$AA$2:$AA$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FA07123-52EA-314A-81EF-989A42CB4DFE}">
+  <dimension ref="A2:F22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="4.83203125" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" customWidth="1"/>
+    <col min="3" max="6" width="10.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="3">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="3">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="3">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="3">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="3">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="3">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="3">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="3">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="3">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="3">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="3">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="3">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D036245-91C1-5842-93DD-735018175DE8}">
+  <dimension ref="B2:R24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="7" max="7" width="4" customWidth="1"/>
+    <col min="10" max="10" width="4.33203125" customWidth="1"/>
+    <col min="13" max="13" width="3" customWidth="1"/>
+    <col min="16" max="16" width="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B2" s="62" t="s">
+        <v>135</v>
+      </c>
+      <c r="C2" s="62"/>
+      <c r="E2" s="58" t="s">
+        <v>130</v>
+      </c>
+      <c r="F2" s="58"/>
+      <c r="H2" s="58" t="s">
+        <v>131</v>
+      </c>
+      <c r="I2" s="58"/>
+      <c r="K2" s="58" t="s">
+        <v>132</v>
+      </c>
+      <c r="L2" s="58"/>
+      <c r="N2" s="58" t="s">
+        <v>133</v>
+      </c>
+      <c r="O2" s="58"/>
+      <c r="Q2" s="58" t="s">
+        <v>134</v>
+      </c>
+      <c r="R2" s="58"/>
+    </row>
+    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="E3" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" s="38"/>
+      <c r="H3" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="I3" s="38"/>
+      <c r="K3" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="L3" s="38"/>
+      <c r="N3" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="O3" s="38"/>
+      <c r="Q3" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="R3" s="38"/>
+    </row>
+    <row r="4" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B4" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="K4" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="L4" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="N4" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="O4" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q4" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="R4" s="28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+    </row>
+    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B2:C3"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4C3C734-6227-7445-884D-1F1A5F3909C7}">
+  <dimension ref="B2:R24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="7" max="7" width="4" customWidth="1"/>
+    <col min="10" max="10" width="4.33203125" customWidth="1"/>
+    <col min="13" max="13" width="3" customWidth="1"/>
+    <col min="16" max="16" width="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B2" s="63" t="s">
+        <v>137</v>
+      </c>
+      <c r="C2" s="63"/>
+      <c r="E2" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="F2" s="59"/>
+      <c r="H2" s="59" t="s">
+        <v>138</v>
+      </c>
+      <c r="I2" s="59"/>
+      <c r="K2" s="59" t="s">
+        <v>139</v>
+      </c>
+      <c r="L2" s="59"/>
+      <c r="N2" s="59" t="s">
+        <v>140</v>
+      </c>
+      <c r="O2" s="59"/>
+      <c r="Q2" s="59" t="s">
+        <v>141</v>
+      </c>
+      <c r="R2" s="59"/>
+    </row>
+    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="E3" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" s="40"/>
+      <c r="H3" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="I3" s="40"/>
+      <c r="K3" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="L3" s="40"/>
+      <c r="N3" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="O3" s="40"/>
+      <c r="Q3" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="R3" s="40"/>
+    </row>
+    <row r="4" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B4" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="K4" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="L4" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="N4" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="O4" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q4" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="R4" s="28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+    </row>
+    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="B2:C3"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="N2:O2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDB4949D-EAAF-AE4C-9BAF-D5BF753E34CD}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60A900FC-A692-B445-95C9-59E70352B291}">
+  <dimension ref="A2:AG51"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="7" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" style="1" customWidth="1"/>
+    <col min="3" max="10" width="8.5" style="1" customWidth="1"/>
+    <col min="11" max="31" width="8.5" customWidth="1"/>
+    <col min="32" max="32" width="8.5" style="1" customWidth="1"/>
+    <col min="33" max="33" width="8.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="C2" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="K2" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="U2" s="6"/>
+      <c r="AA2" s="6" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="C3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="K3" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="L3" t="s">
+        <v>59</v>
+      </c>
+      <c r="U3" s="14"/>
+      <c r="AA3" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="C4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4"/>
+      <c r="G4"/>
+      <c r="K4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" t="s">
+        <v>60</v>
+      </c>
+      <c r="U4" s="14"/>
+      <c r="AA4" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="C5" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D5" t="s">
+        <v>207</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="U5" s="14"/>
+      <c r="AA5" s="1"/>
+      <c r="AB5" s="9"/>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="K6" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="L6" t="s">
+        <v>206</v>
+      </c>
+      <c r="P6" s="1"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="C8" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="51"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="50"/>
+      <c r="I8" s="50"/>
+      <c r="J8" s="50"/>
+      <c r="K8" s="50"/>
+      <c r="L8" s="52"/>
+      <c r="M8" s="52"/>
+      <c r="N8" s="52"/>
+      <c r="O8" s="52"/>
+      <c r="P8" s="1"/>
+      <c r="R8" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="S8" s="50"/>
+      <c r="T8" s="50"/>
+      <c r="U8" s="50"/>
+      <c r="V8" s="50"/>
+      <c r="W8" s="50"/>
+      <c r="X8" s="50" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y8" s="50"/>
+      <c r="Z8" s="50"/>
+      <c r="AA8" s="50"/>
+      <c r="AB8" s="50"/>
+      <c r="AC8" s="50"/>
+      <c r="AD8" s="50"/>
+      <c r="AE8" s="50"/>
+      <c r="AF8" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG8" s="50"/>
+    </row>
+    <row r="9" spans="1:33" ht="18" x14ac:dyDescent="0.25">
+      <c r="A9" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="48" t="s">
+        <v>205</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="J9" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="K9" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="L9" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="M9" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="N9" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="O9" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="P9" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q9" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="R9" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="S9" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="T9" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="U9" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="V9" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="W9" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="X9" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y9" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z9" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA9" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="AB9" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="AC9" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD9" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="AE9" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="AF9" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AG9" s="30" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
+        <v>1</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Soil</t>
+        </is>
+      </c>
+      <c r="C10" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>mc</t>
+        </is>
+      </c>
+      <c r="F10" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>19.6</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="R10" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="S10" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="T10" s="3">
+        <v>2.744</v>
+      </c>
+      <c r="U10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="V10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="W10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>lf</t>
+        </is>
+      </c>
+      <c r="AB10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AC10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AD10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AE10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AF10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AG10" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -12557,10 +13440,19 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+      <c r="AD11" s="18"/>
+      <c r="AE11" s="19"/>
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -12585,10 +13477,19 @@
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3"/>
+      <c r="Z12" s="3"/>
+      <c r="AA12" s="3"/>
+      <c r="AB12" s="3"/>
+      <c r="AC12" s="3"/>
+      <c r="AD12" s="18"/>
+      <c r="AE12" s="19"/>
+      <c r="AF12" s="3"/>
+      <c r="AG12" s="3"/>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -12613,10 +13514,19 @@
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3"/>
+      <c r="Z13" s="3"/>
+      <c r="AA13" s="3"/>
+      <c r="AB13" s="3"/>
+      <c r="AC13" s="3"/>
+      <c r="AD13" s="3"/>
+      <c r="AE13" s="3"/>
+      <c r="AF13" s="3"/>
+      <c r="AG13" s="3"/>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -12641,10 +13551,19 @@
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3"/>
+      <c r="Z14" s="3"/>
+      <c r="AA14" s="3"/>
+      <c r="AB14" s="3"/>
+      <c r="AC14" s="3"/>
+      <c r="AD14" s="3"/>
+      <c r="AE14" s="3"/>
+      <c r="AF14" s="3"/>
+      <c r="AG14" s="3"/>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -12669,10 +13588,19 @@
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3"/>
+      <c r="Z15" s="3"/>
+      <c r="AA15" s="3"/>
+      <c r="AB15" s="3"/>
+      <c r="AC15" s="3"/>
+      <c r="AD15" s="3"/>
+      <c r="AE15" s="3"/>
+      <c r="AF15" s="3"/>
+      <c r="AG15" s="3"/>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -12697,10 +13625,19 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -12725,10 +13662,19 @@
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
       <c r="X17" s="3"/>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3"/>
+      <c r="Z17" s="3"/>
+      <c r="AA17" s="3"/>
+      <c r="AB17" s="3"/>
+      <c r="AC17" s="3"/>
+      <c r="AD17" s="3"/>
+      <c r="AE17" s="3"/>
+      <c r="AF17" s="3"/>
+      <c r="AG17" s="3"/>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -12753,10 +13699,19 @@
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3"/>
+      <c r="Z18" s="3"/>
+      <c r="AA18" s="3"/>
+      <c r="AB18" s="3"/>
+      <c r="AC18" s="3"/>
+      <c r="AD18" s="3"/>
+      <c r="AE18" s="3"/>
+      <c r="AF18" s="3"/>
+      <c r="AG18" s="3"/>
+    </row>
+    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -12781,10 +13736,19 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -12809,10 +13773,19 @@
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
       <c r="X20" s="3"/>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3"/>
+      <c r="Z20" s="3"/>
+      <c r="AA20" s="3"/>
+      <c r="AB20" s="3"/>
+      <c r="AC20" s="3"/>
+      <c r="AD20" s="3"/>
+      <c r="AE20" s="3"/>
+      <c r="AF20" s="3"/>
+      <c r="AG20" s="3"/>
+    </row>
+    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -12837,10 +13810,19 @@
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
       <c r="X21" s="3"/>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3"/>
+      <c r="Z21" s="3"/>
+      <c r="AA21" s="3"/>
+      <c r="AB21" s="3"/>
+      <c r="AC21" s="3"/>
+      <c r="AD21" s="3"/>
+      <c r="AE21" s="3"/>
+      <c r="AF21" s="3"/>
+      <c r="AG21" s="3"/>
+    </row>
+    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -12865,10 +13847,19 @@
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3"/>
+      <c r="AC22" s="3"/>
+      <c r="AD22" s="3"/>
+      <c r="AE22" s="3"/>
+      <c r="AF22" s="3"/>
+      <c r="AG22" s="3"/>
+    </row>
+    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -12893,24 +13884,54 @@
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
-      <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
-      <c r="U24" s="1"/>
-      <c r="V24" s="1"/>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="J25" s="1"/>
+      <c r="Y23" s="3"/>
+      <c r="Z23" s="3"/>
+      <c r="AA23" s="3"/>
+      <c r="AB23" s="3"/>
+      <c r="AC23" s="3"/>
+      <c r="AD23" s="3"/>
+      <c r="AE23" s="3"/>
+      <c r="AF23" s="3"/>
+      <c r="AG23" s="3"/>
+    </row>
+    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A24" s="3">
+        <v>15</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3"/>
+      <c r="Y24" s="3"/>
+      <c r="Z24" s="3"/>
+      <c r="AA24" s="3"/>
+      <c r="AB24" s="3"/>
+      <c r="AC24" s="3"/>
+      <c r="AD24" s="3"/>
+      <c r="AE24" s="3"/>
+      <c r="AF24" s="3"/>
+      <c r="AG24" s="3"/>
+    </row>
+    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -12918,9 +13939,22 @@
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="J26" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1"/>
+      <c r="W25" s="1"/>
+      <c r="X25" s="1"/>
+      <c r="Y25" s="1"/>
+      <c r="Z25" s="1"/>
+      <c r="AA25" s="1"/>
+      <c r="AB25" s="1"/>
+      <c r="AC25" s="1"/>
+      <c r="AD25" s="1"/>
+      <c r="AE25" s="1"/>
+    </row>
+    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -12928,9 +13962,14 @@
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="J27" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1"/>
+      <c r="W26" s="1"/>
+    </row>
+    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -12938,9 +13977,14 @@
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="J28" s="1"/>
+      <c r="R27" s="1"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="1"/>
+      <c r="U27" s="1"/>
+      <c r="V27" s="1"/>
+      <c r="W27" s="1"/>
+    </row>
+    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -12948,9 +13992,14 @@
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="J29" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="1"/>
+      <c r="W28" s="1"/>
+    </row>
+    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -12958,9 +14007,14 @@
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="J30" s="1"/>
+      <c r="R29" s="1"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="1"/>
+      <c r="U29" s="1"/>
+      <c r="V29" s="1"/>
+      <c r="W29" s="1"/>
+    </row>
+    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -12968,9 +14022,14 @@
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="J31" s="1"/>
+      <c r="R30" s="1"/>
+      <c r="S30" s="1"/>
+      <c r="T30" s="1"/>
+      <c r="U30" s="1"/>
+      <c r="V30" s="1"/>
+      <c r="W30" s="1"/>
+    </row>
+    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -12978,9 +14037,14 @@
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="J32" s="1"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1"/>
+      <c r="V31" s="1"/>
+      <c r="W31" s="1"/>
+    </row>
+    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -12988,9 +14052,14 @@
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
-    </row>
-    <row r="33" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J33" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1"/>
+      <c r="W32" s="1"/>
+    </row>
+    <row r="33" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -12998,9 +14067,14 @@
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
-    </row>
-    <row r="34" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J34" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+      <c r="V33" s="1"/>
+      <c r="W33" s="1"/>
+    </row>
+    <row r="34" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -13008,9 +14082,14 @@
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
-    </row>
-    <row r="35" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J35" s="1"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
+      <c r="V34" s="1"/>
+      <c r="W34" s="1"/>
+    </row>
+    <row r="35" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -13018,9 +14097,14 @@
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
-    </row>
-    <row r="36" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J36" s="1"/>
+      <c r="R35" s="1"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="1"/>
+      <c r="U35" s="1"/>
+      <c r="V35" s="1"/>
+      <c r="W35" s="1"/>
+    </row>
+    <row r="36" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
@@ -13028,9 +14112,14 @@
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
-    </row>
-    <row r="37" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J37" s="1"/>
+      <c r="R36" s="1"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="1"/>
+      <c r="U36" s="1"/>
+      <c r="V36" s="1"/>
+      <c r="W36" s="1"/>
+    </row>
+    <row r="37" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
@@ -13038,9 +14127,14 @@
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
-    </row>
-    <row r="38" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J38" s="1"/>
+      <c r="R37" s="1"/>
+      <c r="S37" s="1"/>
+      <c r="T37" s="1"/>
+      <c r="U37" s="1"/>
+      <c r="V37" s="1"/>
+      <c r="W37" s="1"/>
+    </row>
+    <row r="38" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -13048,9 +14142,14 @@
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
-    </row>
-    <row r="39" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J39" s="1"/>
+      <c r="R38" s="1"/>
+      <c r="S38" s="1"/>
+      <c r="T38" s="1"/>
+      <c r="U38" s="1"/>
+      <c r="V38" s="1"/>
+      <c r="W38" s="1"/>
+    </row>
+    <row r="39" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -13058,9 +14157,14 @@
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
-    </row>
-    <row r="40" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J40" s="1"/>
+      <c r="R39" s="1"/>
+      <c r="S39" s="1"/>
+      <c r="T39" s="1"/>
+      <c r="U39" s="1"/>
+      <c r="V39" s="1"/>
+      <c r="W39" s="1"/>
+    </row>
+    <row r="40" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -13068,9 +14172,14 @@
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
-    </row>
-    <row r="41" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J41" s="1"/>
+      <c r="R40" s="1"/>
+      <c r="S40" s="1"/>
+      <c r="T40" s="1"/>
+      <c r="U40" s="1"/>
+      <c r="V40" s="1"/>
+      <c r="W40" s="1"/>
+    </row>
+    <row r="41" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
@@ -13078,9 +14187,14 @@
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
-    </row>
-    <row r="42" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J42" s="1"/>
+      <c r="R41" s="1"/>
+      <c r="S41" s="1"/>
+      <c r="T41" s="1"/>
+      <c r="U41" s="1"/>
+      <c r="V41" s="1"/>
+      <c r="W41" s="1"/>
+    </row>
+    <row r="42" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
@@ -13088,9 +14202,14 @@
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
       <c r="Q42" s="1"/>
-    </row>
-    <row r="43" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J43" s="1"/>
+      <c r="R42" s="1"/>
+      <c r="S42" s="1"/>
+      <c r="T42" s="1"/>
+      <c r="U42" s="1"/>
+      <c r="V42" s="1"/>
+      <c r="W42" s="1"/>
+    </row>
+    <row r="43" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -13098,9 +14217,14 @@
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
       <c r="Q43" s="1"/>
-    </row>
-    <row r="44" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J44" s="1"/>
+      <c r="R43" s="1"/>
+      <c r="S43" s="1"/>
+      <c r="T43" s="1"/>
+      <c r="U43" s="1"/>
+      <c r="V43" s="1"/>
+      <c r="W43" s="1"/>
+    </row>
+    <row r="44" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
@@ -13108,9 +14232,14 @@
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
-    </row>
-    <row r="45" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J45" s="1"/>
+      <c r="R44" s="1"/>
+      <c r="S44" s="1"/>
+      <c r="T44" s="1"/>
+      <c r="U44" s="1"/>
+      <c r="V44" s="1"/>
+      <c r="W44" s="1"/>
+    </row>
+    <row r="45" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
@@ -13118,9 +14247,14 @@
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
       <c r="Q45" s="1"/>
-    </row>
-    <row r="46" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J46" s="1"/>
+      <c r="R45" s="1"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="1"/>
+      <c r="U45" s="1"/>
+      <c r="V45" s="1"/>
+      <c r="W45" s="1"/>
+    </row>
+    <row r="46" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
@@ -13128,9 +14262,14 @@
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
       <c r="Q46" s="1"/>
-    </row>
-    <row r="47" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J47" s="1"/>
+      <c r="R46" s="1"/>
+      <c r="S46" s="1"/>
+      <c r="T46" s="1"/>
+      <c r="U46" s="1"/>
+      <c r="V46" s="1"/>
+      <c r="W46" s="1"/>
+    </row>
+    <row r="47" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
@@ -13138,9 +14277,14 @@
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
-    </row>
-    <row r="48" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J48" s="1"/>
+      <c r="R47" s="1"/>
+      <c r="S47" s="1"/>
+      <c r="T47" s="1"/>
+      <c r="U47" s="1"/>
+      <c r="V47" s="1"/>
+      <c r="W47" s="1"/>
+    </row>
+    <row r="48" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
@@ -13148,9 +14292,14 @@
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
-    </row>
-    <row r="49" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J49" s="1"/>
+      <c r="R48" s="1"/>
+      <c r="S48" s="1"/>
+      <c r="T48" s="1"/>
+      <c r="U48" s="1"/>
+      <c r="V48" s="1"/>
+      <c r="W48" s="1"/>
+    </row>
+    <row r="49" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
@@ -13158,9 +14307,14 @@
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>
       <c r="Q49" s="1"/>
-    </row>
-    <row r="50" spans="10:17" x14ac:dyDescent="0.2">
-      <c r="J50" s="1"/>
+      <c r="R49" s="1"/>
+      <c r="S49" s="1"/>
+      <c r="T49" s="1"/>
+      <c r="U49" s="1"/>
+      <c r="V49" s="1"/>
+      <c r="W49" s="1"/>
+    </row>
+    <row r="50" spans="11:23" x14ac:dyDescent="0.2">
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
@@ -13168,50 +14322,104 @@
       <c r="O50" s="1"/>
       <c r="P50" s="1"/>
       <c r="Q50" s="1"/>
+      <c r="R50" s="1"/>
+      <c r="S50" s="1"/>
+      <c r="T50" s="1"/>
+      <c r="U50" s="1"/>
+      <c r="V50" s="1"/>
+      <c r="W50" s="1"/>
+    </row>
+    <row r="51" spans="11:23" x14ac:dyDescent="0.2">
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="1"/>
+      <c r="R51" s="1"/>
+      <c r="S51" s="1"/>
+      <c r="T51" s="1"/>
+      <c r="U51" s="1"/>
+      <c r="V51" s="1"/>
+      <c r="W51" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="C7:J7"/>
-    <mergeCell ref="L7:Q7"/>
-    <mergeCell ref="W7:X7"/>
-    <mergeCell ref="R7:V7"/>
+    <mergeCell ref="C8:O8"/>
+    <mergeCell ref="R8:W8"/>
+    <mergeCell ref="AF8:AG8"/>
+    <mergeCell ref="X8:AE8"/>
   </mergeCells>
-  <conditionalFormatting sqref="F9:F50">
-    <cfRule type="expression" dxfId="8" priority="3">
-      <formula>$D9="cp"</formula>
+  <conditionalFormatting sqref="F10:I51">
+    <cfRule type="expression" dxfId="14" priority="16">
+      <formula>$E10="pow"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G9:H50">
-    <cfRule type="expression" dxfId="7" priority="2">
-      <formula>$D9="mc"</formula>
+  <conditionalFormatting sqref="G10:G51">
+    <cfRule type="expression" dxfId="13" priority="5">
+      <formula>$E10="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I9:J50">
-    <cfRule type="expression" dxfId="6" priority="4">
-      <formula>$D9="cp"</formula>
+  <conditionalFormatting sqref="H10:I51">
+    <cfRule type="expression" dxfId="12" priority="4">
+      <formula>$E10="mc"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N9:N50">
-    <cfRule type="expression" dxfId="5" priority="6">
-      <formula>$D9="cp"</formula>
+  <conditionalFormatting sqref="J10:K51">
+    <cfRule type="expression" dxfId="11" priority="6">
+      <formula>$E10="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O9:O50">
-    <cfRule type="expression" dxfId="4" priority="13">
-      <formula>$D9="mc"</formula>
+  <conditionalFormatting sqref="L10:O51">
+    <cfRule type="expression" dxfId="10" priority="19">
+      <formula>AND($E10&lt;&gt;"",$E10&lt;&gt;"pow")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P9:Q50">
-    <cfRule type="expression" dxfId="3" priority="8">
-      <formula>$D9="cp"</formula>
+  <conditionalFormatting sqref="Q10:Q51">
+    <cfRule type="expression" dxfId="9" priority="20">
+      <formula>AND($P10&lt;&gt;"",$P10&lt;&gt;"ru")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D9:D50" xr:uid="{374AFD2C-B540-DD4B-A245-8B781F76E64C}">
-      <formula1>$C$3:$C$4</formula1>
+  <conditionalFormatting sqref="S10:U51">
+    <cfRule type="expression" dxfId="8" priority="21">
+      <formula>$E10="pow"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T10:T51">
+    <cfRule type="expression" dxfId="7" priority="8">
+      <formula>$E10="cp"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U10:U51">
+    <cfRule type="expression" dxfId="6" priority="15">
+      <formula>$E10="mc"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V10:W51">
+    <cfRule type="expression" dxfId="5" priority="10">
+      <formula>$E10="cp"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB10:AC101">
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>$AA10="vg"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD10:AE101">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>$AA10="lf"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10:E51" xr:uid="{374AFD2C-B540-DD4B-A245-8B781F76E64C}">
+      <formula1>$C$3:$C$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K9:K50" xr:uid="{D770415C-1ECE-F44B-9D8C-08EF1CF31C8E}">
-      <formula1>$J$3:$J$5</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P10:P51" xr:uid="{D770415C-1ECE-F44B-9D8C-08EF1CF31C8E}">
+      <formula1>$K$3:$K$6</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA10:AA101" xr:uid="{E00A94A9-D864-5843-8FBD-E84775B1C100}">
+      <formula1>$AA$3:$AA$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13219,7 +14427,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4436F470-A09D-8C49-9B48-FB04FA2826AC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D14E9FA-AFF6-A74D-8120-64FF6A371536}">
   <dimension ref="A2:AR27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -13249,266 +14457,268 @@
         <v>46</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="50" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="50"/>
-      <c r="D4" s="50" t="s">
+      <c r="A4" s="53" t="inlineStr">
+        <is>
+          <t>Profile Line #1</t>
+        </is>
+      </c>
+      <c r="B4" s="53"/>
+      <c r="D4" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="50"/>
-      <c r="G4" s="50" t="s">
+      <c r="E4" s="53"/>
+      <c r="G4" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="50"/>
-      <c r="J4" s="50" t="s">
+      <c r="H4" s="53"/>
+      <c r="J4" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="50"/>
-      <c r="M4" s="50" t="s">
+      <c r="K4" s="53"/>
+      <c r="M4" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="50"/>
-      <c r="P4" s="50" t="s">
+      <c r="N4" s="53"/>
+      <c r="P4" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="50"/>
+      <c r="Q4" s="53"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="50" t="s">
+      <c r="S4" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="T4" s="50"/>
+      <c r="T4" s="53"/>
       <c r="U4" s="1"/>
-      <c r="V4" s="50" t="s">
+      <c r="V4" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="W4" s="50"/>
+      <c r="W4" s="53"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="50" t="s">
+      <c r="Y4" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="Z4" s="50"/>
+      <c r="Z4" s="53"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="50" t="s">
+      <c r="AB4" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="AC4" s="50"/>
-      <c r="AE4" s="50" t="s">
+      <c r="AC4" s="53"/>
+      <c r="AE4" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="AF4" s="53"/>
+      <c r="AG4" s="1"/>
+      <c r="AH4" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="AI4" s="53"/>
+      <c r="AJ4" s="1"/>
+      <c r="AK4" s="53" t="s">
+        <v>113</v>
+      </c>
+      <c r="AL4" s="53"/>
+      <c r="AM4" s="1"/>
+      <c r="AN4" s="53" t="s">
         <v>114</v>
       </c>
-      <c r="AF4" s="50"/>
-      <c r="AG4" s="1"/>
-      <c r="AH4" s="50" t="s">
+      <c r="AO4" s="53"/>
+      <c r="AP4" s="1"/>
+      <c r="AQ4" s="53" t="s">
         <v>115</v>
       </c>
-      <c r="AI4" s="50"/>
-      <c r="AJ4" s="1"/>
-      <c r="AK4" s="50" t="s">
-        <v>116</v>
-      </c>
-      <c r="AL4" s="50"/>
-      <c r="AM4" s="1"/>
-      <c r="AN4" s="50" t="s">
-        <v>117</v>
-      </c>
-      <c r="AO4" s="50"/>
-      <c r="AP4" s="1"/>
-      <c r="AQ4" s="50" t="s">
-        <v>118</v>
-      </c>
-      <c r="AR4" s="50"/>
+      <c r="AR4" s="53"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B5" s="42">
         <v>1</v>
       </c>
       <c r="D5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E5" s="42">
         <v>2</v>
       </c>
       <c r="G5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H5" s="42">
         <v>3</v>
       </c>
       <c r="J5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K5" s="42">
         <v>4</v>
       </c>
       <c r="M5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="N5" s="42">
         <v>5</v>
       </c>
       <c r="P5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="Q5" s="42">
         <v>6</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="T5" s="42">
         <v>7</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="W5" s="42">
         <v>8</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="Z5" s="42">
         <v>9</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AC5" s="42">
         <v>10</v>
       </c>
       <c r="AE5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AF5" s="42">
         <v>11</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AI5" s="42">
         <v>12</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AL5" s="42">
         <v>13</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AO5" s="42">
         <v>14</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AR5" s="42">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A6" s="51" t="str">
+      <c r="A6" s="54" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
-        <v>Soil</v>
-      </c>
-      <c r="B6" s="52"/>
-      <c r="D6" s="51" t="str">
+        <v/>
+      </c>
+      <c r="B6" s="55"/>
+      <c r="D6" s="54" t="str">
         <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="E6" s="52"/>
-      <c r="G6" s="51" t="str">
+      <c r="E6" s="55"/>
+      <c r="G6" s="54" t="str">
         <f>_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="H6" s="52"/>
-      <c r="J6" s="51" t="str">
+      <c r="H6" s="55"/>
+      <c r="J6" s="54" t="str">
         <f>_xlfn.XLOOKUP(K5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="K6" s="52"/>
-      <c r="M6" s="51" t="str">
+      <c r="K6" s="55"/>
+      <c r="M6" s="54" t="str">
         <f>_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="N6" s="52"/>
-      <c r="P6" s="51" t="str">
+      <c r="N6" s="55"/>
+      <c r="P6" s="54" t="str">
         <f>_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Q6" s="52"/>
+      <c r="Q6" s="55"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="51" t="str">
+      <c r="S6" s="54" t="str">
         <f>_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="T6" s="52"/>
+      <c r="T6" s="55"/>
       <c r="U6" s="1"/>
-      <c r="V6" s="51" t="str">
+      <c r="V6" s="54" t="str">
         <f>_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="W6" s="52"/>
+      <c r="W6" s="55"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="51" t="str">
+      <c r="Y6" s="54" t="str">
         <f>_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Z6" s="52"/>
+      <c r="Z6" s="55"/>
       <c r="AA6" s="1"/>
-      <c r="AB6" s="51" t="str">
+      <c r="AB6" s="54" t="str">
         <f>_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AC6" s="52"/>
-      <c r="AE6" s="51" t="str">
+      <c r="AC6" s="55"/>
+      <c r="AE6" s="54" t="str">
         <f>_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AF6" s="52"/>
+      <c r="AF6" s="55"/>
       <c r="AG6" s="1"/>
-      <c r="AH6" s="51" t="str">
+      <c r="AH6" s="54" t="str">
         <f>_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AI6" s="52"/>
+      <c r="AI6" s="55"/>
       <c r="AJ6" s="1"/>
-      <c r="AK6" s="51" t="str">
+      <c r="AK6" s="54" t="str">
         <f>_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AL6" s="52"/>
+      <c r="AL6" s="55"/>
       <c r="AM6" s="1"/>
-      <c r="AN6" s="51" t="str">
+      <c r="AN6" s="54" t="str">
         <f>_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AO6" s="52"/>
+      <c r="AO6" s="55"/>
       <c r="AP6" s="1"/>
-      <c r="AQ6" s="51" t="str">
+      <c r="AQ6" s="54" t="str">
         <f>_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AR6" s="52"/>
+      <c r="AR6" s="55"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -13612,10 +14822,10 @@
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="B8" s="3">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -13656,10 +14866,10 @@
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="B9" s="3">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -13700,10 +14910,10 @@
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
-        <v>50</v>
+        <v>50.0</v>
       </c>
       <c r="B10" s="3">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -13744,10 +14954,10 @@
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
-        <v>90</v>
+        <v>90.0</v>
       </c>
       <c r="B11" s="3">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -14464,7 +15674,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D531F6A4-7395-D742-B12A-DB33E9D92D43}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88992C43-9D03-6445-8931-028E950C2356}">
   <dimension ref="A2:AR27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -14491,263 +15701,263 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="53" t="s">
+        <v>150</v>
+      </c>
+      <c r="B4" s="53"/>
+      <c r="D4" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="E4" s="53"/>
+      <c r="G4" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="H4" s="53"/>
+      <c r="J4" s="53" t="s">
         <v>153</v>
       </c>
-      <c r="B4" s="50"/>
-      <c r="D4" s="50" t="s">
+      <c r="K4" s="53"/>
+      <c r="M4" s="53" t="s">
         <v>154</v>
       </c>
-      <c r="E4" s="50"/>
-      <c r="G4" s="50" t="s">
+      <c r="N4" s="53"/>
+      <c r="P4" s="53" t="s">
         <v>155</v>
       </c>
-      <c r="H4" s="50"/>
-      <c r="J4" s="50" t="s">
+      <c r="Q4" s="53"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="53" t="s">
         <v>156</v>
       </c>
-      <c r="K4" s="50"/>
-      <c r="M4" s="50" t="s">
+      <c r="T4" s="53"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="53" t="s">
         <v>157</v>
       </c>
-      <c r="N4" s="50"/>
-      <c r="P4" s="50" t="s">
+      <c r="W4" s="53"/>
+      <c r="X4" s="1"/>
+      <c r="Y4" s="53" t="s">
         <v>158</v>
       </c>
-      <c r="Q4" s="50"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="50" t="s">
+      <c r="Z4" s="53"/>
+      <c r="AA4" s="1"/>
+      <c r="AB4" s="53" t="s">
         <v>159</v>
       </c>
-      <c r="T4" s="50"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="50" t="s">
+      <c r="AC4" s="53"/>
+      <c r="AE4" s="53" t="s">
         <v>160</v>
       </c>
-      <c r="W4" s="50"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="50" t="s">
+      <c r="AF4" s="53"/>
+      <c r="AG4" s="1"/>
+      <c r="AH4" s="53" t="s">
         <v>161</v>
       </c>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="1"/>
-      <c r="AB4" s="50" t="s">
+      <c r="AI4" s="53"/>
+      <c r="AJ4" s="1"/>
+      <c r="AK4" s="53" t="s">
         <v>162</v>
       </c>
-      <c r="AC4" s="50"/>
-      <c r="AE4" s="50" t="s">
+      <c r="AL4" s="53"/>
+      <c r="AM4" s="1"/>
+      <c r="AN4" s="53" t="s">
         <v>163</v>
       </c>
-      <c r="AF4" s="50"/>
-      <c r="AG4" s="1"/>
-      <c r="AH4" s="50" t="s">
+      <c r="AO4" s="53"/>
+      <c r="AP4" s="1"/>
+      <c r="AQ4" s="53" t="s">
         <v>164</v>
       </c>
-      <c r="AI4" s="50"/>
-      <c r="AJ4" s="1"/>
-      <c r="AK4" s="50" t="s">
-        <v>165</v>
-      </c>
-      <c r="AL4" s="50"/>
-      <c r="AM4" s="1"/>
-      <c r="AN4" s="50" t="s">
-        <v>166</v>
-      </c>
-      <c r="AO4" s="50"/>
-      <c r="AP4" s="1"/>
-      <c r="AQ4" s="50" t="s">
-        <v>167</v>
-      </c>
-      <c r="AR4" s="50"/>
+      <c r="AR4" s="53"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B5" s="44">
         <v>1</v>
       </c>
       <c r="D5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E5" s="44">
         <v>2</v>
       </c>
       <c r="G5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H5" s="44">
         <v>3</v>
       </c>
       <c r="J5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K5" s="44">
         <v>4</v>
       </c>
       <c r="M5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="N5" s="44">
         <v>5</v>
       </c>
       <c r="P5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="Q5" s="44">
         <v>6</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="T5" s="44">
         <v>7</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="W5" s="44">
         <v>8</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="Z5" s="44">
         <v>9</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AC5" s="44">
         <v>10</v>
       </c>
       <c r="AE5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AF5" s="44">
         <v>11</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AI5" s="44">
         <v>12</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AL5" s="44">
         <v>13</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AO5" s="44">
         <v>14</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AR5" s="44">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A6" s="53" t="str">
+      <c r="A6" s="56" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
-        <v>Soil</v>
-      </c>
-      <c r="B6" s="54"/>
-      <c r="D6" s="53" t="str">
+        <v/>
+      </c>
+      <c r="B6" s="57"/>
+      <c r="D6" s="56" t="str">
         <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="E6" s="54"/>
-      <c r="G6" s="53" t="str">
+      <c r="E6" s="57"/>
+      <c r="G6" s="56" t="str">
         <f>_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="H6" s="54"/>
-      <c r="J6" s="53" t="str">
+      <c r="H6" s="57"/>
+      <c r="J6" s="56" t="str">
         <f>_xlfn.XLOOKUP(K5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="K6" s="54"/>
-      <c r="M6" s="53" t="str">
+      <c r="K6" s="57"/>
+      <c r="M6" s="56" t="str">
         <f>_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="N6" s="54"/>
-      <c r="P6" s="53" t="str">
+      <c r="N6" s="57"/>
+      <c r="P6" s="56" t="str">
         <f>_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Q6" s="54"/>
+      <c r="Q6" s="57"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="53" t="str">
+      <c r="S6" s="56" t="str">
         <f>_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="T6" s="54"/>
+      <c r="T6" s="57"/>
       <c r="U6" s="1"/>
-      <c r="V6" s="53" t="str">
+      <c r="V6" s="56" t="str">
         <f>_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="W6" s="54"/>
+      <c r="W6" s="57"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="53" t="str">
+      <c r="Y6" s="56" t="str">
         <f>_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Z6" s="54"/>
+      <c r="Z6" s="57"/>
       <c r="AA6" s="1"/>
-      <c r="AB6" s="53" t="str">
+      <c r="AB6" s="56" t="str">
         <f>_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AC6" s="54"/>
-      <c r="AE6" s="53" t="str">
+      <c r="AC6" s="57"/>
+      <c r="AE6" s="56" t="str">
         <f>_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AF6" s="54"/>
+      <c r="AF6" s="57"/>
       <c r="AG6" s="1"/>
-      <c r="AH6" s="53" t="str">
+      <c r="AH6" s="56" t="str">
         <f>_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AI6" s="54"/>
+      <c r="AI6" s="57"/>
       <c r="AJ6" s="1"/>
-      <c r="AK6" s="53" t="str">
+      <c r="AK6" s="56" t="str">
         <f>_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AL6" s="54"/>
+      <c r="AL6" s="57"/>
       <c r="AM6" s="1"/>
-      <c r="AN6" s="53" t="str">
+      <c r="AN6" s="56" t="str">
         <f>_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AO6" s="54"/>
+      <c r="AO6" s="57"/>
       <c r="AP6" s="1"/>
-      <c r="AQ6" s="53" t="str">
+      <c r="AQ6" s="56" t="str">
         <f>_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AR6" s="54"/>
+      <c r="AR6" s="57"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -15687,7 +16897,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3821B4BC-2D03-B047-9DB8-8ECD257276B0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7E1F343-68A5-3340-AF23-43D8E7E1F914}">
   <dimension ref="A2:G23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -15696,14 +16906,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="58" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="D2" s="56" t="s">
+      <c r="B2" s="58"/>
+      <c r="D2" s="59" t="s">
         <v>82</v>
       </c>
-      <c r="E2" s="56"/>
+      <c r="E2" s="59"/>
       <c r="G2" s="24" t="s">
         <v>83</v>
       </c>
@@ -15852,7 +17062,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCE6F868-4227-8740-A8A1-4745562882FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E0556E9-786A-E84F-BF20-677A5EE9D63D}">
   <dimension ref="A2:N16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -15898,21 +17108,21 @@
         <v>1</v>
       </c>
       <c r="B3" s="3">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="C3" s="3">
-        <v>45</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3">
-        <v>30</v>
-      </c>
-      <c r="G3" s="3">
-        <v>25</v>
-      </c>
+        <v>45.0</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Depth</t>
+        </is>
+      </c>
+      <c r="E3" s="3">
+        <v>22.639320225</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="J3" s="1" t="s">
         <v>26</v>
@@ -15926,16 +17136,18 @@
         <v>2</v>
       </c>
       <c r="B4" s="3">
-        <v>42</v>
+        <v>42.0</v>
       </c>
       <c r="C4" s="3">
-        <v>48</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>26</v>
+        <v>48.0</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Depth</t>
+        </is>
       </c>
       <c r="E4" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
@@ -16081,7 +17293,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B481A4B-5762-2B4B-BD1E-7996162F3A9D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6620242D-B699-0640-AD9C-590D8F82AC0F}">
   <dimension ref="A2:F23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -16241,7 +17453,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7976BB56-7732-404C-B58A-55DA7F8052B3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D19B78E-FBCC-4E41-BB37-C8D0D27B23E8}">
   <dimension ref="B2:X22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -16260,36 +17472,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="60" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="F2" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="J2" s="60" t="s">
+        <v>126</v>
+      </c>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="N2" s="60" t="s">
         <v>127</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="F2" s="57" t="s">
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="R2" s="60" t="s">
         <v>128</v>
       </c>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="J2" s="57" t="s">
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="V2" s="60" t="s">
         <v>129</v>
       </c>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="N2" s="57" t="s">
-        <v>130</v>
-      </c>
-      <c r="O2" s="57"/>
-      <c r="P2" s="57"/>
-      <c r="R2" s="57" t="s">
-        <v>131</v>
-      </c>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="V2" s="57" t="s">
-        <v>132</v>
-      </c>
-      <c r="W2" s="57"/>
-      <c r="X2" s="57"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">

--- a/docs/lem/files/xslope_acads_simple.xlsx
+++ b/docs/lem/files/xslope_acads_simple.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D53F4FFA-A72E-9849-8C3B-3C3A51EB7D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6571542-1A3D-6A42-AC36-061894174704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11520" yWindow="2900" windowWidth="42700" windowHeight="22800" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="217">
   <si>
     <t>X</t>
   </si>
@@ -863,6 +863,21 @@
   </si>
   <si>
     <t>Angle</t>
+  </si>
+  <si>
+    <t>Type:</t>
+  </si>
+  <si>
+    <t>Type optons</t>
+  </si>
+  <si>
+    <t>phreatic</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Phreatic surface: static head reduced by cos² of the line's slope.</t>
+  </si>
+  <si>
+    <t>True piezometric line: u = γw × vertical distance below the line (static head).</t>
   </si>
 </sst>
 </file>
@@ -1338,13 +1353,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2560,7 +2575,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>piezo!$A$4:$A$18</c:f>
+              <c:f>piezo!$A$5:$A$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
@@ -2569,7 +2584,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>piezo!$B$4:$B$18</c:f>
+              <c:f>piezo!$B$5:$B$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
@@ -2621,7 +2636,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>piezo!$D$4:$D$18</c:f>
+              <c:f>piezo!$D$5:$D$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
@@ -2630,7 +2645,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>piezo!$E$4:$E$18</c:f>
+              <c:f>piezo!$E$5:$E$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
@@ -10335,7 +10350,7 @@
         <v>79</v>
       </c>
       <c r="D5" s="35">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -13350,10 +13365,18 @@
       <c r="K10" s="3">
         <v>0.0</v>
       </c>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
+      <c r="L10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="N10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0.0</v>
+      </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
           <t>none</t>
@@ -13407,10 +13430,10 @@
         <v>0.0</v>
       </c>
       <c r="AF10" s="3">
-        <v>0.0</v>
+        <v>100000.0</v>
       </c>
       <c r="AG10" s="3">
-        <v>0.0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.2">
@@ -14464,76 +14487,76 @@
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="53" t="inlineStr">
+      <c r="A4" s="55" t="inlineStr">
         <is>
           <t>Profile Line #1</t>
         </is>
       </c>
-      <c r="B4" s="53"/>
-      <c r="D4" s="53" t="s">
+      <c r="B4" s="55"/>
+      <c r="D4" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="53"/>
-      <c r="G4" s="53" t="s">
+      <c r="E4" s="55"/>
+      <c r="G4" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="53"/>
-      <c r="J4" s="53" t="s">
+      <c r="H4" s="55"/>
+      <c r="J4" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="53"/>
-      <c r="M4" s="53" t="s">
+      <c r="K4" s="55"/>
+      <c r="M4" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="53"/>
-      <c r="P4" s="53" t="s">
+      <c r="N4" s="55"/>
+      <c r="P4" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="53"/>
+      <c r="Q4" s="55"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="53" t="s">
+      <c r="S4" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="T4" s="53"/>
+      <c r="T4" s="55"/>
       <c r="U4" s="1"/>
-      <c r="V4" s="53" t="s">
+      <c r="V4" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="W4" s="53"/>
+      <c r="W4" s="55"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="53" t="s">
+      <c r="Y4" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="Z4" s="53"/>
+      <c r="Z4" s="55"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="53" t="s">
+      <c r="AB4" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="AC4" s="53"/>
-      <c r="AE4" s="53" t="s">
+      <c r="AC4" s="55"/>
+      <c r="AE4" s="55" t="s">
         <v>111</v>
       </c>
-      <c r="AF4" s="53"/>
+      <c r="AF4" s="55"/>
       <c r="AG4" s="1"/>
-      <c r="AH4" s="53" t="s">
+      <c r="AH4" s="55" t="s">
         <v>112</v>
       </c>
-      <c r="AI4" s="53"/>
+      <c r="AI4" s="55"/>
       <c r="AJ4" s="1"/>
-      <c r="AK4" s="53" t="s">
+      <c r="AK4" s="55" t="s">
         <v>113</v>
       </c>
-      <c r="AL4" s="53"/>
+      <c r="AL4" s="55"/>
       <c r="AM4" s="1"/>
-      <c r="AN4" s="53" t="s">
+      <c r="AN4" s="55" t="s">
         <v>114</v>
       </c>
-      <c r="AO4" s="53"/>
+      <c r="AO4" s="55"/>
       <c r="AP4" s="1"/>
-      <c r="AQ4" s="53" t="s">
+      <c r="AQ4" s="55" t="s">
         <v>115</v>
       </c>
-      <c r="AR4" s="53"/>
+      <c r="AR4" s="55"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="41" t="s">
@@ -14636,89 +14659,89 @@
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A6" s="54" t="str">
+      <c r="A6" s="53" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="B6" s="55"/>
-      <c r="D6" s="54" t="str">
+      <c r="B6" s="54"/>
+      <c r="D6" s="53" t="str">
         <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="E6" s="55"/>
-      <c r="G6" s="54" t="str">
+      <c r="E6" s="54"/>
+      <c r="G6" s="53" t="str">
         <f>_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="H6" s="55"/>
-      <c r="J6" s="54" t="str">
+      <c r="H6" s="54"/>
+      <c r="J6" s="53" t="str">
         <f>_xlfn.XLOOKUP(K5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="K6" s="55"/>
-      <c r="M6" s="54" t="str">
+      <c r="K6" s="54"/>
+      <c r="M6" s="53" t="str">
         <f>_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="N6" s="55"/>
-      <c r="P6" s="54" t="str">
+      <c r="N6" s="54"/>
+      <c r="P6" s="53" t="str">
         <f>_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Q6" s="55"/>
+      <c r="Q6" s="54"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="54" t="str">
+      <c r="S6" s="53" t="str">
         <f>_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="T6" s="55"/>
+      <c r="T6" s="54"/>
       <c r="U6" s="1"/>
-      <c r="V6" s="54" t="str">
+      <c r="V6" s="53" t="str">
         <f>_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="W6" s="55"/>
+      <c r="W6" s="54"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="54" t="str">
+      <c r="Y6" s="53" t="str">
         <f>_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Z6" s="55"/>
+      <c r="Z6" s="54"/>
       <c r="AA6" s="1"/>
-      <c r="AB6" s="54" t="str">
+      <c r="AB6" s="53" t="str">
         <f>_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AC6" s="55"/>
-      <c r="AE6" s="54" t="str">
+      <c r="AC6" s="54"/>
+      <c r="AE6" s="53" t="str">
         <f>_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AF6" s="55"/>
+      <c r="AF6" s="54"/>
       <c r="AG6" s="1"/>
-      <c r="AH6" s="54" t="str">
+      <c r="AH6" s="53" t="str">
         <f>_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AI6" s="55"/>
+      <c r="AI6" s="54"/>
       <c r="AJ6" s="1"/>
-      <c r="AK6" s="54" t="str">
+      <c r="AK6" s="53" t="str">
         <f>_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AL6" s="55"/>
+      <c r="AL6" s="54"/>
       <c r="AM6" s="1"/>
-      <c r="AN6" s="54" t="str">
+      <c r="AN6" s="53" t="str">
         <f>_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AO6" s="55"/>
+      <c r="AO6" s="54"/>
       <c r="AP6" s="1"/>
-      <c r="AQ6" s="54" t="str">
+      <c r="AQ6" s="53" t="str">
         <f>_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AR6" s="55"/>
+      <c r="AR6" s="54"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -15638,36 +15661,36 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AQ4:AR4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="AB6:AC6"/>
     <mergeCell ref="AE6:AF6"/>
     <mergeCell ref="AH6:AI6"/>
     <mergeCell ref="AK6:AL6"/>
     <mergeCell ref="AN6:AO6"/>
     <mergeCell ref="AQ6:AR6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AQ4:AR4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15705,74 +15728,74 @@
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="55" t="s">
         <v>150</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="D4" s="53" t="s">
+      <c r="B4" s="55"/>
+      <c r="D4" s="55" t="s">
         <v>151</v>
       </c>
-      <c r="E4" s="53"/>
-      <c r="G4" s="53" t="s">
+      <c r="E4" s="55"/>
+      <c r="G4" s="55" t="s">
         <v>152</v>
       </c>
-      <c r="H4" s="53"/>
-      <c r="J4" s="53" t="s">
+      <c r="H4" s="55"/>
+      <c r="J4" s="55" t="s">
         <v>153</v>
       </c>
-      <c r="K4" s="53"/>
-      <c r="M4" s="53" t="s">
+      <c r="K4" s="55"/>
+      <c r="M4" s="55" t="s">
         <v>154</v>
       </c>
-      <c r="N4" s="53"/>
-      <c r="P4" s="53" t="s">
+      <c r="N4" s="55"/>
+      <c r="P4" s="55" t="s">
         <v>155</v>
       </c>
-      <c r="Q4" s="53"/>
+      <c r="Q4" s="55"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="53" t="s">
+      <c r="S4" s="55" t="s">
         <v>156</v>
       </c>
-      <c r="T4" s="53"/>
+      <c r="T4" s="55"/>
       <c r="U4" s="1"/>
-      <c r="V4" s="53" t="s">
+      <c r="V4" s="55" t="s">
         <v>157</v>
       </c>
-      <c r="W4" s="53"/>
+      <c r="W4" s="55"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="53" t="s">
+      <c r="Y4" s="55" t="s">
         <v>158</v>
       </c>
-      <c r="Z4" s="53"/>
+      <c r="Z4" s="55"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="53" t="s">
+      <c r="AB4" s="55" t="s">
         <v>159</v>
       </c>
-      <c r="AC4" s="53"/>
-      <c r="AE4" s="53" t="s">
+      <c r="AC4" s="55"/>
+      <c r="AE4" s="55" t="s">
         <v>160</v>
       </c>
-      <c r="AF4" s="53"/>
+      <c r="AF4" s="55"/>
       <c r="AG4" s="1"/>
-      <c r="AH4" s="53" t="s">
+      <c r="AH4" s="55" t="s">
         <v>161</v>
       </c>
-      <c r="AI4" s="53"/>
+      <c r="AI4" s="55"/>
       <c r="AJ4" s="1"/>
-      <c r="AK4" s="53" t="s">
+      <c r="AK4" s="55" t="s">
         <v>162</v>
       </c>
-      <c r="AL4" s="53"/>
+      <c r="AL4" s="55"/>
       <c r="AM4" s="1"/>
-      <c r="AN4" s="53" t="s">
+      <c r="AN4" s="55" t="s">
         <v>163</v>
       </c>
-      <c r="AO4" s="53"/>
+      <c r="AO4" s="55"/>
       <c r="AP4" s="1"/>
-      <c r="AQ4" s="53" t="s">
+      <c r="AQ4" s="55" t="s">
         <v>164</v>
       </c>
-      <c r="AR4" s="53"/>
+      <c r="AR4" s="55"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="43" t="s">
@@ -16861,14 +16884,12 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="AQ6:AR6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AE6:AF6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AK6:AL6"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="M4:N4"/>
     <mergeCell ref="AK4:AL4"/>
     <mergeCell ref="AN4:AO4"/>
     <mergeCell ref="AQ4:AR4"/>
@@ -16885,12 +16906,14 @@
     <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="AE4:AF4"/>
     <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AQ6:AR6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="AE6:AF6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AK6:AL6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16898,14 +16921,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7E1F343-68A5-3340-AF23-43D8E7E1F914}">
-  <dimension ref="A2:G23"/>
+  <dimension ref="A2:H24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="7" customWidth="1"/>
     <col min="6" max="6" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="58" t="s">
         <v>84</v>
       </c>
@@ -16918,93 +16941,122 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="B3" s="38" t="inlineStr">
+        <is>
+          <t>piezo</t>
+        </is>
+      </c>
+      <c r="D3" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="E3" s="40" t="inlineStr">
+        <is>
+          <t>piezo</t>
+        </is>
+      </c>
+      <c r="G3" s="24"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G4" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G6" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="H6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="D16" s="4"/>
@@ -17052,11 +17104,22 @@
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
     </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="D2:E2"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3 E3" xr:uid="{62365587-5741-D749-B74F-CDA32F05212C}">
+      <formula1>$G$5:$G$6</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/docs/lem/files/xslope_acads_simple.xlsx
+++ b/docs/lem/files/xslope_acads_simple.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6571542-1A3D-6A42-AC36-061894174704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31D06D1B-9F8B-4A48-B6E0-097F17D68253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11520" yWindow="2900" windowWidth="42700" windowHeight="22800" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="34200" windowHeight="19900" activeTab="15" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -28,12 +28,13 @@
     <sheet name="lloads" sheetId="17" r:id="rId13"/>
     <sheet name="seep bc" sheetId="11" r:id="rId14"/>
     <sheet name="seep bc (2)" sheetId="14" r:id="rId15"/>
+    <sheet name="tseep" sheetId="19" r:id="rId16"/>
   </sheets>
   <definedNames>
-    <definedName name="crack_depth">main!$D$9</definedName>
-    <definedName name="crack_depth_water">main!$D$10</definedName>
-    <definedName name="gamma_w">main!$D$8</definedName>
-    <definedName name="k">main!$D$11</definedName>
+    <definedName name="crack_depth">main!$D$11</definedName>
+    <definedName name="crack_depth_water">main!$D$12</definedName>
+    <definedName name="gamma_w">main!$D$10</definedName>
+    <definedName name="k">main!$D$13</definedName>
     <definedName name="max_depth" localSheetId="4">polygon!#REF!</definedName>
     <definedName name="max_depth">profile!$B$2</definedName>
     <definedName name="mesh">mat!#REF!</definedName>
@@ -62,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="266">
   <si>
     <t>X</t>
   </si>
@@ -305,9 +306,6 @@
     <t>s(f)</t>
   </si>
   <si>
-    <t>Base Values</t>
-  </si>
-  <si>
     <t>Standard Deviations</t>
   </si>
   <si>
@@ -450,9 +448,6 @@
     <t>max depth defines the elevation of a horizontal line that is treated as the bottom of the profile</t>
   </si>
   <si>
-    <t>Head:</t>
-  </si>
-  <si>
     <t>seep bc</t>
   </si>
   <si>
@@ -465,9 +460,6 @@
     <t>XSLOPE Input Template</t>
   </si>
   <si>
-    <t>Stress</t>
-  </si>
-  <si>
     <t>E</t>
   </si>
   <si>
@@ -558,40 +550,10 @@
     <t>Distributed Load #6</t>
   </si>
   <si>
-    <t>Specified Head #1</t>
-  </si>
-  <si>
-    <t>Specified Head #2</t>
-  </si>
-  <si>
-    <t>Specified Head #3</t>
-  </si>
-  <si>
-    <t>Specified Head #4</t>
-  </si>
-  <si>
-    <t>Specified Head #5</t>
-  </si>
-  <si>
     <t>Exit Face</t>
   </si>
   <si>
-    <t>Specified Head #1 (2)</t>
-  </si>
-  <si>
     <t>Exit Face (2)</t>
-  </si>
-  <si>
-    <t>Specified Head #2 (2)</t>
-  </si>
-  <si>
-    <t>Specified Head #3 (2)</t>
-  </si>
-  <si>
-    <t>Specified Head #4 (2)</t>
-  </si>
-  <si>
-    <t>Specified Head #5 (2)</t>
   </si>
   <si>
     <t>Distributed Load #1 (2)</t>
@@ -758,16 +720,7 @@
     <t>linear front model (kr0,h0)</t>
   </si>
   <si>
-    <t>van Genuchten model (vb_a, vg_n)</t>
-  </si>
-  <si>
     <t>Unsat model option</t>
-  </si>
-  <si>
-    <t>vg_a</t>
-  </si>
-  <si>
-    <t>vg_n</t>
   </si>
   <si>
     <t>Pore pressure (u) options</t>
@@ -878,6 +831,201 @@
   </si>
   <si>
     <t>True piezometric line: u = γw × vertical distance below the line (static head).</t>
+  </si>
+  <si>
+    <t>hb</t>
+  </si>
+  <si>
+    <t>gard</t>
+  </si>
+  <si>
+    <t>Gardner model (a, n)</t>
+  </si>
+  <si>
+    <t>van Genuchten model (a, n)</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>hb_sci</t>
+  </si>
+  <si>
+    <t>Generalized Hoek-Brown (rock mass): hb_sci, hb_gsi, hb_mi, hb_d</t>
+  </si>
+  <si>
+    <t>hb_gsi</t>
+  </si>
+  <si>
+    <t>hb_mi</t>
+  </si>
+  <si>
+    <t>hb_d</t>
+  </si>
+  <si>
+    <t>nu</t>
+  </si>
+  <si>
+    <t>BC Option:</t>
+  </si>
+  <si>
+    <t>head</t>
+  </si>
+  <si>
+    <t>flux</t>
+  </si>
+  <si>
+    <t>Head/Flux BC #1</t>
+  </si>
+  <si>
+    <t>specified head (len)</t>
+  </si>
+  <si>
+    <t>Head/Flux BC #2</t>
+  </si>
+  <si>
+    <t>Head/Flux BC #3</t>
+  </si>
+  <si>
+    <t>Head/Flux BC #4</t>
+  </si>
+  <si>
+    <t>Head/Flux BC #5</t>
+  </si>
+  <si>
+    <t>Head/Flux BC #1 (2)</t>
+  </si>
+  <si>
+    <t>Head/Flux BC #2 (2)</t>
+  </si>
+  <si>
+    <t>Head/Flux BC #3 (2)</t>
+  </si>
+  <si>
+    <t>Head/Flux BC #4 (2)</t>
+  </si>
+  <si>
+    <t>Head/Flux BC #5 (2)</t>
+  </si>
+  <si>
+    <t>Neumann flux - normal Darcy velocity (len/time), + = inflow</t>
+  </si>
+  <si>
+    <t>polygon</t>
+  </si>
+  <si>
+    <t>Polygons describing the slope geometry</t>
+  </si>
+  <si>
+    <t>piles</t>
+  </si>
+  <si>
+    <t>Piles</t>
+  </si>
+  <si>
+    <t>lloads</t>
+  </si>
+  <si>
+    <t>Line loads</t>
+  </si>
+  <si>
+    <t>elastic</t>
+  </si>
+  <si>
+    <t>Elastic / infinite strength (cannot fail). FEM: no yield; LEM: impenetrable</t>
+  </si>
+  <si>
+    <t>t_cut</t>
+  </si>
+  <si>
+    <t>Shear Strength/Stiffness</t>
+  </si>
+  <si>
+    <t>Color legend</t>
+  </si>
+  <si>
+    <t>phi_b</t>
+  </si>
+  <si>
+    <t>s_cap</t>
+  </si>
+  <si>
+    <t>Unit Options:</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>Imperial</t>
+  </si>
+  <si>
+    <t>Units:</t>
+  </si>
+  <si>
+    <t>Time Units:</t>
+  </si>
+  <si>
+    <t>sec</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>hr</t>
+  </si>
+  <si>
+    <t>day</t>
+  </si>
+  <si>
+    <t>Time:</t>
+  </si>
+  <si>
+    <t>t1</t>
+  </si>
+  <si>
+    <t>t2</t>
+  </si>
+  <si>
+    <t>t3</t>
+  </si>
+  <si>
+    <t>t4</t>
+  </si>
+  <si>
+    <t>t5</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>save_interval:</t>
+  </si>
+  <si>
+    <t>duration:</t>
+  </si>
+  <si>
+    <t>stage_1:</t>
+  </si>
+  <si>
+    <t>stage_2:</t>
+  </si>
+  <si>
+    <t>tseep</t>
+  </si>
+  <si>
+    <t>Transient seepage boundary conditions and run options</t>
+  </si>
+  <si>
+    <t>Ss</t>
+  </si>
+  <si>
+    <t>Sy</t>
+  </si>
+  <si>
+    <t>save_times</t>
+  </si>
+  <si>
+    <t>reservoir</t>
   </si>
 </sst>
 </file>
@@ -1027,7 +1175,7 @@
       <name val="Aptos Narrow"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1090,12 +1238,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1121,6 +1263,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1268,29 +1422,14 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1309,28 +1448,28 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1343,29 +1482,46 @@
     <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1383,14 +1539,14 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="21">
     <dxf>
       <fill>
         <patternFill>
@@ -1409,34 +1565,6 @@
       <fill>
         <patternFill>
           <bgColor theme="1" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1478,7 +1606,77 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="2" tint="-0.499984740745262"/>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6156,7 +6354,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Specified Head #1</c:v>
+                  <c:v>Head/Flux BC #1</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6225,7 +6423,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Specified Head #2</c:v>
+                  <c:v>Head/Flux BC #2</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6294,7 +6492,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Specified Head #3</c:v>
+                  <c:v>Head/Flux BC #3</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6363,7 +6561,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Specified Head #4</c:v>
+                  <c:v>Head/Flux BC #4</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6435,7 +6633,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Specified Head #5</c:v>
+                  <c:v>Head/Flux BC #5</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6579,7 +6777,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Specified Head #1 (2)</c:v>
+                  <c:v>Head/Flux BC #1 (2)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6651,7 +6849,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Specified Head #2 (2)</c:v>
+                  <c:v>Head/Flux BC #2 (2)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6714,7 +6912,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Specified Head #3 (2)</c:v>
+                  <c:v>Head/Flux BC #3 (2)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6777,7 +6975,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Specified Head #4 (2)</c:v>
+                  <c:v>Head/Flux BC #4 (2)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6846,7 +7044,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Specified Head #5 (2)</c:v>
+                  <c:v>Head/Flux BC #5 (2)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8844,6 +9042,499 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>tseep!$C$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>t1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>tseep!$B$3:$B$100</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="98"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>tseep!$C$3:$C$100</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="98"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-538B-9247-859A-D6EC9732CE9B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>tseep!$D$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>t2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>tseep!$B$3:$B$100</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="98"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>tseep!$D$3:$D$100</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="98"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-538B-9247-859A-D6EC9732CE9B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>tseep!$E$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>t3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>tseep!$B$3:$B$100</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="98"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>tseep!$E$3:$E$100</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="98"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-538B-9247-859A-D6EC9732CE9B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>tseep!$F$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>t4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>tseep!$B$3:$B$100</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="98"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>tseep!$F$3:$F$100</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="98"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-538B-9247-859A-D6EC9732CE9B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>tseep!$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>t5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>tseep!$B$3:$B$100</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="98"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>tseep!$G$3:$G$100</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="98"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-538B-9247-859A-D6EC9732CE9B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="782614975"/>
+        <c:axId val="782616767"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="782614975"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="782616767"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="782616767"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="782614975"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -8884,7 +9575,563 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -10008,6 +11255,47 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>99785</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>88901</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>299357</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>99787</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7655F65D-6FA7-DB16-246F-5BDA3120EC02}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -10325,7 +11613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71FAED0A-C8CC-8343-BA2E-B8E4255891E7}">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.6640625" customWidth="1"/>
@@ -10337,7 +11625,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="32" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19" x14ac:dyDescent="0.25">
@@ -10347,46 +11635,46 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C5" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="D5" s="35">
-        <v>13</v>
+        <v>78</v>
+      </c>
+      <c r="D5" s="30">
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="49" t="s">
+      <c r="B7" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
       <c r="F7" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="36" t="s">
+      <c r="G7" s="31" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C8" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="1">
-        <v>9.81</v>
+        <v>243</v>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
       </c>
       <c r="F8" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="G8" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C9" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0.0</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="D9" s="1"/>
       <c r="F9" s="1" t="s">
         <v>19</v>
       </c>
@@ -10396,10 +11684,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C10" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D10" s="1">
-        <v>0.0</v>
+        <v>9.81</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>17</v>
@@ -10411,88 +11699,177 @@
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B11" s="1"/>
       <c r="C11" s="14" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="D11" s="1">
         <v>0.0</v>
       </c>
       <c r="F11" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="G11" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C12" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F12" s="1" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C13" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G13" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G13" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="F14" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G14" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="F15" s="1" t="s">
-        <v>118</v>
+        <v>34</v>
       </c>
       <c r="G15" t="s">
-        <v>120</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="F16" s="1" t="s">
-        <v>36</v>
+        <v>115</v>
       </c>
       <c r="G16" t="s">
-        <v>37</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="1"/>
       <c r="F17" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>122</v>
+        <v>36</v>
+      </c>
+      <c r="G17" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="F18" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G18" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="F19" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G19" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="F20" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G20" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="G18" s="9" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="F21" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="F22" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G22" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="1"/>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B24" s="1"/>
+    </row>
+    <row r="49" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D49" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="50" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D50" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="51" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D51" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="53" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D53" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="54" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D54" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="55" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D55" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="56" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D56" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="57" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D57" s="1" t="s">
+        <v>248</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B7:D7"/>
   </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8" xr:uid="{BAE3FC11-E776-8E44-B1AE-D9B052583E4F}">
+      <formula1>$D$50:$D$51</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D9" xr:uid="{73E87265-AF9F-0944-800E-CFF30E3B4CA4}">
+      <formula1>$D$54:$D$57</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -10518,32 +11895,32 @@
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B2" s="61" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="C2" s="61"/>
       <c r="D2" s="61"/>
       <c r="F2" s="61" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="G2" s="61"/>
       <c r="H2" s="61"/>
       <c r="J2" s="61" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="K2" s="61"/>
       <c r="L2" s="61"/>
       <c r="N2" s="61" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="O2" s="61"/>
       <c r="P2" s="61"/>
       <c r="R2" s="61" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="S2" s="61"/>
       <c r="T2" s="61"/>
       <c r="V2" s="61" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="W2" s="61"/>
       <c r="X2" s="61"/>
@@ -11015,64 +12392,64 @@
         <v>25</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="C2" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="G2" s="40" t="s">
+        <v>192</v>
+      </c>
+      <c r="H2" s="40" t="s">
+        <v>193</v>
+      </c>
+      <c r="I2" s="40" t="s">
+        <v>177</v>
+      </c>
+      <c r="J2" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="K2" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="L2" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="M2" s="27" t="s">
+        <v>178</v>
+      </c>
+      <c r="N2" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="O2" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="P2" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q2" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="R2" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="G2" s="45" t="s">
-        <v>208</v>
-      </c>
-      <c r="H2" s="45" t="s">
-        <v>209</v>
-      </c>
-      <c r="I2" s="45" t="s">
-        <v>193</v>
-      </c>
-      <c r="J2" s="32" t="s">
-        <v>107</v>
-      </c>
-      <c r="K2" s="32" t="s">
-        <v>108</v>
-      </c>
-      <c r="L2" s="32" t="s">
-        <v>109</v>
-      </c>
-      <c r="M2" s="32" t="s">
-        <v>194</v>
-      </c>
-      <c r="N2" s="32" t="s">
-        <v>195</v>
-      </c>
-      <c r="O2" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="P2" s="33" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q2" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="R2" s="33" t="s">
-        <v>106</v>
-      </c>
       <c r="Z2" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="AA2" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="AB2" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
@@ -11103,13 +12480,13 @@
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="Z3" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="AA3" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="AB3" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
@@ -11140,7 +12517,7 @@
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
       <c r="Z4" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -11171,7 +12548,7 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="Z5" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -11258,13 +12635,13 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="Z8" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="AA8" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="AB8" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
@@ -11295,13 +12672,13 @@
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="Z9" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="AA9" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="AB9" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
@@ -11332,13 +12709,13 @@
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
       <c r="Z10" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="AA10" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="AB10" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
@@ -11369,13 +12746,13 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="Z11" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="AA11" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="AB11" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -11687,25 +13064,25 @@
       <c r="R22" s="3"/>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="T23" s="47"/>
+      <c r="T23" s="42"/>
       <c r="U23" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.2">
       <c r="K24" s="9"/>
       <c r="L24" s="9"/>
-      <c r="T24" s="31"/>
+      <c r="T24" s="26"/>
       <c r="U24" s="9" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.2">
       <c r="K25" s="9"/>
       <c r="L25" s="9"/>
-      <c r="T25" s="34"/>
+      <c r="T25" s="29"/>
       <c r="U25" s="9" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -11743,58 +13120,58 @@
         <v>25</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="C2" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="G2" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="H2" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="I2" s="40" t="s">
+        <v>177</v>
+      </c>
+      <c r="J2" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="K2" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="L2" s="41" t="s">
+        <v>157</v>
+      </c>
+      <c r="M2" s="41" t="s">
+        <v>158</v>
+      </c>
+      <c r="N2" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="O2" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="P2" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="G2" s="45" t="s">
-        <v>165</v>
-      </c>
-      <c r="H2" s="45" t="s">
-        <v>173</v>
-      </c>
-      <c r="I2" s="45" t="s">
-        <v>193</v>
-      </c>
-      <c r="J2" s="32" t="s">
-        <v>166</v>
-      </c>
-      <c r="K2" s="32" t="s">
-        <v>167</v>
-      </c>
-      <c r="L2" s="46" t="s">
-        <v>170</v>
-      </c>
-      <c r="M2" s="46" t="s">
-        <v>171</v>
-      </c>
-      <c r="N2" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="O2" s="33" t="s">
-        <v>168</v>
-      </c>
-      <c r="P2" s="33" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q2" s="33" t="s">
-        <v>177</v>
+      <c r="Q2" s="28" t="s">
+        <v>164</v>
       </c>
       <c r="Z2" t="s">
         <v>40</v>
       </c>
       <c r="AA2" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
@@ -11818,10 +13195,10 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="Z3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA3" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
@@ -12022,21 +13399,21 @@
       <c r="K15" s="9"/>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="S16" s="47"/>
+      <c r="S16" s="42"/>
       <c r="T16" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="19:20" x14ac:dyDescent="0.2">
-      <c r="S17" s="31"/>
+      <c r="S17" s="26"/>
       <c r="T17" s="9" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="19:20" x14ac:dyDescent="0.2">
-      <c r="S18" s="34"/>
+      <c r="S18" s="29"/>
       <c r="T18" s="9" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -12068,7 +13445,7 @@
         <v>25</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>3</v>
@@ -12077,10 +13454,10 @@
         <v>4</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -12290,7 +13667,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D036245-91C1-5842-93DD-735018175DE8}">
-  <dimension ref="B2:R24"/>
+  <dimension ref="B2:U24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -12301,95 +13678,104 @@
     <col min="16" max="16" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="62" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C2" s="62"/>
       <c r="E2" s="58" t="s">
-        <v>130</v>
+        <v>215</v>
       </c>
       <c r="F2" s="58"/>
       <c r="H2" s="58" t="s">
-        <v>131</v>
+        <v>217</v>
       </c>
       <c r="I2" s="58"/>
       <c r="K2" s="58" t="s">
-        <v>132</v>
+        <v>218</v>
       </c>
       <c r="L2" s="58"/>
       <c r="N2" s="58" t="s">
-        <v>133</v>
+        <v>219</v>
       </c>
       <c r="O2" s="58"/>
       <c r="Q2" s="58" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="R2" s="58"/>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B3" s="62"/>
       <c r="C3" s="62"/>
-      <c r="E3" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="F3" s="38"/>
-      <c r="H3" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="I3" s="38"/>
-      <c r="K3" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="L3" s="38"/>
-      <c r="N3" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="O3" s="38"/>
-      <c r="Q3" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="R3" s="38"/>
-    </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B4" s="28" t="s">
+      <c r="E3" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="F3" s="33"/>
+      <c r="H3" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="I3" s="33"/>
+      <c r="K3" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="L3" s="33"/>
+      <c r="N3" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="O3" s="33"/>
+      <c r="Q3" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="R3" s="33"/>
+      <c r="T3" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="28" t="s">
+      <c r="I4" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="28" t="s">
+      <c r="K4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="L4" s="28" t="s">
+      <c r="L4" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="N4" s="28" t="s">
+      <c r="N4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O4" s="28" t="s">
+      <c r="O4" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="Q4" s="28" t="s">
+      <c r="Q4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="R4" s="28" t="s">
+      <c r="R4" s="25" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T4" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="U4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="5" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="E5" s="3"/>
@@ -12402,8 +13788,14 @@
       <c r="O5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
-    </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T5" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="U5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="6" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="E6" s="3"/>
@@ -12416,8 +13808,12 @@
       <c r="O6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
-    </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T6" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="U6" s="9"/>
+    </row>
+    <row r="7" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="E7" s="3"/>
@@ -12431,7 +13827,7 @@
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="E8" s="3"/>
@@ -12445,7 +13841,7 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="E9" s="3"/>
@@ -12459,7 +13855,7 @@
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="E10" s="3"/>
@@ -12473,7 +13869,7 @@
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="E11" s="3"/>
@@ -12487,7 +13883,7 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="E12" s="3"/>
@@ -12501,7 +13897,7 @@
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="E13" s="3"/>
@@ -12515,7 +13911,7 @@
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
     </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="E14" s="3"/>
@@ -12529,7 +13925,7 @@
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
     </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="E15" s="3"/>
@@ -12543,7 +13939,7 @@
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
     </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="E16" s="3"/>
@@ -12678,13 +14074,18 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3 H3 K3 N3 Q3" xr:uid="{21F200C9-4829-4345-9958-0F754F272AD0}">
+      <formula1>$T$4:$T$6</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4C3C734-6227-7445-884D-1F1A5F3909C7}">
-  <dimension ref="B2:R24"/>
+  <dimension ref="B2:U24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -12695,95 +14096,104 @@
     <col min="16" max="16" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="63" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="C2" s="63"/>
       <c r="E2" s="59" t="s">
-        <v>136</v>
+        <v>221</v>
       </c>
       <c r="F2" s="59"/>
       <c r="H2" s="59" t="s">
-        <v>138</v>
+        <v>222</v>
       </c>
       <c r="I2" s="59"/>
       <c r="K2" s="59" t="s">
-        <v>139</v>
+        <v>223</v>
       </c>
       <c r="L2" s="59"/>
       <c r="N2" s="59" t="s">
-        <v>140</v>
+        <v>224</v>
       </c>
       <c r="O2" s="59"/>
       <c r="Q2" s="59" t="s">
-        <v>141</v>
+        <v>225</v>
       </c>
       <c r="R2" s="59"/>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B3" s="63"/>
       <c r="C3" s="63"/>
-      <c r="E3" s="39" t="s">
-        <v>94</v>
-      </c>
-      <c r="F3" s="40"/>
-      <c r="H3" s="39" t="s">
-        <v>94</v>
-      </c>
-      <c r="I3" s="40"/>
-      <c r="K3" s="39" t="s">
-        <v>94</v>
-      </c>
-      <c r="L3" s="40"/>
-      <c r="N3" s="39" t="s">
-        <v>94</v>
-      </c>
-      <c r="O3" s="40"/>
-      <c r="Q3" s="39" t="s">
-        <v>94</v>
-      </c>
-      <c r="R3" s="40"/>
-    </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B4" s="28" t="s">
+      <c r="E3" s="34" t="s">
+        <v>213</v>
+      </c>
+      <c r="F3" s="35"/>
+      <c r="H3" s="34" t="s">
+        <v>213</v>
+      </c>
+      <c r="I3" s="35"/>
+      <c r="K3" s="34" t="s">
+        <v>213</v>
+      </c>
+      <c r="L3" s="35"/>
+      <c r="N3" s="34" t="s">
+        <v>213</v>
+      </c>
+      <c r="O3" s="35"/>
+      <c r="Q3" s="34" t="s">
+        <v>213</v>
+      </c>
+      <c r="R3" s="35"/>
+      <c r="T3" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="28" t="s">
+      <c r="I4" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="28" t="s">
+      <c r="K4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="L4" s="28" t="s">
+      <c r="L4" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="N4" s="28" t="s">
+      <c r="N4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O4" s="28" t="s">
+      <c r="O4" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="Q4" s="28" t="s">
+      <c r="Q4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="R4" s="28" t="s">
+      <c r="R4" s="25" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T4" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="U4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="5" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="E5" s="3"/>
@@ -12796,8 +14206,14 @@
       <c r="O5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
-    </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T5" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="U5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="6" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="E6" s="3"/>
@@ -12811,7 +14227,7 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="E7" s="3"/>
@@ -12825,7 +14241,7 @@
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="E8" s="3"/>
@@ -12839,7 +14255,7 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="E9" s="3"/>
@@ -12853,7 +14269,7 @@
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="E10" s="3"/>
@@ -12867,7 +14283,7 @@
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="E11" s="3"/>
@@ -12881,7 +14297,7 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="E12" s="3"/>
@@ -12895,7 +14311,7 @@
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="E13" s="3"/>
@@ -12909,7 +14325,7 @@
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
     </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="E14" s="3"/>
@@ -12923,7 +14339,7 @@
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
     </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="E15" s="3"/>
@@ -12937,7 +14353,7 @@
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
     </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="E16" s="3"/>
@@ -13072,7 +14488,945 @@
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="N2:O2"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3 H3 K3 N3 Q3" xr:uid="{68C61D93-1721-F843-8E53-0F0E50006C65}">
+      <formula1>$T$4:$T$5</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B20D353C-FC33-C347-9989-88B2E3FC7B94}">
+  <dimension ref="B2:J100"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3.5" customWidth="1"/>
+    <col min="2" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="7.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B2" s="50" t="s">
+        <v>255</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>251</v>
+      </c>
+      <c r="E2" s="50" t="s">
+        <v>252</v>
+      </c>
+      <c r="F2" s="50" t="s">
+        <v>253</v>
+      </c>
+      <c r="G2" s="50" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="I3" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="I5" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="J5" s="3"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="I7" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="I8" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="J10" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="J11" s="4"/>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="J12" s="4"/>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="J13" s="4"/>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="J16" s="4"/>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="J18" s="4"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="J19" s="4"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="J21" s="4"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="J22" s="4"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="J23" s="4"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="J24" s="4"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="J25" s="4"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="J26" s="4"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="J27" s="4"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="J28" s="4"/>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="J29" s="4"/>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="J30" s="4"/>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="J31" s="4"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="J32" s="4"/>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="J33" s="4"/>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="J34" s="4"/>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="J35" s="4"/>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="J36" s="4"/>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="J37" s="4"/>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="J38" s="4"/>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="J39" s="4"/>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="J40" s="4"/>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="J41" s="4"/>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="J42" s="4"/>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="J43" s="4"/>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="J44" s="4"/>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="J45" s="4"/>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="J46" s="4"/>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="J47" s="4"/>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="J48" s="4"/>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="J49" s="4"/>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="J50" s="4"/>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="J51" s="4"/>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="J52" s="4"/>
+    </row>
+    <row r="53" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="J53" s="4"/>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="J54" s="4"/>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="J55" s="4"/>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="J56" s="4"/>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="J57" s="4"/>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="J58" s="4"/>
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="J59" s="4"/>
+    </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="J60" s="4"/>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="J61" s="4"/>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="J62" s="4"/>
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
+      <c r="J63" s="4"/>
+    </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
+      <c r="J64" s="4"/>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3"/>
+      <c r="J65" s="4"/>
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
+      <c r="J66" s="4"/>
+    </row>
+    <row r="67" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="J67" s="4"/>
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="J68" s="4"/>
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="J69" s="4"/>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="J70" s="4"/>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
+      <c r="J71" s="4"/>
+    </row>
+    <row r="72" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+      <c r="J72" s="4"/>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
+      <c r="J73" s="4"/>
+    </row>
+    <row r="74" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3"/>
+      <c r="J74" s="4"/>
+    </row>
+    <row r="75" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
+      <c r="J75" s="4"/>
+    </row>
+    <row r="76" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+      <c r="J76" s="4"/>
+    </row>
+    <row r="77" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
+      <c r="J77" s="4"/>
+    </row>
+    <row r="78" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="J78" s="4"/>
+    </row>
+    <row r="79" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3"/>
+      <c r="J79" s="4"/>
+    </row>
+    <row r="80" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
+      <c r="J80" s="4"/>
+    </row>
+    <row r="81" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3"/>
+      <c r="J81" s="4"/>
+    </row>
+    <row r="82" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
+      <c r="J82" s="4"/>
+    </row>
+    <row r="83" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3"/>
+      <c r="J83" s="4"/>
+    </row>
+    <row r="84" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
+      <c r="J84" s="4"/>
+    </row>
+    <row r="85" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3"/>
+      <c r="J85" s="4"/>
+    </row>
+    <row r="86" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
+      <c r="J86" s="4"/>
+    </row>
+    <row r="87" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
+      <c r="J87" s="4"/>
+    </row>
+    <row r="88" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B88" s="3"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
+      <c r="J88" s="4"/>
+    </row>
+    <row r="89" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
+      <c r="J89" s="4"/>
+    </row>
+    <row r="90" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+      <c r="J90" s="4"/>
+    </row>
+    <row r="91" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
+      <c r="J91" s="4"/>
+    </row>
+    <row r="92" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
+      <c r="J92" s="4"/>
+    </row>
+    <row r="93" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
+      <c r="J93" s="4"/>
+    </row>
+    <row r="94" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
+      <c r="J94" s="4"/>
+    </row>
+    <row r="95" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
+      <c r="J95" s="4"/>
+    </row>
+    <row r="96" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
+      <c r="J96" s="4"/>
+    </row>
+    <row r="97" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
+      <c r="J97" s="4"/>
+    </row>
+    <row r="98" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+      <c r="J98" s="4"/>
+    </row>
+    <row r="99" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
+      <c r="J99" s="4"/>
+    </row>
+    <row r="100" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
+      <c r="J100" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -13088,394 +15442,443 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60A900FC-A692-B445-95C9-59E70352B291}">
-  <dimension ref="A2:AG51"/>
+  <dimension ref="A2:AP52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" style="1" customWidth="1"/>
     <col min="3" max="10" width="8.5" style="1" customWidth="1"/>
-    <col min="11" max="31" width="8.5" customWidth="1"/>
-    <col min="32" max="32" width="8.5" style="1" customWidth="1"/>
-    <col min="33" max="33" width="8.5" customWidth="1"/>
+    <col min="11" max="42" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C2" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E2"/>
       <c r="F2"/>
       <c r="G2"/>
-      <c r="K2" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="U2" s="6"/>
-      <c r="AA2" s="6" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L2" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="AD2" s="6"/>
+      <c r="AJ2" s="6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C3" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F3"/>
       <c r="G3"/>
-      <c r="K3" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L3" t="s">
-        <v>59</v>
-      </c>
-      <c r="U3" s="14"/>
-      <c r="AA3" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="O3" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="P3" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD3" s="14"/>
+      <c r="AJ3" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="4" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" t="s">
         <v>70</v>
-      </c>
-      <c r="D4" t="s">
-        <v>71</v>
       </c>
       <c r="F4"/>
       <c r="G4"/>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="42"/>
+      <c r="M4" t="s">
+        <v>161</v>
+      </c>
+      <c r="O4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L4" t="s">
-        <v>60</v>
-      </c>
-      <c r="U4" s="14"/>
-      <c r="AA4" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="P4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD4" s="14"/>
+      <c r="AJ4" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C5" s="1" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="D5" t="s">
+        <v>191</v>
+      </c>
+      <c r="L5" s="26"/>
+      <c r="M5" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="AD5" s="14"/>
+      <c r="AJ5" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="AK5" s="9" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="C6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="L6" s="29"/>
+      <c r="M6" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="P6" t="s">
+        <v>190</v>
+      </c>
+      <c r="AE6" s="1"/>
+      <c r="AF6" s="1"/>
+    </row>
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="C7" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="AE7" s="1"/>
+      <c r="AF7" s="1"/>
+    </row>
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="C9" s="52" t="s">
+        <v>236</v>
+      </c>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="52"/>
+      <c r="K9" s="52"/>
+      <c r="L9" s="52"/>
+      <c r="M9" s="52"/>
+      <c r="N9" s="52"/>
+      <c r="O9" s="52"/>
+      <c r="P9" s="52"/>
+      <c r="Q9" s="52"/>
+      <c r="R9" s="52"/>
+      <c r="S9" s="52"/>
+      <c r="T9" s="52"/>
+      <c r="U9" s="52"/>
+      <c r="V9" s="52"/>
+      <c r="W9" s="52"/>
+      <c r="X9" s="52"/>
+      <c r="Y9" s="52"/>
+      <c r="Z9" s="52"/>
+      <c r="AA9" s="52" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB9" s="52"/>
+      <c r="AC9" s="52"/>
+      <c r="AD9" s="52"/>
+      <c r="AE9" s="52"/>
+      <c r="AF9" s="52"/>
+      <c r="AG9" s="52" t="s">
+        <v>91</v>
+      </c>
+      <c r="AH9" s="52"/>
+      <c r="AI9" s="52"/>
+      <c r="AJ9" s="52"/>
+      <c r="AK9" s="52"/>
+      <c r="AL9" s="52"/>
+      <c r="AM9" s="52"/>
+      <c r="AN9" s="52"/>
+      <c r="AO9" s="52"/>
+      <c r="AP9" s="52"/>
+    </row>
+    <row r="10" spans="1:42" ht="18" x14ac:dyDescent="0.25">
+      <c r="A10" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="E10" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="45" t="s">
+        <v>51</v>
+      </c>
+      <c r="H10" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="I10" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="J10" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="K10" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="L10" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="M10" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="N10" s="43" t="s">
+        <v>211</v>
+      </c>
+      <c r="O10" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="P10" s="44" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q10" s="44" t="s">
+        <v>238</v>
+      </c>
+      <c r="R10" s="44" t="s">
+        <v>239</v>
+      </c>
+      <c r="S10" s="44" t="s">
+        <v>173</v>
+      </c>
+      <c r="T10" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="U10" s="44" t="s">
+        <v>175</v>
+      </c>
+      <c r="V10" s="44" t="s">
+        <v>176</v>
+      </c>
+      <c r="W10" s="44" t="s">
+        <v>206</v>
+      </c>
+      <c r="X10" s="44" t="s">
+        <v>208</v>
+      </c>
+      <c r="Y10" s="44" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z10" s="44" t="s">
+        <v>210</v>
+      </c>
+      <c r="AA10" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB10" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC10" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD10" s="46" t="s">
+        <v>73</v>
+      </c>
+      <c r="AE10" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF10" s="47" t="s">
+        <v>136</v>
+      </c>
+      <c r="AG10" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="L5" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="U5" s="14"/>
-      <c r="AA5" s="1"/>
-      <c r="AB5" s="9"/>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="K6" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="L6" t="s">
-        <v>206</v>
-      </c>
-      <c r="P6" s="1"/>
-      <c r="V6" s="1"/>
-      <c r="W6" s="1"/>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="C8" s="50" t="s">
-        <v>57</v>
-      </c>
-      <c r="D8" s="51"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
-      <c r="L8" s="52"/>
-      <c r="M8" s="52"/>
-      <c r="N8" s="52"/>
-      <c r="O8" s="52"/>
-      <c r="P8" s="1"/>
-      <c r="R8" s="50" t="s">
-        <v>58</v>
-      </c>
-      <c r="S8" s="50"/>
-      <c r="T8" s="50"/>
-      <c r="U8" s="50"/>
-      <c r="V8" s="50"/>
-      <c r="W8" s="50"/>
-      <c r="X8" s="50" t="s">
-        <v>92</v>
-      </c>
-      <c r="Y8" s="50"/>
-      <c r="Z8" s="50"/>
-      <c r="AA8" s="50"/>
-      <c r="AB8" s="50"/>
-      <c r="AC8" s="50"/>
-      <c r="AD8" s="50"/>
-      <c r="AE8" s="50"/>
-      <c r="AF8" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG8" s="50"/>
-    </row>
-    <row r="9" spans="1:33" ht="18" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="48" t="s">
+      <c r="AH10" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI10" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ10" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK10" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="AL10" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="AM10" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="E9" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="H9" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="I9" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="J9" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="K9" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="L9" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="M9" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="N9" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="O9" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="P9" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q9" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="R9" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="S9" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="T9" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="U9" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="V9" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="W9" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="X9" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y9" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="Z9" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA9" s="25" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB9" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="AC9" s="25" t="s">
-        <v>97</v>
-      </c>
-      <c r="AD9" s="25" t="s">
-        <v>184</v>
-      </c>
-      <c r="AE9" s="25" t="s">
-        <v>185</v>
-      </c>
-      <c r="AF9" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AG9" s="30" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
+      <c r="AN10" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="AO10" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="AP10" s="23" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
         <v>1</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Soil</t>
         </is>
       </c>
-      <c r="C10" s="3">
+      <c r="C11" s="3">
         <v>20.0</v>
       </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="D11" s="3"/>
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>mc</t>
         </is>
       </c>
-      <c r="F10" s="3">
+      <c r="F11" s="3">
         <v>3.0</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G11" s="3">
         <v>19.6</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H11" s="3">
         <v>0.0</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I11" s="3">
         <v>0.0</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J11" s="3">
         <v>0.0</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K11" s="3">
         <v>0.0</v>
       </c>
-      <c r="L10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="M10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="N10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="O10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
+      <c r="L11" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="M11" s="3">
+        <v>100000.0</v>
+      </c>
+      <c r="N11" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="Q10" s="3">
+      <c r="P11" s="3">
         <v>0.0</v>
       </c>
-      <c r="R10" s="3">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="T11" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="U11" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="V11" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="W11" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X11" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y11" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Z11" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AA11" s="3">
         <v>1.2</v>
       </c>
-      <c r="S10" s="3">
+      <c r="AB11" s="3">
         <v>1.8</v>
       </c>
-      <c r="T10" s="3">
+      <c r="AC11" s="3">
         <v>2.744</v>
       </c>
-      <c r="U10" s="3">
+      <c r="AD11" s="3">
         <v>0.0</v>
       </c>
-      <c r="V10" s="3">
+      <c r="AE11" s="3">
         <v>0.0</v>
       </c>
-      <c r="W10" s="3">
+      <c r="AF11" s="3">
         <v>0.0</v>
       </c>
-      <c r="X10" s="3">
+      <c r="AG11" s="3">
         <v>0.0</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AH11" s="3">
         <v>0.0</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AI11" s="3">
         <v>0.0</v>
       </c>
-      <c r="AA10" s="3" t="inlineStr">
+      <c r="AJ11" s="3" t="inlineStr">
         <is>
           <t>lf</t>
         </is>
       </c>
-      <c r="AB10" s="3">
+      <c r="AK11" s="3">
         <v>0.0</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AL11" s="3">
         <v>0.0</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AM11" s="3">
         <v>0.0</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AN11" s="3">
         <v>0.0</v>
       </c>
-      <c r="AF10" s="3">
-        <v>100000.0</v>
-      </c>
-      <c r="AG10" s="3">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+    </row>
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
         <v>2</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
-      <c r="AA11" s="3"/>
-      <c r="AB11" s="3"/>
-      <c r="AC11" s="3"/>
-      <c r="AD11" s="18"/>
-      <c r="AE11" s="19"/>
-      <c r="AF11" s="3"/>
-      <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A12" s="3">
-        <v>3</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -13505,14 +15908,23 @@
       <c r="AA12" s="3"/>
       <c r="AB12" s="3"/>
       <c r="AC12" s="3"/>
-      <c r="AD12" s="18"/>
-      <c r="AE12" s="19"/>
+      <c r="AD12" s="3"/>
+      <c r="AE12" s="3"/>
       <c r="AF12" s="3"/>
       <c r="AG12" s="3"/>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3"/>
+      <c r="AI12" s="3"/>
+      <c r="AJ12" s="3"/>
+      <c r="AK12" s="3"/>
+      <c r="AL12" s="3"/>
+      <c r="AM12" s="18"/>
+      <c r="AN12" s="19"/>
+      <c r="AO12" s="19"/>
+      <c r="AP12" s="19"/>
+    </row>
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -13546,10 +15958,19 @@
       <c r="AE13" s="3"/>
       <c r="AF13" s="3"/>
       <c r="AG13" s="3"/>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3"/>
+      <c r="AI13" s="3"/>
+      <c r="AJ13" s="3"/>
+      <c r="AK13" s="3"/>
+      <c r="AL13" s="3"/>
+      <c r="AM13" s="18"/>
+      <c r="AN13" s="19"/>
+      <c r="AO13" s="19"/>
+      <c r="AP13" s="19"/>
+    </row>
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -13583,10 +16004,19 @@
       <c r="AE14" s="3"/>
       <c r="AF14" s="3"/>
       <c r="AG14" s="3"/>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3"/>
+      <c r="AI14" s="3"/>
+      <c r="AJ14" s="3"/>
+      <c r="AK14" s="3"/>
+      <c r="AL14" s="3"/>
+      <c r="AM14" s="3"/>
+      <c r="AN14" s="3"/>
+      <c r="AO14" s="3"/>
+      <c r="AP14" s="3"/>
+    </row>
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -13620,10 +16050,19 @@
       <c r="AE15" s="3"/>
       <c r="AF15" s="3"/>
       <c r="AG15" s="3"/>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3"/>
+      <c r="AI15" s="3"/>
+      <c r="AJ15" s="3"/>
+      <c r="AK15" s="3"/>
+      <c r="AL15" s="3"/>
+      <c r="AM15" s="3"/>
+      <c r="AN15" s="3"/>
+      <c r="AO15" s="3"/>
+      <c r="AP15" s="3"/>
+    </row>
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -13657,10 +16096,19 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
+    </row>
+    <row r="17" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -13694,10 +16142,19 @@
       <c r="AE17" s="3"/>
       <c r="AF17" s="3"/>
       <c r="AG17" s="3"/>
-    </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3"/>
+      <c r="AI17" s="3"/>
+      <c r="AJ17" s="3"/>
+      <c r="AK17" s="3"/>
+      <c r="AL17" s="3"/>
+      <c r="AM17" s="3"/>
+      <c r="AN17" s="3"/>
+      <c r="AO17" s="3"/>
+      <c r="AP17" s="3"/>
+    </row>
+    <row r="18" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -13731,10 +16188,19 @@
       <c r="AE18" s="3"/>
       <c r="AF18" s="3"/>
       <c r="AG18" s="3"/>
-    </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3"/>
+      <c r="AI18" s="3"/>
+      <c r="AJ18" s="3"/>
+      <c r="AK18" s="3"/>
+      <c r="AL18" s="3"/>
+      <c r="AM18" s="3"/>
+      <c r="AN18" s="3"/>
+      <c r="AO18" s="3"/>
+      <c r="AP18" s="3"/>
+    </row>
+    <row r="19" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -13768,10 +16234,19 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+    </row>
+    <row r="20" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -13805,10 +16280,19 @@
       <c r="AE20" s="3"/>
       <c r="AF20" s="3"/>
       <c r="AG20" s="3"/>
-    </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3"/>
+      <c r="AI20" s="3"/>
+      <c r="AJ20" s="3"/>
+      <c r="AK20" s="3"/>
+      <c r="AL20" s="3"/>
+      <c r="AM20" s="3"/>
+      <c r="AN20" s="3"/>
+      <c r="AO20" s="3"/>
+      <c r="AP20" s="3"/>
+    </row>
+    <row r="21" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -13842,10 +16326,19 @@
       <c r="AE21" s="3"/>
       <c r="AF21" s="3"/>
       <c r="AG21" s="3"/>
-    </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3"/>
+      <c r="AI21" s="3"/>
+      <c r="AJ21" s="3"/>
+      <c r="AK21" s="3"/>
+      <c r="AL21" s="3"/>
+      <c r="AM21" s="3"/>
+      <c r="AN21" s="3"/>
+      <c r="AO21" s="3"/>
+      <c r="AP21" s="3"/>
+    </row>
+    <row r="22" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -13879,10 +16372,19 @@
       <c r="AE22" s="3"/>
       <c r="AF22" s="3"/>
       <c r="AG22" s="3"/>
-    </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3"/>
+      <c r="AI22" s="3"/>
+      <c r="AJ22" s="3"/>
+      <c r="AK22" s="3"/>
+      <c r="AL22" s="3"/>
+      <c r="AM22" s="3"/>
+      <c r="AN22" s="3"/>
+      <c r="AO22" s="3"/>
+      <c r="AP22" s="3"/>
+    </row>
+    <row r="23" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -13916,10 +16418,19 @@
       <c r="AE23" s="3"/>
       <c r="AF23" s="3"/>
       <c r="AG23" s="3"/>
-    </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3"/>
+      <c r="AI23" s="3"/>
+      <c r="AJ23" s="3"/>
+      <c r="AK23" s="3"/>
+      <c r="AL23" s="3"/>
+      <c r="AM23" s="3"/>
+      <c r="AN23" s="3"/>
+      <c r="AO23" s="3"/>
+      <c r="AP23" s="3"/>
+    </row>
+    <row r="24" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -13953,31 +16464,63 @@
       <c r="AE24" s="3"/>
       <c r="AF24" s="3"/>
       <c r="AG24" s="3"/>
-    </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="1"/>
-      <c r="S25" s="1"/>
-      <c r="T25" s="1"/>
-      <c r="U25" s="1"/>
-      <c r="V25" s="1"/>
-      <c r="W25" s="1"/>
-      <c r="X25" s="1"/>
-      <c r="Y25" s="1"/>
-      <c r="Z25" s="1"/>
-      <c r="AA25" s="1"/>
-      <c r="AB25" s="1"/>
-      <c r="AC25" s="1"/>
-      <c r="AD25" s="1"/>
-      <c r="AE25" s="1"/>
-    </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3"/>
+      <c r="AI24" s="3"/>
+      <c r="AJ24" s="3"/>
+      <c r="AK24" s="3"/>
+      <c r="AL24" s="3"/>
+      <c r="AM24" s="3"/>
+      <c r="AN24" s="3"/>
+      <c r="AO24" s="3"/>
+      <c r="AP24" s="3"/>
+    </row>
+    <row r="25" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A25" s="3">
+        <v>15</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="3"/>
+      <c r="V25" s="3"/>
+      <c r="W25" s="3"/>
+      <c r="X25" s="3"/>
+      <c r="Y25" s="3"/>
+      <c r="Z25" s="3"/>
+      <c r="AA25" s="3"/>
+      <c r="AB25" s="3"/>
+      <c r="AC25" s="3"/>
+      <c r="AD25" s="3"/>
+      <c r="AE25" s="3"/>
+      <c r="AF25" s="3"/>
+      <c r="AG25" s="3"/>
+      <c r="AH25" s="3"/>
+      <c r="AI25" s="3"/>
+      <c r="AJ25" s="3"/>
+      <c r="AK25" s="3"/>
+      <c r="AL25" s="3"/>
+      <c r="AM25" s="3"/>
+      <c r="AN25" s="3"/>
+      <c r="AO25" s="3"/>
+      <c r="AP25" s="3"/>
+    </row>
+    <row r="26" spans="1:42" x14ac:dyDescent="0.2">
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -13991,8 +16534,27 @@
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
-    </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="X26" s="1"/>
+      <c r="Y26" s="1"/>
+      <c r="Z26" s="1"/>
+      <c r="AA26" s="1"/>
+      <c r="AB26" s="1"/>
+      <c r="AC26" s="1"/>
+      <c r="AD26" s="1"/>
+      <c r="AE26" s="1"/>
+      <c r="AF26" s="1"/>
+      <c r="AG26" s="1"/>
+      <c r="AH26" s="1"/>
+      <c r="AI26" s="1"/>
+      <c r="AJ26" s="1"/>
+      <c r="AK26" s="1"/>
+      <c r="AL26" s="1"/>
+      <c r="AM26" s="1"/>
+      <c r="AN26" s="1"/>
+      <c r="AO26" s="1"/>
+      <c r="AP26" s="1"/>
+    </row>
+    <row r="27" spans="1:42" x14ac:dyDescent="0.2">
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -14006,8 +16568,17 @@
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
-    </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="X27" s="1"/>
+      <c r="Y27" s="1"/>
+      <c r="Z27" s="1"/>
+      <c r="AA27" s="1"/>
+      <c r="AB27" s="1"/>
+      <c r="AC27" s="1"/>
+      <c r="AD27" s="1"/>
+      <c r="AE27" s="1"/>
+      <c r="AF27" s="1"/>
+    </row>
+    <row r="28" spans="1:42" x14ac:dyDescent="0.2">
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -14021,8 +16592,17 @@
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
-    </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="X28" s="1"/>
+      <c r="Y28" s="1"/>
+      <c r="Z28" s="1"/>
+      <c r="AA28" s="1"/>
+      <c r="AB28" s="1"/>
+      <c r="AC28" s="1"/>
+      <c r="AD28" s="1"/>
+      <c r="AE28" s="1"/>
+      <c r="AF28" s="1"/>
+    </row>
+    <row r="29" spans="1:42" x14ac:dyDescent="0.2">
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -14036,8 +16616,17 @@
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
-    </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="X29" s="1"/>
+      <c r="Y29" s="1"/>
+      <c r="Z29" s="1"/>
+      <c r="AA29" s="1"/>
+      <c r="AB29" s="1"/>
+      <c r="AC29" s="1"/>
+      <c r="AD29" s="1"/>
+      <c r="AE29" s="1"/>
+      <c r="AF29" s="1"/>
+    </row>
+    <row r="30" spans="1:42" x14ac:dyDescent="0.2">
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -14051,8 +16640,17 @@
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
-    </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="X30" s="1"/>
+      <c r="Y30" s="1"/>
+      <c r="Z30" s="1"/>
+      <c r="AA30" s="1"/>
+      <c r="AB30" s="1"/>
+      <c r="AC30" s="1"/>
+      <c r="AD30" s="1"/>
+      <c r="AE30" s="1"/>
+      <c r="AF30" s="1"/>
+    </row>
+    <row r="31" spans="1:42" x14ac:dyDescent="0.2">
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -14066,8 +16664,17 @@
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
-    </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="X31" s="1"/>
+      <c r="Y31" s="1"/>
+      <c r="Z31" s="1"/>
+      <c r="AA31" s="1"/>
+      <c r="AB31" s="1"/>
+      <c r="AC31" s="1"/>
+      <c r="AD31" s="1"/>
+      <c r="AE31" s="1"/>
+      <c r="AF31" s="1"/>
+    </row>
+    <row r="32" spans="1:42" x14ac:dyDescent="0.2">
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -14081,8 +16688,17 @@
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
-    </row>
-    <row r="33" spans="11:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="1"/>
+      <c r="Y32" s="1"/>
+      <c r="Z32" s="1"/>
+      <c r="AA32" s="1"/>
+      <c r="AB32" s="1"/>
+      <c r="AC32" s="1"/>
+      <c r="AD32" s="1"/>
+      <c r="AE32" s="1"/>
+      <c r="AF32" s="1"/>
+    </row>
+    <row r="33" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -14096,8 +16712,17 @@
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
       <c r="W33" s="1"/>
-    </row>
-    <row r="34" spans="11:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="1"/>
+      <c r="Y33" s="1"/>
+      <c r="Z33" s="1"/>
+      <c r="AA33" s="1"/>
+      <c r="AB33" s="1"/>
+      <c r="AC33" s="1"/>
+      <c r="AD33" s="1"/>
+      <c r="AE33" s="1"/>
+      <c r="AF33" s="1"/>
+    </row>
+    <row r="34" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -14111,8 +16736,17 @@
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
-    </row>
-    <row r="35" spans="11:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="1"/>
+      <c r="Y34" s="1"/>
+      <c r="Z34" s="1"/>
+      <c r="AA34" s="1"/>
+      <c r="AB34" s="1"/>
+      <c r="AC34" s="1"/>
+      <c r="AD34" s="1"/>
+      <c r="AE34" s="1"/>
+      <c r="AF34" s="1"/>
+    </row>
+    <row r="35" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -14126,8 +16760,17 @@
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
-    </row>
-    <row r="36" spans="11:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="1"/>
+      <c r="Y35" s="1"/>
+      <c r="Z35" s="1"/>
+      <c r="AA35" s="1"/>
+      <c r="AB35" s="1"/>
+      <c r="AC35" s="1"/>
+      <c r="AD35" s="1"/>
+      <c r="AE35" s="1"/>
+      <c r="AF35" s="1"/>
+    </row>
+    <row r="36" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
@@ -14141,8 +16784,17 @@
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
       <c r="W36" s="1"/>
-    </row>
-    <row r="37" spans="11:23" x14ac:dyDescent="0.2">
+      <c r="X36" s="1"/>
+      <c r="Y36" s="1"/>
+      <c r="Z36" s="1"/>
+      <c r="AA36" s="1"/>
+      <c r="AB36" s="1"/>
+      <c r="AC36" s="1"/>
+      <c r="AD36" s="1"/>
+      <c r="AE36" s="1"/>
+      <c r="AF36" s="1"/>
+    </row>
+    <row r="37" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
@@ -14156,8 +16808,17 @@
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
       <c r="W37" s="1"/>
-    </row>
-    <row r="38" spans="11:23" x14ac:dyDescent="0.2">
+      <c r="X37" s="1"/>
+      <c r="Y37" s="1"/>
+      <c r="Z37" s="1"/>
+      <c r="AA37" s="1"/>
+      <c r="AB37" s="1"/>
+      <c r="AC37" s="1"/>
+      <c r="AD37" s="1"/>
+      <c r="AE37" s="1"/>
+      <c r="AF37" s="1"/>
+    </row>
+    <row r="38" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -14171,8 +16832,17 @@
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
       <c r="W38" s="1"/>
-    </row>
-    <row r="39" spans="11:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="1"/>
+      <c r="Y38" s="1"/>
+      <c r="Z38" s="1"/>
+      <c r="AA38" s="1"/>
+      <c r="AB38" s="1"/>
+      <c r="AC38" s="1"/>
+      <c r="AD38" s="1"/>
+      <c r="AE38" s="1"/>
+      <c r="AF38" s="1"/>
+    </row>
+    <row r="39" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -14186,8 +16856,17 @@
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
-    </row>
-    <row r="40" spans="11:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="1"/>
+      <c r="Y39" s="1"/>
+      <c r="Z39" s="1"/>
+      <c r="AA39" s="1"/>
+      <c r="AB39" s="1"/>
+      <c r="AC39" s="1"/>
+      <c r="AD39" s="1"/>
+      <c r="AE39" s="1"/>
+      <c r="AF39" s="1"/>
+    </row>
+    <row r="40" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -14201,8 +16880,17 @@
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1"/>
-    </row>
-    <row r="41" spans="11:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="1"/>
+      <c r="Y40" s="1"/>
+      <c r="Z40" s="1"/>
+      <c r="AA40" s="1"/>
+      <c r="AB40" s="1"/>
+      <c r="AC40" s="1"/>
+      <c r="AD40" s="1"/>
+      <c r="AE40" s="1"/>
+      <c r="AF40" s="1"/>
+    </row>
+    <row r="41" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
@@ -14216,8 +16904,17 @@
       <c r="U41" s="1"/>
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
-    </row>
-    <row r="42" spans="11:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="1"/>
+      <c r="Y41" s="1"/>
+      <c r="Z41" s="1"/>
+      <c r="AA41" s="1"/>
+      <c r="AB41" s="1"/>
+      <c r="AC41" s="1"/>
+      <c r="AD41" s="1"/>
+      <c r="AE41" s="1"/>
+      <c r="AF41" s="1"/>
+    </row>
+    <row r="42" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
@@ -14231,8 +16928,17 @@
       <c r="U42" s="1"/>
       <c r="V42" s="1"/>
       <c r="W42" s="1"/>
-    </row>
-    <row r="43" spans="11:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="1"/>
+      <c r="Y42" s="1"/>
+      <c r="Z42" s="1"/>
+      <c r="AA42" s="1"/>
+      <c r="AB42" s="1"/>
+      <c r="AC42" s="1"/>
+      <c r="AD42" s="1"/>
+      <c r="AE42" s="1"/>
+      <c r="AF42" s="1"/>
+    </row>
+    <row r="43" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -14246,8 +16952,17 @@
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
       <c r="W43" s="1"/>
-    </row>
-    <row r="44" spans="11:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="1"/>
+      <c r="Y43" s="1"/>
+      <c r="Z43" s="1"/>
+      <c r="AA43" s="1"/>
+      <c r="AB43" s="1"/>
+      <c r="AC43" s="1"/>
+      <c r="AD43" s="1"/>
+      <c r="AE43" s="1"/>
+      <c r="AF43" s="1"/>
+    </row>
+    <row r="44" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
@@ -14261,8 +16976,17 @@
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
       <c r="W44" s="1"/>
-    </row>
-    <row r="45" spans="11:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="1"/>
+      <c r="Y44" s="1"/>
+      <c r="Z44" s="1"/>
+      <c r="AA44" s="1"/>
+      <c r="AB44" s="1"/>
+      <c r="AC44" s="1"/>
+      <c r="AD44" s="1"/>
+      <c r="AE44" s="1"/>
+      <c r="AF44" s="1"/>
+    </row>
+    <row r="45" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
@@ -14276,8 +17000,17 @@
       <c r="U45" s="1"/>
       <c r="V45" s="1"/>
       <c r="W45" s="1"/>
-    </row>
-    <row r="46" spans="11:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="1"/>
+      <c r="Y45" s="1"/>
+      <c r="Z45" s="1"/>
+      <c r="AA45" s="1"/>
+      <c r="AB45" s="1"/>
+      <c r="AC45" s="1"/>
+      <c r="AD45" s="1"/>
+      <c r="AE45" s="1"/>
+      <c r="AF45" s="1"/>
+    </row>
+    <row r="46" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
@@ -14291,8 +17024,17 @@
       <c r="U46" s="1"/>
       <c r="V46" s="1"/>
       <c r="W46" s="1"/>
-    </row>
-    <row r="47" spans="11:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="1"/>
+      <c r="Y46" s="1"/>
+      <c r="Z46" s="1"/>
+      <c r="AA46" s="1"/>
+      <c r="AB46" s="1"/>
+      <c r="AC46" s="1"/>
+      <c r="AD46" s="1"/>
+      <c r="AE46" s="1"/>
+      <c r="AF46" s="1"/>
+    </row>
+    <row r="47" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
@@ -14306,8 +17048,17 @@
       <c r="U47" s="1"/>
       <c r="V47" s="1"/>
       <c r="W47" s="1"/>
-    </row>
-    <row r="48" spans="11:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="1"/>
+      <c r="Y47" s="1"/>
+      <c r="Z47" s="1"/>
+      <c r="AA47" s="1"/>
+      <c r="AB47" s="1"/>
+      <c r="AC47" s="1"/>
+      <c r="AD47" s="1"/>
+      <c r="AE47" s="1"/>
+      <c r="AF47" s="1"/>
+    </row>
+    <row r="48" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
@@ -14321,8 +17072,17 @@
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
       <c r="W48" s="1"/>
-    </row>
-    <row r="49" spans="11:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="1"/>
+      <c r="Y48" s="1"/>
+      <c r="Z48" s="1"/>
+      <c r="AA48" s="1"/>
+      <c r="AB48" s="1"/>
+      <c r="AC48" s="1"/>
+      <c r="AD48" s="1"/>
+      <c r="AE48" s="1"/>
+      <c r="AF48" s="1"/>
+    </row>
+    <row r="49" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
@@ -14336,8 +17096,17 @@
       <c r="U49" s="1"/>
       <c r="V49" s="1"/>
       <c r="W49" s="1"/>
-    </row>
-    <row r="50" spans="11:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="1"/>
+      <c r="Y49" s="1"/>
+      <c r="Z49" s="1"/>
+      <c r="AA49" s="1"/>
+      <c r="AB49" s="1"/>
+      <c r="AC49" s="1"/>
+      <c r="AD49" s="1"/>
+      <c r="AE49" s="1"/>
+      <c r="AF49" s="1"/>
+    </row>
+    <row r="50" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
@@ -14351,8 +17120,17 @@
       <c r="U50" s="1"/>
       <c r="V50" s="1"/>
       <c r="W50" s="1"/>
-    </row>
-    <row r="51" spans="11:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="1"/>
+      <c r="Y50" s="1"/>
+      <c r="Z50" s="1"/>
+      <c r="AA50" s="1"/>
+      <c r="AB50" s="1"/>
+      <c r="AC50" s="1"/>
+      <c r="AD50" s="1"/>
+      <c r="AE50" s="1"/>
+      <c r="AF50" s="1"/>
+    </row>
+    <row r="51" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
@@ -14366,83 +17144,141 @@
       <c r="U51" s="1"/>
       <c r="V51" s="1"/>
       <c r="W51" s="1"/>
+      <c r="X51" s="1"/>
+      <c r="Y51" s="1"/>
+      <c r="Z51" s="1"/>
+      <c r="AA51" s="1"/>
+      <c r="AB51" s="1"/>
+      <c r="AC51" s="1"/>
+      <c r="AD51" s="1"/>
+      <c r="AE51" s="1"/>
+      <c r="AF51" s="1"/>
+    </row>
+    <row r="52" spans="11:32" x14ac:dyDescent="0.2">
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1"/>
+      <c r="N52" s="1"/>
+      <c r="O52" s="1"/>
+      <c r="P52" s="1"/>
+      <c r="Q52" s="1"/>
+      <c r="R52" s="1"/>
+      <c r="S52" s="1"/>
+      <c r="T52" s="1"/>
+      <c r="U52" s="1"/>
+      <c r="V52" s="1"/>
+      <c r="W52" s="1"/>
+      <c r="X52" s="1"/>
+      <c r="Y52" s="1"/>
+      <c r="Z52" s="1"/>
+      <c r="AA52" s="1"/>
+      <c r="AB52" s="1"/>
+      <c r="AC52" s="1"/>
+      <c r="AD52" s="1"/>
+      <c r="AE52" s="1"/>
+      <c r="AF52" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="C8:O8"/>
-    <mergeCell ref="R8:W8"/>
-    <mergeCell ref="AF8:AG8"/>
-    <mergeCell ref="X8:AE8"/>
+  <mergeCells count="3">
+    <mergeCell ref="AA9:AF9"/>
+    <mergeCell ref="C9:Z9"/>
+    <mergeCell ref="AG9:AP9"/>
   </mergeCells>
-  <conditionalFormatting sqref="F10:I51">
-    <cfRule type="expression" dxfId="14" priority="16">
-      <formula>$E10="pow"</formula>
+  <conditionalFormatting sqref="F11:K52 AB11:AF52">
+    <cfRule type="expression" dxfId="20" priority="6">
+      <formula>$E11="hb"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="7">
+      <formula>$E11="pow"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G10:G51">
-    <cfRule type="expression" dxfId="13" priority="5">
-      <formula>$E10="cp"</formula>
+  <conditionalFormatting sqref="F11:L52">
+    <cfRule type="expression" dxfId="18" priority="19">
+      <formula>$E11="elastic"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H10:I51">
-    <cfRule type="expression" dxfId="12" priority="4">
-      <formula>$E10="mc"</formula>
+  <conditionalFormatting sqref="G11:G52">
+    <cfRule type="expression" dxfId="17" priority="8">
+      <formula>$E11="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J10:K51">
-    <cfRule type="expression" dxfId="11" priority="6">
-      <formula>$E10="cp"</formula>
+  <conditionalFormatting sqref="H11:I52">
+    <cfRule type="expression" dxfId="16" priority="9">
+      <formula>$E11="mc"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L10:O51">
-    <cfRule type="expression" dxfId="10" priority="19">
-      <formula>AND($E10&lt;&gt;"",$E10&lt;&gt;"pow")</formula>
+  <conditionalFormatting sqref="J11:K52">
+    <cfRule type="expression" dxfId="15" priority="10">
+      <formula>$E11="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q10:Q51">
-    <cfRule type="expression" dxfId="9" priority="20">
-      <formula>AND($P10&lt;&gt;"",$P10&lt;&gt;"ru")</formula>
+  <conditionalFormatting sqref="O11:R52">
+    <cfRule type="expression" dxfId="14" priority="4">
+      <formula>$E11="elastic"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S10:U51">
-    <cfRule type="expression" dxfId="8" priority="21">
-      <formula>$E10="pow"</formula>
+  <conditionalFormatting sqref="P11:P52">
+    <cfRule type="expression" dxfId="13" priority="13">
+      <formula>AND($O11&lt;&gt;"",$O11&lt;&gt;"ru")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T10:T51">
-    <cfRule type="expression" dxfId="7" priority="8">
-      <formula>$E10="cp"</formula>
+  <conditionalFormatting sqref="Q11:R52">
+    <cfRule type="expression" dxfId="12" priority="3">
+      <formula>$E11="cp"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="5">
+      <formula>AND($O11&lt;&gt;"",$O11&lt;&gt;"piezo",$O11&lt;&gt;"seep")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U10:U51">
-    <cfRule type="expression" dxfId="6" priority="15">
-      <formula>$E10="mc"</formula>
+  <conditionalFormatting sqref="S11:V52">
+    <cfRule type="expression" dxfId="10" priority="11">
+      <formula>AND($E11&lt;&gt;"",$E11&lt;&gt;"pow")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V10:W51">
-    <cfRule type="expression" dxfId="5" priority="10">
-      <formula>$E10="cp"</formula>
+  <conditionalFormatting sqref="W11:Z52">
+    <cfRule type="expression" dxfId="9" priority="12">
+      <formula>AND($E11&lt;&gt;"",$E11&lt;&gt;"hb")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB10:AC101">
-    <cfRule type="expression" dxfId="4" priority="2">
-      <formula>$AA10="vg"</formula>
+  <conditionalFormatting sqref="AB11:AF52">
+    <cfRule type="expression" dxfId="8" priority="21">
+      <formula>$E11="elastic"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD10:AE101">
+  <conditionalFormatting sqref="AC11:AC52">
+    <cfRule type="expression" dxfId="7" priority="14">
+      <formula>$E11="cp"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD11:AD52">
+    <cfRule type="expression" dxfId="6" priority="15">
+      <formula>$E11="mc"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE11:AF52">
+    <cfRule type="expression" dxfId="5" priority="16">
+      <formula>$E11="cp"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK11:AL52">
+    <cfRule type="expression" dxfId="4" priority="17">
+      <formula>OR($AJ11="vg",$AJ11="gard")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AM11:AN52">
     <cfRule type="expression" dxfId="3" priority="1">
-      <formula>$AA10="lf"</formula>
+      <formula>$AJ11="lf"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10:E51" xr:uid="{374AFD2C-B540-DD4B-A245-8B781F76E64C}">
-      <formula1>$C$3:$C$5</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E11:E52" xr:uid="{374AFD2C-B540-DD4B-A245-8B781F76E64C}">
+      <formula1>$C$3:$C$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P10:P51" xr:uid="{D770415C-1ECE-F44B-9D8C-08EF1CF31C8E}">
-      <formula1>$K$3:$K$6</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ11:AJ102" xr:uid="{E00A94A9-D864-5843-8FBD-E84775B1C100}">
+      <formula1>$AJ$3:$AJ$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA10:AA101" xr:uid="{E00A94A9-D864-5843-8FBD-E84775B1C100}">
-      <formula1>$AA$3:$AA$4</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O11:O52" xr:uid="{D770415C-1ECE-F44B-9D8C-08EF1CF31C8E}">
+      <formula1>$O$3:$O$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14482,8 +17318,8 @@
       <c r="B2" s="3">
         <v>20.0</v>
       </c>
-      <c r="D2" s="27" t="s">
-        <v>93</v>
+      <c r="D2" s="24" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
@@ -14534,127 +17370,127 @@
       </c>
       <c r="AC4" s="55"/>
       <c r="AE4" s="55" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AF4" s="55"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AI4" s="55"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="AL4" s="55"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="AO4" s="55"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="AR4" s="55"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A5" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="B5" s="42">
+      <c r="A5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" s="37">
         <v>1</v>
       </c>
-      <c r="D5" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="E5" s="42">
+      <c r="D5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="E5" s="37">
         <v>2</v>
       </c>
-      <c r="G5" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="H5" s="42">
+      <c r="G5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="H5" s="37">
         <v>3</v>
       </c>
-      <c r="J5" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="K5" s="42">
+      <c r="J5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="K5" s="37">
         <v>4</v>
       </c>
-      <c r="M5" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="N5" s="42">
+      <c r="M5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="N5" s="37">
         <v>5</v>
       </c>
-      <c r="P5" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q5" s="42">
+      <c r="P5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q5" s="37">
         <v>6</v>
       </c>
       <c r="R5" s="1"/>
-      <c r="S5" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="T5" s="42">
+      <c r="S5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="T5" s="37">
         <v>7</v>
       </c>
       <c r="U5" s="1"/>
-      <c r="V5" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="W5" s="42">
+      <c r="V5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="W5" s="37">
         <v>8</v>
       </c>
       <c r="X5" s="1"/>
-      <c r="Y5" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z5" s="42">
+      <c r="Y5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z5" s="37">
         <v>9</v>
       </c>
       <c r="AA5" s="1"/>
-      <c r="AB5" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="AC5" s="42">
+      <c r="AB5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="AC5" s="37">
         <v>10</v>
       </c>
-      <c r="AE5" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="AF5" s="42">
+      <c r="AE5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF5" s="37">
         <v>11</v>
       </c>
       <c r="AG5" s="1"/>
-      <c r="AH5" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="AI5" s="42">
+      <c r="AH5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="AI5" s="37">
         <v>12</v>
       </c>
       <c r="AJ5" s="1"/>
-      <c r="AK5" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="AL5" s="42">
+      <c r="AK5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="AL5" s="37">
         <v>13</v>
       </c>
       <c r="AM5" s="1"/>
-      <c r="AN5" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="AO5" s="42">
+      <c r="AN5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="AO5" s="37">
         <v>14</v>
       </c>
       <c r="AP5" s="1"/>
-      <c r="AQ5" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="AR5" s="42">
+      <c r="AQ5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="AR5" s="37">
         <v>15</v>
       </c>
     </row>
@@ -15723,177 +18559,177 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
-        <v>169</v>
+      <c r="A2" s="24" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A4" s="55" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="B4" s="55"/>
       <c r="D4" s="55" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="E4" s="55"/>
       <c r="G4" s="55" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="H4" s="55"/>
       <c r="J4" s="55" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="K4" s="55"/>
       <c r="M4" s="55" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="N4" s="55"/>
       <c r="P4" s="55" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="Q4" s="55"/>
       <c r="R4" s="1"/>
       <c r="S4" s="55" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="T4" s="55"/>
       <c r="U4" s="1"/>
       <c r="V4" s="55" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="W4" s="55"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="55" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="Z4" s="55"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="55" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="AC4" s="55"/>
       <c r="AE4" s="55" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="AF4" s="55"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="AI4" s="55"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="AL4" s="55"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="AO4" s="55"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="AR4" s="55"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A5" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="B5" s="44">
+      <c r="A5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" s="39">
         <v>1</v>
       </c>
-      <c r="D5" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="E5" s="44">
+      <c r="D5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="E5" s="39">
         <v>2</v>
       </c>
-      <c r="G5" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="H5" s="44">
+      <c r="G5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="H5" s="39">
         <v>3</v>
       </c>
-      <c r="J5" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="K5" s="44">
+      <c r="J5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="K5" s="39">
         <v>4</v>
       </c>
-      <c r="M5" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="N5" s="44">
+      <c r="M5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="N5" s="39">
         <v>5</v>
       </c>
-      <c r="P5" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q5" s="44">
+      <c r="P5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q5" s="39">
         <v>6</v>
       </c>
       <c r="R5" s="1"/>
-      <c r="S5" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="T5" s="44">
+      <c r="S5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="T5" s="39">
         <v>7</v>
       </c>
       <c r="U5" s="1"/>
-      <c r="V5" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="W5" s="44">
+      <c r="V5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="W5" s="39">
         <v>8</v>
       </c>
       <c r="X5" s="1"/>
-      <c r="Y5" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z5" s="44">
+      <c r="Y5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z5" s="39">
         <v>9</v>
       </c>
       <c r="AA5" s="1"/>
-      <c r="AB5" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="AC5" s="44">
+      <c r="AB5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="AC5" s="39">
         <v>10</v>
       </c>
-      <c r="AE5" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="AF5" s="44">
+      <c r="AE5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF5" s="39">
         <v>11</v>
       </c>
       <c r="AG5" s="1"/>
-      <c r="AH5" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="AI5" s="44">
+      <c r="AH5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="AI5" s="39">
         <v>12</v>
       </c>
       <c r="AJ5" s="1"/>
-      <c r="AK5" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="AL5" s="44">
+      <c r="AK5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="AL5" s="39">
         <v>13</v>
       </c>
       <c r="AM5" s="1"/>
-      <c r="AN5" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="AO5" s="44">
+      <c r="AN5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="AO5" s="39">
         <v>14</v>
       </c>
       <c r="AP5" s="1"/>
-      <c r="AQ5" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="AR5" s="44">
+      <c r="AQ5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="AR5" s="39">
         <v>15</v>
       </c>
     </row>
@@ -16930,35 +19766,35 @@
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="58" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B2" s="58"/>
       <c r="D2" s="59" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" s="59"/>
+      <c r="G2" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="E2" s="59"/>
-      <c r="G2" s="24" t="s">
-        <v>83</v>
-      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="37" t="s">
-        <v>212</v>
-      </c>
-      <c r="B3" s="38" t="inlineStr">
+      <c r="A3" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="33" t="inlineStr">
         <is>
           <t>piezo</t>
         </is>
       </c>
-      <c r="D3" s="39" t="s">
-        <v>212</v>
-      </c>
-      <c r="E3" s="40" t="inlineStr">
+      <c r="D3" s="34" t="s">
+        <v>196</v>
+      </c>
+      <c r="E3" s="35" t="inlineStr">
         <is>
           <t>piezo</t>
         </is>
       </c>
-      <c r="G3" s="24"/>
+      <c r="G3" s="22"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
@@ -16974,7 +19810,7 @@
         <v>4</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="H4" s="1"/>
     </row>
@@ -16987,7 +19823,7 @@
         <v>21</v>
       </c>
       <c r="H5" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -16996,10 +19832,10 @@
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="G6" s="1" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="H6" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -17139,10 +19975,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="13" t="s">
         <v>61</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>62</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>29</v>
@@ -17157,7 +19993,7 @@
         <v>28</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>30</v>
@@ -17234,10 +20070,10 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="J5" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -17409,10 +20245,10 @@
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="E5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F5" t="s">
         <v>76</v>
-      </c>
-      <c r="F5" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -17536,32 +20372,32 @@
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B2" s="60" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C2" s="60"/>
       <c r="D2" s="60"/>
       <c r="F2" s="60" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G2" s="60"/>
       <c r="H2" s="60"/>
       <c r="J2" s="60" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K2" s="60"/>
       <c r="L2" s="60"/>
       <c r="N2" s="60" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="O2" s="60"/>
       <c r="P2" s="60"/>
       <c r="R2" s="60" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="S2" s="60"/>
       <c r="T2" s="60"/>
       <c r="V2" s="60" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="W2" s="60"/>
       <c r="X2" s="60"/>

--- a/docs/lem/files/xslope_acads_simple.xlsx
+++ b/docs/lem/files/xslope_acads_simple.xlsx
@@ -11702,7 +11702,7 @@
         <v>49</v>
       </c>
       <c r="D11" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>227</v>
@@ -11716,7 +11716,7 @@
         <v>48</v>
       </c>
       <c r="D12" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>21</v>
@@ -11730,7 +11730,7 @@
         <v>74</v>
       </c>
       <c r="D13" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>23</v>
@@ -15774,61 +15774,35 @@
       <c r="G11" s="3">
         <v>19.6</v>
       </c>
-      <c r="H11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K11" s="3">
-        <v>0.0</v>
-      </c>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
       <c r="L11" s="3">
         <v>3.0</v>
       </c>
       <c r="M11" s="3">
-        <v>100000.0</v>
+        <v>50000.0</v>
       </c>
       <c r="N11" s="3">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="P11" s="3">
-        <v>0.0</v>
-      </c>
+      <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-      <c r="S11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="T11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="U11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="V11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="W11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="X11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Y11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Z11" s="3">
-        <v>0.0</v>
-      </c>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
       <c r="AA11" s="3">
         <v>1.2</v>
       </c>
@@ -15838,41 +15812,17 @@
       <c r="AC11" s="3">
         <v>2.744</v>
       </c>
-      <c r="AD11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AE11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AF11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AG11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AH11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AI11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AJ11" s="3" t="inlineStr">
-        <is>
-          <t>lf</t>
-        </is>
-      </c>
-      <c r="AK11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AL11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AM11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AN11" s="3">
-        <v>0.0</v>
-      </c>
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
     </row>
@@ -17316,17 +17266,15 @@
         <v>46</v>
       </c>
       <c r="B2" s="3">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="D2" s="24" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="55" t="inlineStr">
-        <is>
-          <t>Profile Line #1</t>
-        </is>
+      <c r="A4" s="55" t="s">
+        <v>2</v>
       </c>
       <c r="B4" s="55"/>
       <c r="D4" s="55" t="s">
@@ -17681,10 +17629,10 @@
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B8" s="3">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -17725,10 +17673,10 @@
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="B9" s="3">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -17769,10 +17717,10 @@
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="B10" s="3">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -17813,10 +17761,10 @@
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="B11" s="3">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -19781,19 +19729,11 @@
       <c r="A3" s="32" t="s">
         <v>196</v>
       </c>
-      <c r="B3" s="33" t="inlineStr">
-        <is>
-          <t>piezo</t>
-        </is>
-      </c>
+      <c r="B3" s="33"/>
       <c r="D3" s="34" t="s">
         <v>196</v>
       </c>
-      <c r="E3" s="35" t="inlineStr">
-        <is>
-          <t>piezo</t>
-        </is>
-      </c>
+      <c r="E3" s="35"/>
       <c r="G3" s="22"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -20007,21 +19947,23 @@
         <v>1</v>
       </c>
       <c r="B3" s="3">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="C3" s="3">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Depth</t>
+          <t>Intercept</t>
         </is>
       </c>
-      <c r="E3" s="3">
-        <v>22.639320225</v>
-      </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3">
+        <v>30</v>
+      </c>
+      <c r="G3" s="3">
+        <v>25</v>
+      </c>
       <c r="H3" s="3"/>
       <c r="J3" s="1" t="s">
         <v>26</v>
@@ -20035,10 +19977,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="3">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -20046,7 +19988,7 @@
         </is>
       </c>
       <c r="E4" s="3">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>

--- a/docs/lem/files/xslope_acads_simple.xlsx
+++ b/docs/lem/files/xslope_acads_simple.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="318">
   <si>
     <t>XSLOPE Input Template</t>
   </si>
@@ -992,6 +992,167 @@
   </si>
   <si>
     <t>auto</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>g</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(c)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(c/p)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(d)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>s(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>psi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>g</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>sat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>q</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>p</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -3243,7 +3404,7 @@
         <v>270</v>
       </c>
       <c r="H2" s="40" t="s">
-        <v>271</v>
+        <v>317</v>
       </c>
       <c r="I2" s="40" t="s">
         <v>253</v>
@@ -5722,7 +5883,7 @@
         <v>111</v>
       </c>
       <c r="D10" s="48" t="s">
-        <v>112</v>
+        <v>316</v>
       </c>
       <c r="E10" s="44" t="s">
         <v>113</v>
@@ -5791,22 +5952,22 @@
         <v>133</v>
       </c>
       <c r="AA10" s="46" t="s">
-        <v>134</v>
+        <v>311</v>
       </c>
       <c r="AB10" s="46" t="s">
-        <v>135</v>
+        <v>312</v>
       </c>
       <c r="AC10" s="47" t="s">
         <v>136</v>
       </c>
       <c r="AD10" s="46" t="s">
-        <v>137</v>
+        <v>313</v>
       </c>
       <c r="AE10" s="46" t="s">
-        <v>138</v>
+        <v>314</v>
       </c>
       <c r="AF10" s="47" t="s">
-        <v>139</v>
+        <v>315</v>
       </c>
       <c r="AG10" s="23" t="s">
         <v>140</v>

--- a/docs/lem/files/xslope_acads_simple.xlsx
+++ b/docs/lem/files/xslope_acads_simple.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11708D50-B4AE-4447-916E-877A7873BC20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{523500CF-89B8-4644-B955-31C74218CF4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="33220" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="4320" windowWidth="46940" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -223,6 +223,12 @@
     <t>Water loads:</t>
   </si>
   <si>
+    <t>auto</t>
+  </si>
+  <si>
+    <t>Surface family:</t>
+  </si>
+  <si>
     <t>Unit Options:</t>
   </si>
   <si>
@@ -397,9 +403,6 @@
     <t>g</t>
   </si>
   <si>
-    <t>gsat</t>
-  </si>
-  <si>
     <t>option</t>
   </si>
   <si>
@@ -463,24 +466,9 @@
     <t>hb_d</t>
   </si>
   <si>
-    <t>s(g)</t>
-  </si>
-  <si>
-    <t>s(c)</t>
-  </si>
-  <si>
     <t>s(f)</t>
   </si>
   <si>
-    <t>s(c/p)</t>
-  </si>
-  <si>
-    <t>s(d)</t>
-  </si>
-  <si>
-    <t>s(psi)</t>
-  </si>
-  <si>
     <t>k1</t>
   </si>
   <si>
@@ -874,9 +862,6 @@
     <t>H</t>
   </si>
   <si>
-    <t>qp</t>
-  </si>
-  <si>
     <t>D</t>
   </si>
   <si>
@@ -892,9 +877,6 @@
     <t>I</t>
   </si>
   <si>
-    <t>Fixity</t>
-  </si>
-  <si>
     <t>P</t>
   </si>
   <si>
@@ -991,7 +973,24 @@
     <t>save_times</t>
   </si>
   <si>
-    <t>auto</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(c)</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1048,26 +1047,6 @@
         <rFont val="Aptos Narrow"/>
         <scheme val="minor"/>
       </rPr>
-      <t>(c)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="0"/>
-        <rFont val="Symbol"/>
-        <charset val="2"/>
-      </rPr>
-      <t>s</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="0"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>(c/p)</t>
     </r>
   </si>
@@ -1133,26 +1112,28 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <rFont val="Symbol"/>
-        <charset val="2"/>
-      </rPr>
-      <t>q</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>p</t>
-    </r>
+    <t>yr</t>
+  </si>
+  <si>
+    <t>Adhesion</t>
+  </si>
+  <si>
+    <t>Delta</t>
+  </si>
+  <si>
+    <t>1D element size:</t>
+  </si>
+  <si>
+    <t>Head</t>
+  </si>
+  <si>
+    <t>Tip</t>
+  </si>
+  <si>
+    <t>Pinned</t>
+  </si>
+  <si>
+    <t>Unrotated</t>
   </si>
 </sst>
 </file>
@@ -1919,6 +1900,645 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>217714</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>54430</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>90714</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B0FB8E9-E4E3-974A-BE46-8E599C58A56D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16455571" y="254001"/>
+          <a:ext cx="3855358" cy="4027713"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Label</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = name used in error messages, summaries, and plots</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>(x1, y1), (x2, y2) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t>= start and end of reinforcement line</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="1"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Type</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = support preset, fills Dir and Appl: Geosynthetic (Tangent, Active), Nail (Axial, Passive), Tieback (Axial, Active), Anchor (Axial, Active)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Dir</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = force direction at the slip surface (LEM only): Tangent = reorients along slip surface (flexible); Axial = along the reinforcement line (rigid). Set by Type; overtype to override.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Appl</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = force application (LEM only): Active = allowable force, not divided by FS (default). Passive = ultimate force, divided by FS. Set by Type; overtype to override.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Tmax</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = tensile capacity (force/length; or force per element if Spacing is given)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Lp1, Lp2 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t>= pullout length at end 1 / end 2 (0 = fully anchored)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Adhesion</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = soii-reinforcement interface adhesion (blank</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" baseline="0"/>
+            <a:t> = use Lp)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>Delta</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" baseline="0"/>
+            <a:t> = soil-reinforcement interface friction angle (blank = use Lp)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Tend1, Tend2 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t>= anchorage/plate/connection capacity at end 1 / end 2 (0 = friction only)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Spacing</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = out-of-plane spacing for discrete supports (nails, tiebacks); blank or 1 for geosynthetics</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Tres</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = residual capacity after rupture (FEM only)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>E</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = modulus of elasticity of reinforcement (FEM only)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Area</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = cross-sectional area of reinforcement (FEM only)</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+          </a:br>
+          <a:endParaRPr lang="en-US" sz="1100" b="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>290286</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>126999</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>553358</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>54428</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6B716B0-439A-6440-8742-7BC140EF924C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14205857" y="126999"/>
+          <a:ext cx="3156858" cy="2521858"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>(x1,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t> y1), (x2, y2) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>= top and bottom of pile</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>H</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> = Pile force magnitude (kN/m or lb/ft). </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>appl</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = force application (LEM only): Active = allowable force, not divided by FS (default). Passive = ultimate force, divided by FS.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>D</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t> = </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Pile diameter</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> (ft or m)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>S</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t> = center to center pile spacing</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> (ft or m)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Vcap</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = Shear</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> capacity of pile (force)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Mcap</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = Moment capacity of pile (force x length)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>E</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> = Young's modulus of pile material (force/lengh^2)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>I </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>= </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Moment of inertia (length^4)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>Area</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> = </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Cross-sectional area (length^2)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Head</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = Pile head fixity status</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Tip</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = Pile tip fixity status</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2236,7 +2856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.6640625" customWidth="1"/>
@@ -2261,7 +2881,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="30">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -2325,7 +2945,7 @@
         <v>17</v>
       </c>
       <c r="D11" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>18</v>
@@ -2339,7 +2959,7 @@
         <v>20</v>
       </c>
       <c r="D12" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>21</v>
@@ -2353,7 +2973,7 @@
         <v>23</v>
       </c>
       <c r="D13" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>24</v>
@@ -2396,7 +3016,9 @@
       <c r="G16" t="s">
         <v>34</v>
       </c>
-      <c r="D16"/>
+      <c r="D16">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="1"/>
@@ -2437,7 +3059,7 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C20" s="14" t="s">
-        <v>45</v>
+        <v>313</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>46</v>
@@ -2449,7 +3071,7 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C21" s="14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>49</v>
@@ -2461,33 +3083,42 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C22" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="1"/>
+        <v>48</v>
+      </c>
       <c r="F22" s="1"/>
+      <c r="D22"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="1"/>
       <c r="C23" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="1"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B24" s="1"/>
+      <c r="C24" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="1" t="inlineStr">
+      <c r="D24" s="1" t="inlineStr">
         <is>
           <t>auto</t>
         </is>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B24" s="1"/>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C25" s="14" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="49" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D49" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D50" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="4:4" x14ac:dyDescent="0.2">
@@ -2497,22 +3128,22 @@
     </row>
     <row r="53" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D53" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D54" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="55" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D55" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D56" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57" spans="4:4" x14ac:dyDescent="0.2">
@@ -2520,121 +3151,129 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D59" s="1" t="s">
-        <v>60</v>
+    <row r="58" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D58" s="1" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="60" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D60" s="1" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
     </row>
     <row r="61" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D61" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="63" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D63" s="1" t="s">
-        <v>62</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="62" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D62" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="64" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D64" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="65" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D65" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="66" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D66" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="67" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D67" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="68" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D68" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="69" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D69" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="70" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D70" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="71" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D71" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="73" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D73" s="1" t="s">
         <v>71</v>
+      </c>
+    </row>
+    <row r="72" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D72" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="74" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D74" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="75" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D75" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="76" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D76" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="77" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D77" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="78" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D78" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D79" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B7:D7"/>
   </mergeCells>
-  <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D22" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D23" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"rollers,fixed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>$D$50:$D$51</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D9" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>$D$54:$D$57</formula1>
+      <formula1>$D$54:$D$58</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D17" xr:uid="{00000000-0002-0000-0000-000003000000}">
-      <formula1>$D$60:$D$61</formula1>
+      <formula1>$D$61:$D$62</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D14" xr:uid="{00000000-0002-0000-0000-000004000000}">
-      <formula1>$D$64:$D$71</formula1>
+      <formula1>$D$65:$D$72</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D18" xr:uid="{00000000-0002-0000-0000-000005000000}">
-      <formula1>$D$74:$D$78</formula1>
+      <formula1>$D$75:$D$79</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D23" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D24" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>"auto,manual"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D25" xr:uid="{00000000-0002-0000-0000-000007000000}">
+      <formula1>"circular,non-circular"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2643,83 +3282,89 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A2:AB25"/>
+  <dimension ref="A2:AD25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="1" customWidth="1"/>
     <col min="2" max="6" width="10.83203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="13.1640625" customWidth="1"/>
-    <col min="10" max="12" width="10.83203125" style="1" customWidth="1"/>
-    <col min="16" max="18" width="10.83203125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="4.33203125" customWidth="1"/>
+    <col min="10" max="14" width="10.83203125" style="1" customWidth="1"/>
+    <col min="18" max="20" width="10.83203125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="4.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="F2" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="G2" s="40" t="s">
         <v>247</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="H2" s="40" t="s">
         <v>248</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="I2" s="40" t="s">
         <v>249</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="J2" s="27" t="s">
         <v>250</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="K2" s="27" t="s">
         <v>251</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="L2" s="27" t="s">
         <v>252</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="M2" s="27" t="s">
+        <v>311</v>
+      </c>
+      <c r="N2" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="O2" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="P2" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="Q2" s="27" t="s">
         <v>255</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="R2" s="28" t="s">
         <v>256</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="S2" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="T2" s="28" t="s">
         <v>257</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="AB2" t="s">
         <v>258</v>
       </c>
-      <c r="O2" s="27" t="s">
+      <c r="AC2" t="s">
         <v>259</v>
       </c>
-      <c r="P2" s="28" t="s">
+      <c r="AD2" t="s">
         <v>260</v>
       </c>
-      <c r="Q2" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="R2" s="28" t="s">
-        <v>261</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>262</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>263</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -2730,11 +3375,11 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3" t="str">
-        <f t="shared" ref="H3:H22" si="0">IF($G3="","",IFERROR(VLOOKUP($G3,$Z$8:$AB$11,2,0),""))</f>
+        <f t="shared" ref="H3:H22" si="0">IF($G3="","",IFERROR(VLOOKUP($G3,$AB$8:$AD$11,2,0),""))</f>
         <v/>
       </c>
       <c r="I3" s="3" t="str">
-        <f t="shared" ref="I3:I22" si="1">IF($G3="","",IFERROR(VLOOKUP($G3,$Z$8:$AB$11,3,0),""))</f>
+        <f t="shared" ref="I3:I22" si="1">IF($G3="","",IFERROR(VLOOKUP($G3,$AB$8:$AD$11,3,0),""))</f>
         <v/>
       </c>
       <c r="J3" s="3"/>
@@ -2746,17 +3391,19 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
-      <c r="Z3" t="s">
-        <v>265</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>266</v>
-      </c>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
       <c r="AB3" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+        <v>261</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>262</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -2783,11 +3430,13 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
-      <c r="Z4" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="AB4" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -2814,11 +3463,13 @@
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
-      <c r="Z5" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="AB5" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -2845,8 +3496,10 @@
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -2873,8 +3526,10 @@
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -2901,17 +3556,19 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
-      <c r="Z8" t="s">
-        <v>262</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>263</v>
-      </c>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
       <c r="AB8" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+        <v>258</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>259</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -2938,17 +3595,19 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
-      <c r="Z9" t="s">
-        <v>265</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>266</v>
-      </c>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
       <c r="AB9" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+        <v>261</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>262</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -2975,17 +3634,19 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
-      <c r="Z10" t="s">
-        <v>268</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>266</v>
-      </c>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
       <c r="AB10" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" t="s">
+        <v>262</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -3012,17 +3673,19 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-      <c r="Z11" t="s">
-        <v>269</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>266</v>
-      </c>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
       <c r="AB11" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+        <v>265</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>262</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -3049,8 +3712,10 @@
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -3077,8 +3742,10 @@
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -3105,8 +3772,10 @@
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -3133,8 +3802,10 @@
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -3161,8 +3832,10 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -3189,8 +3862,10 @@
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+      <c r="T17" s="3"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -3217,8 +3892,10 @@
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -3245,8 +3922,10 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -3273,8 +3952,10 @@
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -3301,8 +3982,10 @@
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+      <c r="T21" s="3"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -3329,115 +4012,118 @@
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="T23" s="42"/>
-      <c r="U23" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="V23" s="42"/>
+      <c r="W23" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="K24" s="9"/>
       <c r="L24" s="9"/>
-      <c r="T24" s="26"/>
-      <c r="U24" s="9" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="26"/>
+      <c r="W24" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="K25" s="9"/>
       <c r="L25" s="9"/>
-      <c r="T25" s="29"/>
-      <c r="U25" s="9" t="s">
-        <v>102</v>
+      <c r="V25" s="29"/>
+      <c r="W25" s="9" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G22" xr:uid="{00000000-0002-0000-0900-000000000000}">
-      <formula1>$Z$2:$Z$5</formula1>
+      <formula1>$AB$2:$AB$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H22" xr:uid="{00000000-0002-0000-0900-000001000000}">
-      <formula1>$AA$2:$AA$3</formula1>
+      <formula1>$AC$2:$AC$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I22" xr:uid="{00000000-0002-0000-0900-000002000000}">
-      <formula1>$AB$2:$AB$3</formula1>
+      <formula1>$AD$2:$AD$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A2:AA18"/>
+  <dimension ref="A2:AA17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" style="1" customWidth="1"/>
-    <col min="3" max="8" width="10.83203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5" customWidth="1"/>
-    <col min="10" max="17" width="10.83203125" style="1" customWidth="1"/>
+    <col min="3" max="7" width="10.83203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5" customWidth="1"/>
+    <col min="9" max="17" width="10.83203125" style="1" customWidth="1"/>
     <col min="18" max="18" width="5.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="F2" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="E2" s="12" t="s">
+      <c r="G2" s="40" t="s">
+        <v>266</v>
+      </c>
+      <c r="H2" s="40" t="s">
         <v>249</v>
       </c>
-      <c r="F2" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="G2" s="40" t="s">
+      <c r="I2" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="J2" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="K2" s="41" t="s">
+        <v>269</v>
+      </c>
+      <c r="L2" s="41" t="s">
         <v>270</v>
       </c>
-      <c r="H2" s="40" t="s">
-        <v>317</v>
-      </c>
-      <c r="I2" s="40" t="s">
-        <v>253</v>
-      </c>
-      <c r="J2" s="27" t="s">
-        <v>272</v>
-      </c>
-      <c r="K2" s="27" t="s">
-        <v>273</v>
-      </c>
-      <c r="L2" s="41" t="s">
-        <v>274</v>
-      </c>
-      <c r="M2" s="41" t="s">
-        <v>275</v>
+      <c r="M2" s="28" t="s">
+        <v>122</v>
       </c>
       <c r="N2" s="28" t="s">
-        <v>121</v>
+        <v>271</v>
       </c>
       <c r="O2" s="28" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="P2" s="28" t="s">
-        <v>261</v>
+        <v>314</v>
       </c>
       <c r="Q2" s="28" t="s">
-        <v>277</v>
+        <v>315</v>
       </c>
       <c r="Z2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="AA2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
@@ -3461,10 +4147,10 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="Z3" t="s">
-        <v>230</v>
+        <v>316</v>
       </c>
       <c r="AA3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
@@ -3487,6 +4173,9 @@
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
+      <c r="Z4" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
@@ -3508,6 +4197,9 @@
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
+      <c r="Z5" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
@@ -3657,41 +4349,38 @@
       <c r="Q12" s="3"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="I14" s="9"/>
       <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
+      <c r="S15" s="42"/>
+      <c r="T15" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="S16" s="42"/>
-      <c r="T16" t="s">
-        <v>89</v>
+      <c r="S16" s="26"/>
+      <c r="T16" s="9" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="19:20" x14ac:dyDescent="0.2">
-      <c r="S17" s="26"/>
+      <c r="S17" s="29"/>
       <c r="T17" s="9" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="18" spans="19:20" x14ac:dyDescent="0.2">
-      <c r="S18" s="29"/>
-      <c r="T18" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q3:Q12" xr:uid="{00000000-0002-0000-0A00-000000000000}">
-      <formula1>$Z$2:$Z$3</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H12" xr:uid="{00000000-0002-0000-0A00-000001000000}">
+      <formula1>$AA$2:$AA$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I12" xr:uid="{00000000-0002-0000-0A00-000001000000}">
-      <formula1>$AA$2:$AA$3</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:Q12" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+      <formula1>$Z$2:$Z$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3707,22 +4396,22 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -3945,27 +4634,27 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="64" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="59" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="F2" s="54"/>
       <c r="H2" s="59" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="I2" s="54"/>
       <c r="K2" s="59" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="L2" s="54"/>
       <c r="N2" s="59" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="O2" s="54"/>
       <c r="Q2" s="59" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="R2" s="54"/>
     </row>
@@ -3973,71 +4662,71 @@
       <c r="B3" s="66"/>
       <c r="C3" s="67"/>
       <c r="E3" s="32" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="F3" s="33"/>
       <c r="H3" s="32" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="I3" s="33"/>
       <c r="K3" s="32" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="L3" s="33"/>
       <c r="N3" s="32" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="O3" s="33"/>
       <c r="Q3" s="32" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="R3" s="33"/>
       <c r="T3" s="6" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="K4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="L4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="N4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="O4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="Q4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="R4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="U4" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -4054,10 +4743,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="U5" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -4074,7 +4763,7 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="T6" s="1" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="U6" s="9"/>
     </row>
@@ -4363,27 +5052,27 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="68" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="60" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="F2" s="54"/>
       <c r="H2" s="60" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="I2" s="54"/>
       <c r="K2" s="60" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="L2" s="54"/>
       <c r="N2" s="60" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="O2" s="54"/>
       <c r="Q2" s="60" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="R2" s="54"/>
     </row>
@@ -4391,71 +5080,71 @@
       <c r="B3" s="66"/>
       <c r="C3" s="67"/>
       <c r="E3" s="34" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="F3" s="35"/>
       <c r="H3" s="34" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="I3" s="35"/>
       <c r="K3" s="34" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="L3" s="35"/>
       <c r="N3" s="34" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="O3" s="35"/>
       <c r="Q3" s="34" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="R3" s="35"/>
       <c r="T3" s="6" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="K4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="L4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="N4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="O4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="Q4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="R4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="U4" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -4472,10 +5161,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="U5" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -4774,22 +5463,22 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B2" s="50" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="C2" s="50" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="D2" s="50" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E2" s="50" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="F2" s="50" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="G2" s="50" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
@@ -4800,7 +5489,7 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="I3" s="14" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -4822,7 +5511,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="I5" s="14" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -4844,7 +5533,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="I7" s="14" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -4856,7 +5545,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="I8" s="14" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -4868,7 +5557,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="I9" s="14" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="J9" s="3"/>
     </row>
@@ -4888,7 +5577,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="J11" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.2">
@@ -5710,123 +6399,123 @@
   <sheetData>
     <row r="2" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C2" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AD2" s="6"/>
       <c r="AJ2" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C3" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AD3" s="14"/>
       <c r="AJ3" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AK3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C4" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L4" s="42"/>
       <c r="M4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>18</v>
       </c>
       <c r="P4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AD4" s="14"/>
       <c r="AJ4" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AK4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C5" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L5" s="26"/>
       <c r="M5" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P5" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AD5" s="14"/>
       <c r="AJ5" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK5" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C6" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L6" s="29"/>
       <c r="M6" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="P6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AE6" s="1"/>
       <c r="AF6" s="1"/>
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AE7" s="1"/>
       <c r="AF7" s="1"/>
     </row>
     <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="53" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D9" s="52"/>
       <c r="E9" s="52"/>
@@ -5852,7 +6541,7 @@
       <c r="Y9" s="54"/>
       <c r="Z9" s="54"/>
       <c r="AA9" s="53" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AB9" s="54"/>
       <c r="AC9" s="54"/>
@@ -5860,7 +6549,7 @@
       <c r="AE9" s="54"/>
       <c r="AF9" s="54"/>
       <c r="AG9" s="53" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AH9" s="54"/>
       <c r="AI9" s="54"/>
@@ -5877,127 +6566,127 @@
         <v>8</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C10" s="45" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D10" s="48" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F10" s="44" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G10" s="45" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H10" s="44" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I10" s="44" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J10" s="49" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K10" s="49" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M10" s="21" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N10" s="43" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O10" s="44" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P10" s="44" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q10" s="44" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="R10" s="44" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="S10" s="44" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="T10" s="44" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="U10" s="44" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="V10" s="44" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="W10" s="44" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="X10" s="44" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Y10" s="44" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Z10" s="44" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AA10" s="46" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AB10" s="46" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="AC10" s="47" t="s">
+        <v>135</v>
+      </c>
+      <c r="AD10" s="46" t="s">
+        <v>306</v>
+      </c>
+      <c r="AE10" s="46" t="s">
+        <v>307</v>
+      </c>
+      <c r="AF10" s="47" t="s">
+        <v>308</v>
+      </c>
+      <c r="AG10" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="AD10" s="46" t="s">
-        <v>313</v>
-      </c>
-      <c r="AE10" s="46" t="s">
-        <v>314</v>
-      </c>
-      <c r="AF10" s="47" t="s">
-        <v>315</v>
-      </c>
-      <c r="AG10" s="23" t="s">
+      <c r="AH10" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="AI10" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ10" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="AK10" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="AH10" s="23" t="s">
+      <c r="AL10" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="AI10" s="23" t="s">
+      <c r="AM10" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="AJ10" s="23" t="s">
+      <c r="AN10" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="AK10" s="23" t="s">
+      <c r="AO10" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="AL10" s="23" t="s">
+      <c r="AP10" s="23" t="s">
         <v>145</v>
-      </c>
-      <c r="AM10" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="AN10" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="AO10" s="23" t="s">
-        <v>148</v>
-      </c>
-      <c r="AP10" s="23" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.2">
@@ -6024,18 +6713,10 @@
       <c r="G11" s="3">
         <v>19.6</v>
       </c>
-      <c r="H11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K11" s="3">
-        <v>0.0</v>
-      </c>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
       <c r="L11" s="3">
         <v>3.0</v>
       </c>
@@ -6050,35 +6731,17 @@
           <t>none</t>
         </is>
       </c>
-      <c r="P11" s="3">
-        <v>0.0</v>
-      </c>
+      <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-      <c r="S11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="T11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="U11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="V11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="W11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="X11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Y11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Z11" s="3">
-        <v>0.0</v>
-      </c>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
       <c r="AA11" s="3">
         <v>1.2</v>
       </c>
@@ -6088,41 +6751,17 @@
       <c r="AC11" s="3">
         <v>2.744</v>
       </c>
-      <c r="AD11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AE11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AF11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AG11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AH11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AI11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AJ11" s="3" t="inlineStr">
-        <is>
-          <t>lf</t>
-        </is>
-      </c>
-      <c r="AK11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AL11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AM11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AN11" s="3">
-        <v>0.0</v>
-      </c>
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
     </row>
@@ -7558,185 +8197,183 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B2" s="3">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="N2" s="24" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="55" t="inlineStr">
-        <is>
-          <t>Profile Line #1</t>
-        </is>
+      <c r="A4" s="55" t="s">
+        <v>149</v>
       </c>
       <c r="B4" s="52"/>
       <c r="D4" s="55" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E4" s="52"/>
       <c r="G4" s="55" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H4" s="52"/>
       <c r="J4" s="55" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="K4" s="52"/>
       <c r="M4" s="55" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N4" s="52"/>
       <c r="P4" s="55" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="Q4" s="54"/>
       <c r="R4" s="1"/>
       <c r="S4" s="55" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="T4" s="54"/>
       <c r="U4" s="1"/>
       <c r="V4" s="55" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="W4" s="54"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="55" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="Z4" s="54"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="55" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AC4" s="54"/>
       <c r="AE4" s="55" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="AF4" s="54"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="AI4" s="54"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="AL4" s="54"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="AO4" s="54"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="AR4" s="54"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B5" s="37">
         <v>1</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E5" s="37">
         <v>2</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="H5" s="37">
         <v>3</v>
       </c>
       <c r="J5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="K5" s="37">
         <v>4</v>
       </c>
       <c r="M5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="N5" s="37">
         <v>5</v>
       </c>
       <c r="P5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="Q5" s="37">
         <v>6</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="T5" s="37">
         <v>7</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="W5" s="37">
         <v>8</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="Z5" s="37">
         <v>9</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AC5" s="37">
         <v>10</v>
       </c>
       <c r="AE5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AF5" s="37">
         <v>11</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AI5" s="37">
         <v>12</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AL5" s="37">
         <v>13</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AO5" s="37">
         <v>14</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AR5" s="37">
         <v>15</v>
@@ -7829,180 +8466,180 @@
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B7" s="37"/>
       <c r="D7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E7" s="37"/>
       <c r="G7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="H7" s="37"/>
       <c r="J7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="K7" s="37"/>
       <c r="M7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="N7" s="37"/>
       <c r="P7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="Q7" s="37"/>
       <c r="R7" s="1"/>
       <c r="S7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="T7" s="37"/>
       <c r="U7" s="1"/>
       <c r="V7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="W7" s="37"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="Z7" s="37"/>
       <c r="AA7" s="1"/>
       <c r="AB7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AC7" s="37"/>
       <c r="AE7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AF7" s="37"/>
       <c r="AG7" s="1"/>
       <c r="AH7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AI7" s="37"/>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AL7" s="37"/>
       <c r="AM7" s="1"/>
       <c r="AN7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AO7" s="37"/>
       <c r="AP7" s="1"/>
       <c r="AQ7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AR7" s="37"/>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="R8" s="1"/>
       <c r="S8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="U8" s="1"/>
       <c r="V8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AA8" s="1"/>
       <c r="AB8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AC8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AG8" s="1"/>
       <c r="AH8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AI8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AL8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AM8" s="1"/>
       <c r="AN8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AO8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AR8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B9" s="3">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -8043,10 +8680,10 @@
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="B10" s="3">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -8087,10 +8724,10 @@
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="B11" s="3">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -8131,10 +8768,10 @@
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="B12" s="3">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -8824,27 +9461,27 @@
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="S4:T4"/>
     <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="P6:Q6"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="Y4:Z4"/>
     <mergeCell ref="AB6:AC6"/>
     <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="A6:B6"/>
     <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="AH4:AI4"/>
     <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="P6:Q6"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="V6:W6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="Y6:Z6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8878,277 +9515,277 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A4" s="55" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B4" s="52"/>
       <c r="D4" s="55" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E4" s="52"/>
       <c r="G4" s="55" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="H4" s="52"/>
       <c r="J4" s="55" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="K4" s="52"/>
       <c r="M4" s="55" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="N4" s="52"/>
       <c r="P4" s="55" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="Q4" s="54"/>
       <c r="R4" s="1"/>
       <c r="S4" s="55" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="T4" s="54"/>
       <c r="U4" s="1"/>
       <c r="V4" s="55" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="W4" s="54"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="55" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="Z4" s="54"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="55" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="AC4" s="54"/>
       <c r="AE4" s="55" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="AF4" s="54"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="AI4" s="54"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="AL4" s="54"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="AO4" s="54"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="AR4" s="54"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="H5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="K5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="M5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="N5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="P5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="Q5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="T5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="W5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="Z5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="AC5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="AE5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="AF5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="AI5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="AL5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="AO5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="AR5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B6" s="39">
         <v>1</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E6" s="39">
         <v>2</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="H6" s="39">
         <v>3</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="K6" s="39">
         <v>4</v>
       </c>
       <c r="M6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="N6" s="39">
         <v>5</v>
       </c>
       <c r="P6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="Q6" s="39">
         <v>6</v>
       </c>
       <c r="R6" s="1"/>
       <c r="S6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="T6" s="39">
         <v>7</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="W6" s="39">
         <v>8</v>
       </c>
       <c r="X6" s="1"/>
       <c r="Y6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="Z6" s="39">
         <v>9</v>
       </c>
       <c r="AA6" s="1"/>
       <c r="AB6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AC6" s="39">
         <v>10</v>
       </c>
       <c r="AE6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AF6" s="39">
         <v>11</v>
       </c>
       <c r="AG6" s="1"/>
       <c r="AH6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AI6" s="39">
         <v>12</v>
       </c>
       <c r="AJ6" s="1"/>
       <c r="AK6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AL6" s="39">
         <v>13</v>
       </c>
       <c r="AM6" s="1"/>
       <c r="AN6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AO6" s="39">
         <v>14</v>
       </c>
       <c r="AP6" s="1"/>
       <c r="AQ6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AR6" s="39">
         <v>15</v>
@@ -9241,172 +9878,172 @@
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B8" s="39"/>
       <c r="D8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E8" s="39"/>
       <c r="G8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="H8" s="39"/>
       <c r="J8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="K8" s="39"/>
       <c r="M8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="N8" s="39"/>
       <c r="P8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="Q8" s="39"/>
       <c r="R8" s="1"/>
       <c r="S8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="T8" s="39"/>
       <c r="U8" s="1"/>
       <c r="V8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="W8" s="39"/>
       <c r="X8" s="1"/>
       <c r="Y8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="Z8" s="39"/>
       <c r="AA8" s="1"/>
       <c r="AB8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AC8" s="39"/>
       <c r="AE8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AF8" s="39"/>
       <c r="AG8" s="1"/>
       <c r="AH8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AI8" s="39"/>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AL8" s="39"/>
       <c r="AM8" s="1"/>
       <c r="AN8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AO8" s="39"/>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AR8" s="39"/>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="R9" s="1"/>
       <c r="S9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="U9" s="1"/>
       <c r="V9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="X9" s="1"/>
       <c r="Y9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AA9" s="1"/>
       <c r="AB9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AC9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AE9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AF9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AG9" s="1"/>
       <c r="AH9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AI9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AJ9" s="1"/>
       <c r="AK9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AL9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AM9" s="1"/>
       <c r="AN9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AO9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AP9" s="1"/>
       <c r="AQ9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AR9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.2">
@@ -10211,36 +10848,36 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="AN7:AO7"/>
-    <mergeCell ref="M4:N4"/>
     <mergeCell ref="S4:T4"/>
-    <mergeCell ref="AE4:AF4"/>
     <mergeCell ref="AQ7:AR7"/>
     <mergeCell ref="AN4:AO4"/>
     <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="J4:K4"/>
     <mergeCell ref="Y7:Z7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="D4:E4"/>
     <mergeCell ref="AQ4:AR4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="P4:Q4"/>
     <mergeCell ref="Y4:Z4"/>
     <mergeCell ref="AE7:AF7"/>
     <mergeCell ref="AK7:AL7"/>
     <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="AN7:AO7"/>
+    <mergeCell ref="AH7:AI7"/>
+    <mergeCell ref="AE4:AF4"/>
     <mergeCell ref="V4:W4"/>
     <mergeCell ref="V7:W7"/>
+    <mergeCell ref="P7:Q7"/>
     <mergeCell ref="AB7:AC7"/>
-    <mergeCell ref="AH7:AI7"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <conditionalFormatting sqref="B6 A7:B7">
     <cfRule type="expression" dxfId="17" priority="1">
@@ -10337,51 +10974,43 @@
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="59" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B2" s="54"/>
       <c r="D2" s="60" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E2" s="54"/>
       <c r="G2" s="22" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="32" t="s">
-        <v>189</v>
-      </c>
-      <c r="B3" s="33" t="inlineStr">
-        <is>
-          <t>piezo</t>
-        </is>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="B3" s="33"/>
       <c r="D3" s="34" t="s">
-        <v>189</v>
-      </c>
-      <c r="E3" s="35" t="inlineStr">
-        <is>
-          <t>piezo</t>
-        </is>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="E3" s="35"/>
       <c r="G3" s="22"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="H4" s="1"/>
     </row>
@@ -10394,7 +11023,7 @@
         <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -10403,10 +11032,10 @@
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="G6" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H6" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -10543,31 +11172,31 @@
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="E2" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="F2" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="J2" s="5" t="s">
         <v>202</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>206</v>
       </c>
       <c r="K2" s="10" t="s">
         <v>5</v>
@@ -10578,27 +11207,29 @@
         <v>1</v>
       </c>
       <c r="B3" s="3">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="C3" s="3">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Depth</t>
+          <t>Intercept</t>
         </is>
       </c>
-      <c r="E3" s="3">
-        <v>22.639320225</v>
-      </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3">
+        <v>30</v>
+      </c>
+      <c r="G3" s="3">
+        <v>25</v>
+      </c>
       <c r="H3" s="3"/>
       <c r="J3" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -10606,10 +11237,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="3">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -10617,16 +11248,16 @@
         </is>
       </c>
       <c r="E4" s="3">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="J4" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -10641,10 +11272,10 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="J5" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="K5" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -10671,7 +11302,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="J7" s="5" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -10686,9 +11317,8 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="J8" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="K8"/>
+        <v>209</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
@@ -10702,9 +11332,8 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="J9" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="K9"/>
+        <v>210</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
@@ -10718,9 +11347,8 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="J10" s="14" t="s">
-        <v>215</v>
-      </c>
-      <c r="K10"/>
+        <v>211</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
@@ -10734,9 +11362,8 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="J11" s="14" t="s">
-        <v>216</v>
-      </c>
-      <c r="K11"/>
+        <v>212</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
@@ -10750,31 +11377,27 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="J12" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="K12"/>
+        <v>213</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J13" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="K13"/>
+        <v>214</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J14" s="14" t="s">
-        <v>219</v>
-      </c>
-      <c r="K14"/>
+        <v>215</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J15" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="K15"/>
+        <v>216</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J16" s="14" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -10783,9 +11406,8 @@
     </row>
     <row r="17" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J17" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="K17"/>
+        <v>218</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E3:E42">
@@ -10824,16 +11446,16 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>5</v>
@@ -10844,10 +11466,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="F3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -10855,10 +11477,10 @@
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="E4" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F4" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -10866,10 +11488,10 @@
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="E5" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F5" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -10993,128 +11615,128 @@
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B2" t="str">
-        <f>IF(main!$D$23="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
+        <f>IF(main!$D$24="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
         <v>Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.</v>
       </c>
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B4" s="61" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
       <c r="F4" s="61" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G4" s="62"/>
       <c r="H4" s="62"/>
       <c r="J4" s="61" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="K4" s="62"/>
       <c r="L4" s="62"/>
       <c r="N4" s="61" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="R4" s="61" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="S4" s="62"/>
       <c r="T4" s="62"/>
       <c r="V4" s="61" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="W4" s="62"/>
       <c r="X4" s="62"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="39"/>
       <c r="F5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G5" s="57"/>
       <c r="H5" s="39"/>
       <c r="J5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="K5" s="57"/>
       <c r="L5" s="39"/>
       <c r="N5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="O5" s="57"/>
       <c r="P5" s="39"/>
       <c r="R5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="S5" s="57"/>
       <c r="T5" s="39"/>
       <c r="V5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="W5" s="57"/>
       <c r="X5" s="39"/>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.2">
@@ -11499,18 +12121,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="R4:T4"/>
+    <mergeCell ref="B4:D4"/>
     <mergeCell ref="V5:W5"/>
+    <mergeCell ref="F4:H4"/>
     <mergeCell ref="V4:X4"/>
-    <mergeCell ref="R4:T4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N5:O5"/>
     <mergeCell ref="R5:S5"/>
-    <mergeCell ref="F5:G5"/>
     <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5 H5 L5 P5 T5 X5" xr:uid="{00000000-0002-0000-0700-000000000000}">
@@ -11542,128 +12164,128 @@
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B2" t="str">
-        <f>IF(main!$D$23="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
+        <f>IF(main!$D$24="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
         <v>Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.</v>
       </c>
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B4" s="63" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
       <c r="F4" s="63" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="G4" s="62"/>
       <c r="H4" s="62"/>
       <c r="J4" s="63" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="K4" s="62"/>
       <c r="L4" s="62"/>
       <c r="N4" s="63" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="R4" s="63" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="S4" s="62"/>
       <c r="T4" s="62"/>
       <c r="V4" s="63" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="W4" s="62"/>
       <c r="X4" s="62"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="39"/>
       <c r="F5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G5" s="57"/>
       <c r="H5" s="39"/>
       <c r="J5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="K5" s="57"/>
       <c r="L5" s="39"/>
       <c r="N5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="O5" s="57"/>
       <c r="P5" s="39"/>
       <c r="R5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="S5" s="57"/>
       <c r="T5" s="39"/>
       <c r="V5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="W5" s="57"/>
       <c r="X5" s="39"/>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.2">
@@ -12048,18 +12670,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="R4:T4"/>
+    <mergeCell ref="B4:D4"/>
     <mergeCell ref="V5:W5"/>
+    <mergeCell ref="F4:H4"/>
     <mergeCell ref="V4:X4"/>
-    <mergeCell ref="R4:T4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N5:O5"/>
     <mergeCell ref="R5:S5"/>
-    <mergeCell ref="F5:G5"/>
     <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5 H5 L5 P5 T5 X5" xr:uid="{00000000-0002-0000-0800-000000000000}">
